--- a/Schlagdifferentialgleichung/Programme/excelDir/CharactExponentenMultiplikatoren_ebeta0dot000_mu0_mu10_Auswahl1.xlsx
+++ b/Schlagdifferentialgleichung/Programme/excelDir/CharactExponentenMultiplikatoren_ebeta0dot000_mu0_mu10_Auswahl1.xlsx
@@ -13,7 +13,94 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="87">
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
   <si>
     <t>muChar</t>
   </si>
@@ -268,91 +355,91 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="X1" s="0" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="Y1" s="0" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="Z1" s="0" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="AA1" s="0" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="AB1" s="0" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="AC1" s="0" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2">

--- a/Schlagdifferentialgleichung/Programme/excelDir/CharactExponentenMultiplikatoren_ebeta0dot000_mu0_mu10_Auswahl1.xlsx
+++ b/Schlagdifferentialgleichung/Programme/excelDir/CharactExponentenMultiplikatoren_ebeta0dot000_mu0_mu10_Auswahl1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="319">
   <si>
     <t>muChar</t>
   </si>
@@ -271,6 +271,702 @@
   </si>
   <si>
     <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>muChar</t>
+  </si>
+  <si>
+    <t>RealCharExp01</t>
+  </si>
+  <si>
+    <t>RealCharExp02</t>
+  </si>
+  <si>
+    <t>RealCharExp03</t>
+  </si>
+  <si>
+    <t>RealCharExp04</t>
+  </si>
+  <si>
+    <t>RealCharExp05</t>
+  </si>
+  <si>
+    <t>RealCharExp06</t>
+  </si>
+  <si>
+    <t>ImagCharExp01</t>
+  </si>
+  <si>
+    <t>ImagCharExp02</t>
+  </si>
+  <si>
+    <t>ImagCharExp03</t>
+  </si>
+  <si>
+    <t>ImagCharExp04</t>
+  </si>
+  <si>
+    <t>ImagCharExp05</t>
+  </si>
+  <si>
+    <t>ImagCharExp06</t>
+  </si>
+  <si>
+    <t>RealCharMult01</t>
+  </si>
+  <si>
+    <t>RealCharMult02</t>
+  </si>
+  <si>
+    <t>RealCharMult03</t>
+  </si>
+  <si>
+    <t>RealCharMult04</t>
+  </si>
+  <si>
+    <t>RealCharMult05</t>
+  </si>
+  <si>
+    <t>RealCharMult06</t>
+  </si>
+  <si>
+    <t>ImagCharMult01</t>
+  </si>
+  <si>
+    <t>ImagCharMult02</t>
+  </si>
+  <si>
+    <t>ImagCharMult03</t>
+  </si>
+  <si>
+    <t>ImagCharMult04</t>
+  </si>
+  <si>
+    <t>ImagCharMult05</t>
+  </si>
+  <si>
+    <t>ImagCharMult06</t>
+  </si>
+  <si>
+    <t>RealCharExp1Corrected</t>
+  </si>
+  <si>
+    <t>RealCharExp2Corrected</t>
+  </si>
+  <si>
+    <t>ImagCharExp1Corrected</t>
   </si>
   <si>
     <t>ImagCharExp2Corrected</t>
@@ -323,16 +1019,16 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.48828125" customWidth="true"/>
-    <col min="2" max="2" width="14.7109375" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="13.37890625" customWidth="true"/>
-    <col min="6" max="6" width="13.37890625" customWidth="true"/>
-    <col min="7" max="7" width="13.37890625" customWidth="true"/>
+    <col min="2" max="2" width="13.37890625" customWidth="true"/>
+    <col min="3" max="3" width="13.37890625" customWidth="true"/>
+    <col min="4" max="4" width="13.37890625" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
+    <col min="6" max="6" width="14.7109375" customWidth="true"/>
+    <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="16.046875" customWidth="true"/>
-    <col min="9" max="9" width="16.046875" customWidth="true"/>
+    <col min="9" max="9" width="16.37890625" customWidth="true"/>
     <col min="10" max="10" width="16.046875" customWidth="true"/>
-    <col min="11" max="11" width="16.37890625" customWidth="true"/>
+    <col min="11" max="11" width="16.046875" customWidth="true"/>
     <col min="12" max="12" width="16.046875" customWidth="true"/>
     <col min="13" max="13" width="16.046875" customWidth="true"/>
     <col min="14" max="14" width="16.046875" customWidth="true"/>
@@ -341,105 +1037,105 @@
     <col min="17" max="17" width="16.046875" customWidth="true"/>
     <col min="18" max="18" width="16.046875" customWidth="true"/>
     <col min="19" max="19" width="16.046875" customWidth="true"/>
-    <col min="20" max="20" width="16.046875" customWidth="true"/>
+    <col min="20" max="20" width="16.37890625" customWidth="true"/>
     <col min="21" max="21" width="16.046875" customWidth="true"/>
     <col min="22" max="22" width="15.37890625" customWidth="true"/>
     <col min="23" max="23" width="16.046875" customWidth="true"/>
-    <col min="24" max="24" width="16.37890625" customWidth="true"/>
-    <col min="25" max="25" width="15.7109375" customWidth="true"/>
+    <col min="24" max="24" width="16.046875" customWidth="true"/>
+    <col min="25" max="25" width="15.37890625" customWidth="true"/>
     <col min="26" max="26" width="20.48828125" customWidth="true"/>
-    <col min="27" max="27" width="20.93359375" customWidth="true"/>
-    <col min="28" max="28" width="20.48828125" customWidth="true"/>
+    <col min="27" max="27" width="20.48828125" customWidth="true"/>
+    <col min="28" max="28" width="20.93359375" customWidth="true"/>
     <col min="29" max="29" width="20.93359375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>59</v>
+        <v>291</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>60</v>
+        <v>292</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>61</v>
+        <v>293</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>63</v>
+        <v>295</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>64</v>
+        <v>296</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>65</v>
+        <v>297</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>66</v>
+        <v>298</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>67</v>
+        <v>299</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>70</v>
+        <v>302</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>71</v>
+        <v>303</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>72</v>
+        <v>304</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>73</v>
+        <v>305</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>74</v>
+        <v>306</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>75</v>
+        <v>307</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>76</v>
+        <v>308</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>78</v>
+        <v>310</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="X1" s="0" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="Y1" s="0" t="s">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="Z1" s="0" t="s">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="AA1" s="0" t="s">
-        <v>84</v>
+        <v>316</v>
       </c>
       <c r="AB1" s="0" t="s">
-        <v>85</v>
+        <v>317</v>
       </c>
       <c r="AC1" s="0" t="s">
-        <v>86</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
@@ -522,10 +1218,10 @@
         <v>-0.32325042726113407</v>
       </c>
       <c r="AA2" s="0">
+        <v>-0.32325042726113273</v>
+      </c>
+      <c r="AB2" s="0">
         <v>-1.0536865417444952</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>-0.32325042726113273</v>
       </c>
       <c r="AC2" s="0">
         <v>1.0536865417444952</v>
@@ -611,13 +1307,13 @@
         <v>-0.32325042726113357</v>
       </c>
       <c r="AA3" s="0">
-        <v>-1.0544409847499825</v>
+        <v>-0.32325042726113323</v>
       </c>
       <c r="AB3" s="0">
-        <v>-0.32325042726113323</v>
+        <v>-1.0544409847499823</v>
       </c>
       <c r="AC3" s="0">
-        <v>1.0544409847499825</v>
+        <v>1.0544409847499823</v>
       </c>
     </row>
     <row r="4">
@@ -700,10 +1396,10 @@
         <v>-0.32325042726113318</v>
       </c>
       <c r="AA4" s="0">
+        <v>-0.32325042726113362</v>
+      </c>
+      <c r="AB4" s="0">
         <v>-1.0562584318322303</v>
-      </c>
-      <c r="AB4" s="0">
-        <v>-0.32325042726113362</v>
       </c>
       <c r="AC4" s="0">
         <v>1.0562584318322303</v>
@@ -789,10 +1485,10 @@
         <v>-0.32325042726113318</v>
       </c>
       <c r="AA5" s="0">
+        <v>-0.32325042726113362</v>
+      </c>
+      <c r="AB5" s="0">
         <v>-1.0579183220047219</v>
-      </c>
-      <c r="AB5" s="0">
-        <v>-0.32325042726113362</v>
       </c>
       <c r="AC5" s="0">
         <v>1.0579183220047219</v>
@@ -809,16 +1505,16 @@
         <v>-0.32325042726113384</v>
       </c>
       <c r="D6" s="0">
+        <v>-0.32325042726113312</v>
+      </c>
+      <c r="E6" s="0">
+        <v>-0.32325042726113312</v>
+      </c>
+      <c r="F6" s="0">
         <v>-0.32325042726113323</v>
       </c>
-      <c r="E6" s="0">
+      <c r="G6" s="0">
         <v>-0.32325042726113323</v>
-      </c>
-      <c r="F6" s="0">
-        <v>-0.32325042726113312</v>
-      </c>
-      <c r="G6" s="0">
-        <v>-0.32325042726113312</v>
       </c>
       <c r="H6" s="0">
         <v>-0.057548816284477423</v>
@@ -827,16 +1523,16 @@
         <v>0.057548816284477423</v>
       </c>
       <c r="J6" s="0">
+        <v>-0.057548816284478714</v>
+      </c>
+      <c r="K6" s="0">
+        <v>0.057548816284478714</v>
+      </c>
+      <c r="L6" s="0">
         <v>-0.057548816284477798</v>
       </c>
-      <c r="K6" s="0">
+      <c r="M6" s="0">
         <v>0.057548816284477798</v>
-      </c>
-      <c r="L6" s="0">
-        <v>-0.057548816284478714</v>
-      </c>
-      <c r="M6" s="0">
-        <v>0.057548816284478714</v>
       </c>
       <c r="N6" s="0">
         <v>0.12271480768700738</v>
@@ -845,16 +1541,16 @@
         <v>0.12271480768700738</v>
       </c>
       <c r="P6" s="0">
+        <v>0.12271480768700757</v>
+      </c>
+      <c r="Q6" s="0">
+        <v>0.12271480768700757</v>
+      </c>
+      <c r="R6" s="0">
         <v>0.12271480768700774</v>
       </c>
-      <c r="Q6" s="0">
+      <c r="S6" s="0">
         <v>0.12271480768700774</v>
-      </c>
-      <c r="R6" s="0">
-        <v>0.12271480768700757</v>
-      </c>
-      <c r="S6" s="0">
-        <v>0.12271480768700757</v>
       </c>
       <c r="T6" s="0">
         <v>-0.04641308035586672</v>
@@ -863,25 +1559,25 @@
         <v>0.04641308035586672</v>
       </c>
       <c r="V6" s="0">
+        <v>-0.046413080355867928</v>
+      </c>
+      <c r="W6" s="0">
+        <v>0.046413080355867928</v>
+      </c>
+      <c r="X6" s="0">
         <v>-0.046413080355867185</v>
       </c>
-      <c r="W6" s="0">
+      <c r="Y6" s="0">
         <v>0.046413080355867185</v>
       </c>
-      <c r="X6" s="0">
-        <v>-0.046413080355867928</v>
-      </c>
-      <c r="Y6" s="0">
-        <v>0.046413080355867928</v>
-      </c>
       <c r="Z6" s="0">
-        <v>-0.32325042726113357</v>
+        <v>-0.32325042726113368</v>
       </c>
       <c r="AA6" s="0">
+        <v>-0.32325042726113312</v>
+      </c>
+      <c r="AB6" s="0">
         <v>-1.0575488162844786</v>
-      </c>
-      <c r="AB6" s="0">
-        <v>-0.32325042726113323</v>
       </c>
       <c r="AC6" s="0">
         <v>1.0575488162844786</v>
@@ -892,16 +1588,16 @@
         <v>0.5</v>
       </c>
       <c r="B7" s="0">
+        <v>-0.32325042726113323</v>
+      </c>
+      <c r="C7" s="0">
+        <v>-0.32325042726113323</v>
+      </c>
+      <c r="D7" s="0">
         <v>-0.32325042726113334</v>
       </c>
-      <c r="C7" s="0">
+      <c r="E7" s="0">
         <v>-0.32325042726113334</v>
-      </c>
-      <c r="D7" s="0">
-        <v>-0.32325042726113323</v>
-      </c>
-      <c r="E7" s="0">
-        <v>-0.32325042726113323</v>
       </c>
       <c r="F7" s="0">
         <v>-0.32325042726113207</v>
@@ -910,16 +1606,16 @@
         <v>-0.32325042726113207</v>
       </c>
       <c r="H7" s="0">
+        <v>-0.052216268896802115</v>
+      </c>
+      <c r="I7" s="0">
+        <v>0.052216268896802115</v>
+      </c>
+      <c r="J7" s="0">
         <v>-0.052216268896800894</v>
       </c>
-      <c r="I7" s="0">
+      <c r="K7" s="0">
         <v>0.052216268896800894</v>
-      </c>
-      <c r="J7" s="0">
-        <v>-0.052216268896802115</v>
-      </c>
-      <c r="K7" s="0">
-        <v>0.052216268896802115</v>
       </c>
       <c r="L7" s="0">
         <v>-0.052216268896802753</v>
@@ -928,16 +1624,16 @@
         <v>0.052216268896802753</v>
       </c>
       <c r="N7" s="0">
+        <v>0.12420073076000025</v>
+      </c>
+      <c r="O7" s="0">
+        <v>0.12420073076000025</v>
+      </c>
+      <c r="P7" s="0">
         <v>0.12420073076000053</v>
       </c>
-      <c r="O7" s="0">
+      <c r="Q7" s="0">
         <v>0.12420073076000053</v>
-      </c>
-      <c r="P7" s="0">
-        <v>0.12420073076000025</v>
-      </c>
-      <c r="Q7" s="0">
-        <v>0.12420073076000025</v>
       </c>
       <c r="R7" s="0">
         <v>0.12420073076000099</v>
@@ -946,16 +1642,16 @@
         <v>0.12420073076000099</v>
       </c>
       <c r="T7" s="0">
+        <v>-0.042276193448102725</v>
+      </c>
+      <c r="U7" s="0">
+        <v>0.042276193448102725</v>
+      </c>
+      <c r="V7" s="0">
         <v>-0.042276193448101761</v>
       </c>
-      <c r="U7" s="0">
+      <c r="W7" s="0">
         <v>0.042276193448101761</v>
-      </c>
-      <c r="V7" s="0">
-        <v>-0.042276193448102725</v>
-      </c>
-      <c r="W7" s="0">
-        <v>0.042276193448102725</v>
       </c>
       <c r="X7" s="0">
         <v>-0.04227619344810353</v>
@@ -964,16 +1660,16 @@
         <v>0.04227619344810353</v>
       </c>
       <c r="Z7" s="0">
-        <v>-0.32325042726113334</v>
+        <v>-0.32325042726113323</v>
       </c>
       <c r="AA7" s="0">
-        <v>-1.0522162688968026</v>
+        <v>-0.32325042726113357</v>
       </c>
       <c r="AB7" s="0">
-        <v>-0.32325042726113357</v>
+        <v>-1.0522162688968022</v>
       </c>
       <c r="AC7" s="0">
-        <v>1.0522162688968026</v>
+        <v>1.0522162688968022</v>
       </c>
     </row>
     <row r="8">
@@ -987,16 +1683,16 @@
         <v>-0.32325042726113318</v>
       </c>
       <c r="D8" s="0">
+        <v>-0.32325042726113273</v>
+      </c>
+      <c r="E8" s="0">
+        <v>-0.32325042726113273</v>
+      </c>
+      <c r="F8" s="0">
         <v>-0.32325042726113307</v>
       </c>
-      <c r="E8" s="0">
+      <c r="G8" s="0">
         <v>-0.32325042726113307</v>
-      </c>
-      <c r="F8" s="0">
-        <v>-0.32325042726113273</v>
-      </c>
-      <c r="G8" s="0">
-        <v>-0.32325042726113273</v>
       </c>
       <c r="H8" s="0">
         <v>-0.034651489906914537</v>
@@ -1005,16 +1701,16 @@
         <v>0.034651489906914537</v>
       </c>
       <c r="J8" s="0">
+        <v>-0.034651489906914267</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0.034651489906914267</v>
+      </c>
+      <c r="L8" s="0">
         <v>-0.034651489906913066</v>
       </c>
-      <c r="K8" s="0">
+      <c r="M8" s="0">
         <v>0.034651489906913066</v>
-      </c>
-      <c r="L8" s="0">
-        <v>-0.034651489906914267</v>
-      </c>
-      <c r="M8" s="0">
-        <v>0.034651489906914267</v>
       </c>
       <c r="N8" s="0">
         <v>0.12810137135433475</v>
@@ -1023,16 +1719,16 @@
         <v>0.12810137135433475</v>
       </c>
       <c r="P8" s="0">
+        <v>0.12810137135433511</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>0.12810137135433511</v>
+      </c>
+      <c r="R8" s="0">
         <v>0.12810137135433514</v>
       </c>
-      <c r="Q8" s="0">
+      <c r="S8" s="0">
         <v>0.12810137135433514</v>
-      </c>
-      <c r="R8" s="0">
-        <v>0.12810137135433511</v>
-      </c>
-      <c r="S8" s="0">
-        <v>0.12810137135433511</v>
       </c>
       <c r="T8" s="0">
         <v>-0.02833966673971863</v>
@@ -1041,28 +1737,28 @@
         <v>0.02833966673971863</v>
       </c>
       <c r="V8" s="0">
+        <v>-0.02833966673971848</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0.02833966673971848</v>
+      </c>
+      <c r="X8" s="0">
         <v>-0.028339666739717471</v>
       </c>
-      <c r="W8" s="0">
+      <c r="Y8" s="0">
         <v>0.028339666739717471</v>
       </c>
-      <c r="X8" s="0">
-        <v>-0.02833966673971848</v>
-      </c>
-      <c r="Y8" s="0">
-        <v>0.02833966673971848</v>
-      </c>
       <c r="Z8" s="0">
-        <v>-0.32325042726113318</v>
+        <v>-0.32325042726113407</v>
       </c>
       <c r="AA8" s="0">
-        <v>-1.0346514899069146</v>
+        <v>-0.32325042726113273</v>
       </c>
       <c r="AB8" s="0">
-        <v>-0.32325042726113373</v>
+        <v>-1.0346514899069144</v>
       </c>
       <c r="AC8" s="0">
-        <v>1.0346514899069146</v>
+        <v>1.0346514899069144</v>
       </c>
     </row>
     <row r="9">
@@ -1070,40 +1766,40 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="B9" s="0">
+        <v>-0.36498371736349239</v>
+      </c>
+      <c r="C9" s="0">
+        <v>-0.36498371736349239</v>
+      </c>
+      <c r="D9" s="0">
         <v>-0.36498371736349067</v>
       </c>
-      <c r="C9" s="0">
+      <c r="E9" s="0">
         <v>-0.28151713715877524</v>
       </c>
-      <c r="D9" s="0">
+      <c r="F9" s="0">
         <v>-0.28151713715877524</v>
       </c>
-      <c r="E9" s="0">
+      <c r="G9" s="0">
         <v>-0.28151713715877458</v>
       </c>
-      <c r="F9" s="0">
-        <v>-0.36498371736349239</v>
-      </c>
-      <c r="G9" s="0">
-        <v>-0.36498371736349239</v>
-      </c>
       <c r="H9" s="0">
-        <v>0</v>
+        <v>-1.3501558495502491e-15</v>
       </c>
       <c r="I9" s="0">
+        <v>1.3501558495502491e-15</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0">
         <v>-6.9999800653743587e-16</v>
       </c>
-      <c r="J9" s="0">
+      <c r="L9" s="0">
         <v>6.9999800653743587e-16</v>
       </c>
-      <c r="K9" s="0">
-        <v>0</v>
-      </c>
-      <c r="L9" s="0">
-        <v>-1.3501558495502491e-15</v>
-      </c>
       <c r="M9" s="0">
-        <v>1.3501558495502491e-15</v>
+        <v>0</v>
       </c>
       <c r="N9" s="0">
         <v>0.10093683737444575</v>
@@ -1142,16 +1838,16 @@
         <v>0</v>
       </c>
       <c r="Z9" s="0">
-        <v>-0.36498371736349222</v>
+        <v>-0.36498371736349156</v>
       </c>
       <c r="AA9" s="0">
-        <v>-1.0000000000000013</v>
+        <v>-0.28151713715877524</v>
       </c>
       <c r="AB9" s="0">
-        <v>-0.28151713715877458</v>
+        <v>-0.99999999999999933</v>
       </c>
       <c r="AC9" s="0">
-        <v>1.0000000000000013</v>
+        <v>0.99999999999999933</v>
       </c>
     </row>
     <row r="10">
@@ -1159,28 +1855,28 @@
         <v>0.80000000000000004</v>
       </c>
       <c r="B10" s="0">
+        <v>-0.40471751255019511</v>
+      </c>
+      <c r="C10" s="0">
+        <v>-0.40471751255019511</v>
+      </c>
+      <c r="D10" s="0">
+        <v>-0.4047175125501915</v>
+      </c>
+      <c r="E10" s="0">
+        <v>-0.24178334197207396</v>
+      </c>
+      <c r="F10" s="0">
+        <v>-0.24178334197207216</v>
+      </c>
+      <c r="G10" s="0">
         <v>-0.24178334197207152</v>
       </c>
-      <c r="C10" s="0">
-        <v>-0.24178334197207216</v>
-      </c>
-      <c r="D10" s="0">
-        <v>-0.24178334197207396</v>
-      </c>
-      <c r="E10" s="0">
-        <v>-0.4047175125501915</v>
-      </c>
-      <c r="F10" s="0">
-        <v>-0.40471751255019511</v>
-      </c>
-      <c r="G10" s="0">
-        <v>-0.40471751255019511</v>
-      </c>
       <c r="H10" s="0">
-        <v>0</v>
+        <v>-6.1536813147660791e-16</v>
       </c>
       <c r="I10" s="0">
-        <v>0</v>
+        <v>6.1536813147660791e-16</v>
       </c>
       <c r="J10" s="0">
         <v>0</v>
@@ -1189,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="0">
-        <v>-6.1536813147660791e-16</v>
+        <v>0</v>
       </c>
       <c r="M10" s="0">
-        <v>6.1536813147660791e-16</v>
+        <v>0</v>
       </c>
       <c r="N10" s="0">
         <v>0.078636828884671883</v>
@@ -1231,16 +1927,16 @@
         <v>0</v>
       </c>
       <c r="Z10" s="0">
-        <v>-0.24178334197207152</v>
+        <v>-0.40471751255019284</v>
       </c>
       <c r="AA10" s="0">
-        <v>-1.0000000000000007</v>
+        <v>-0.24178334197207396</v>
       </c>
       <c r="AB10" s="0">
-        <v>-0.40471751255019528</v>
+        <v>-1</v>
       </c>
       <c r="AC10" s="0">
-        <v>1.0000000000000007</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1248,37 +1944,37 @@
         <v>0.90000000000000002</v>
       </c>
       <c r="B11" s="0">
+        <v>-0.44179985129861504</v>
+      </c>
+      <c r="C11" s="0">
+        <v>-0.44179985129861238</v>
+      </c>
+      <c r="D11" s="0">
+        <v>-0.44179985129861088</v>
+      </c>
+      <c r="E11" s="0">
+        <v>-0.20470100322365464</v>
+      </c>
+      <c r="F11" s="0">
+        <v>-0.20470100322365464</v>
+      </c>
+      <c r="G11" s="0">
         <v>-0.20470100322364962</v>
       </c>
-      <c r="C11" s="0">
-        <v>-0.20470100322365464</v>
-      </c>
-      <c r="D11" s="0">
-        <v>-0.20470100322365464</v>
-      </c>
-      <c r="E11" s="0">
-        <v>-0.44179985129861088</v>
-      </c>
-      <c r="F11" s="0">
-        <v>-0.44179985129861238</v>
-      </c>
-      <c r="G11" s="0">
-        <v>-0.44179985129861504</v>
-      </c>
       <c r="H11" s="0">
         <v>0</v>
       </c>
       <c r="I11" s="0">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0">
         <v>-1.2789064389463208e-16</v>
       </c>
-      <c r="J11" s="0">
+      <c r="L11" s="0">
         <v>1.2789064389463208e-16</v>
-      </c>
-      <c r="K11" s="0">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0">
-        <v>0</v>
       </c>
       <c r="M11" s="0">
         <v>0</v>
@@ -1320,16 +2016,16 @@
         <v>0</v>
       </c>
       <c r="Z11" s="0">
-        <v>-0.20470100322364962</v>
+        <v>-0.44179985129861216</v>
       </c>
       <c r="AA11" s="0">
-        <v>-1.0000000000000002</v>
+        <v>-0.20470100322365464</v>
       </c>
       <c r="AB11" s="0">
-        <v>-0.44179985129861721</v>
+        <v>-0.99999999999999989</v>
       </c>
       <c r="AC11" s="0">
-        <v>1.0000000000000002</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="12">
@@ -1337,40 +2033,40 @@
         <v>1</v>
       </c>
       <c r="B12" s="0">
+        <v>-0.47997298220040863</v>
+      </c>
+      <c r="C12" s="0">
+        <v>-0.47997298220040863</v>
+      </c>
+      <c r="D12" s="0">
+        <v>-0.47997298220040358</v>
+      </c>
+      <c r="E12" s="0">
+        <v>-0.16652787232185814</v>
+      </c>
+      <c r="F12" s="0">
         <v>-0.16652787232185748</v>
       </c>
-      <c r="C12" s="0">
+      <c r="G12" s="0">
         <v>-0.16652787232185748</v>
       </c>
-      <c r="D12" s="0">
-        <v>-0.16652787232185814</v>
-      </c>
-      <c r="E12" s="0">
-        <v>-0.47997298220040358</v>
-      </c>
-      <c r="F12" s="0">
-        <v>-0.47997298220040863</v>
-      </c>
-      <c r="G12" s="0">
-        <v>-0.47997298220040863</v>
-      </c>
       <c r="H12" s="0">
+        <v>-8.879459637163465e-16</v>
+      </c>
+      <c r="I12" s="0">
+        <v>8.879459637163465e-16</v>
+      </c>
+      <c r="J12" s="0">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0">
+        <v>0</v>
+      </c>
+      <c r="L12" s="0">
         <v>-8.1357772963239231e-16</v>
       </c>
-      <c r="I12" s="0">
+      <c r="M12" s="0">
         <v>8.1357772963239231e-16</v>
-      </c>
-      <c r="J12" s="0">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0">
-        <v>0</v>
-      </c>
-      <c r="L12" s="0">
-        <v>-8.879459637163465e-16</v>
-      </c>
-      <c r="M12" s="0">
-        <v>8.879459637163465e-16</v>
       </c>
       <c r="N12" s="0">
         <v>0.049008614529227293</v>
@@ -1409,13 +2105,13 @@
         <v>1.7954178467471398e-15</v>
       </c>
       <c r="Z12" s="0">
-        <v>-0.16652787232185748</v>
+        <v>-0.47997298220040863</v>
       </c>
       <c r="AA12" s="0">
+        <v>-0.16652787232185814</v>
+      </c>
+      <c r="AB12" s="0">
         <v>-1.0000000000000009</v>
-      </c>
-      <c r="AB12" s="0">
-        <v>-0.47997298220040929</v>
       </c>
       <c r="AC12" s="0">
         <v>1.0000000000000009</v>
@@ -1426,37 +2122,37 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B13" s="0">
+        <v>-0.51997171709658463</v>
+      </c>
+      <c r="C13" s="0">
+        <v>-0.51997171709658241</v>
+      </c>
+      <c r="D13" s="0">
+        <v>-0.51997171709658241</v>
+      </c>
+      <c r="E13" s="0">
+        <v>-0.12652913742568561</v>
+      </c>
+      <c r="F13" s="0">
+        <v>-0.1265291374256842</v>
+      </c>
+      <c r="G13" s="0">
         <v>-0.12652913742568264</v>
       </c>
-      <c r="C13" s="0">
-        <v>-0.1265291374256842</v>
-      </c>
-      <c r="D13" s="0">
-        <v>-0.12652913742568561</v>
-      </c>
-      <c r="E13" s="0">
-        <v>-0.51997171709658241</v>
-      </c>
-      <c r="F13" s="0">
-        <v>-0.51997171709658241</v>
-      </c>
-      <c r="G13" s="0">
-        <v>-0.51997171709658463</v>
-      </c>
       <c r="H13" s="0">
         <v>0</v>
       </c>
       <c r="I13" s="0">
-        <v>0</v>
+        <v>-3.7999167445005124e-15</v>
       </c>
       <c r="J13" s="0">
-        <v>0</v>
+        <v>3.7999167445005124e-15</v>
       </c>
       <c r="K13" s="0">
-        <v>-3.7999167445005124e-15</v>
+        <v>0</v>
       </c>
       <c r="L13" s="0">
-        <v>3.7999167445005124e-15</v>
+        <v>0</v>
       </c>
       <c r="M13" s="0">
         <v>0</v>
@@ -1498,16 +2194,16 @@
         <v>0</v>
       </c>
       <c r="Z13" s="0">
-        <v>-0.12652913742568264</v>
+        <v>-0.51997171709658119</v>
       </c>
       <c r="AA13" s="0">
-        <v>-1.0000000000000038</v>
+        <v>-0.12652913742568561</v>
       </c>
       <c r="AB13" s="0">
-        <v>-0.51997171709658419</v>
+        <v>-1</v>
       </c>
       <c r="AC13" s="0">
-        <v>1.0000000000000038</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1515,22 +2211,22 @@
         <v>1.2000000000000002</v>
       </c>
       <c r="B14" s="0">
+        <v>-0.56189849489578725</v>
+      </c>
+      <c r="C14" s="0">
+        <v>-0.56189849489578292</v>
+      </c>
+      <c r="D14" s="0">
+        <v>-0.56189849489577826</v>
+      </c>
+      <c r="E14" s="0">
+        <v>-0.084602359626487933</v>
+      </c>
+      <c r="F14" s="0">
+        <v>-0.084602359626487864</v>
+      </c>
+      <c r="G14" s="0">
         <v>-0.084602359626487031</v>
-      </c>
-      <c r="C14" s="0">
-        <v>-0.084602359626487933</v>
-      </c>
-      <c r="D14" s="0">
-        <v>-0.084602359626487864</v>
-      </c>
-      <c r="E14" s="0">
-        <v>-0.56189849489577826</v>
-      </c>
-      <c r="F14" s="0">
-        <v>-0.56189849489578292</v>
-      </c>
-      <c r="G14" s="0">
-        <v>-0.56189849489578725</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -1587,13 +2283,13 @@
         <v>0</v>
       </c>
       <c r="Z14" s="0">
-        <v>-0.084602359626487031</v>
+        <v>-0.56189849489577881</v>
       </c>
       <c r="AA14" s="0">
+        <v>-0.084602359626487933</v>
+      </c>
+      <c r="AB14" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB14" s="0">
-        <v>-0.5618984948957797</v>
       </c>
       <c r="AC14" s="0">
         <v>1</v>
@@ -1604,40 +2300,40 @@
         <v>1.3</v>
       </c>
       <c r="B15" s="0">
+        <v>-0.60565245633499731</v>
+      </c>
+      <c r="C15" s="0">
+        <v>-0.60565245633499731</v>
+      </c>
+      <c r="D15" s="0">
+        <v>-0.60565245633499343</v>
+      </c>
+      <c r="E15" s="0">
+        <v>-0.04084839818726619</v>
+      </c>
+      <c r="F15" s="0">
         <v>-0.040848398187265295</v>
       </c>
-      <c r="C15" s="0">
+      <c r="G15" s="0">
         <v>-0.040848398187265295</v>
       </c>
-      <c r="D15" s="0">
-        <v>-0.04084839818726619</v>
-      </c>
-      <c r="E15" s="0">
-        <v>-0.60565245633499343</v>
-      </c>
-      <c r="F15" s="0">
-        <v>-0.60565245633499731</v>
-      </c>
-      <c r="G15" s="0">
-        <v>-0.60565245633499731</v>
-      </c>
       <c r="H15" s="0">
+        <v>-4.2375290271750751e-15</v>
+      </c>
+      <c r="I15" s="0">
+        <v>4.2375290271750751e-15</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0">
         <v>-5.4314006914528575e-16</v>
       </c>
-      <c r="I15" s="0">
+      <c r="M15" s="0">
         <v>5.4314006914528575e-16</v>
-      </c>
-      <c r="J15" s="0">
-        <v>0</v>
-      </c>
-      <c r="K15" s="0">
-        <v>0</v>
-      </c>
-      <c r="L15" s="0">
-        <v>-4.2375290271750751e-15</v>
-      </c>
-      <c r="M15" s="0">
-        <v>4.2375290271750751e-15</v>
       </c>
       <c r="N15" s="0">
         <v>0.022249703086157591</v>
@@ -1676,16 +2372,16 @@
         <v>2.6401374310301131e-15</v>
       </c>
       <c r="Z15" s="0">
-        <v>-0.040848398187265295</v>
+        <v>-0.60565245633500053</v>
       </c>
       <c r="AA15" s="0">
-        <v>-1.0000000000000042</v>
+        <v>-0.04084839818726619</v>
       </c>
       <c r="AB15" s="0">
-        <v>-0.60565245633500153</v>
+        <v>-1</v>
       </c>
       <c r="AC15" s="0">
-        <v>1.0000000000000042</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1693,37 +2389,37 @@
         <v>1.4000000000000001</v>
       </c>
       <c r="B16" s="0">
+        <v>-0.6510675621147225</v>
+      </c>
+      <c r="C16" s="0">
+        <v>-0.65106756211469963</v>
+      </c>
+      <c r="D16" s="0">
+        <v>-0.6510675621146893</v>
+      </c>
+      <c r="E16" s="0">
+        <v>0.0045667075924346861</v>
+      </c>
+      <c r="F16" s="0">
+        <v>0.0045667075924346861</v>
+      </c>
+      <c r="G16" s="0">
         <v>0.0045667075924350643</v>
       </c>
-      <c r="C16" s="0">
-        <v>0.0045667075924346861</v>
-      </c>
-      <c r="D16" s="0">
-        <v>0.0045667075924346861</v>
-      </c>
-      <c r="E16" s="0">
-        <v>-0.6510675621146893</v>
-      </c>
-      <c r="F16" s="0">
-        <v>-0.65106756211469963</v>
-      </c>
-      <c r="G16" s="0">
-        <v>-0.6510675621147225</v>
-      </c>
       <c r="H16" s="0">
         <v>0</v>
       </c>
       <c r="I16" s="0">
+        <v>0</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0">
         <v>-9.4538059925565045e-16</v>
       </c>
-      <c r="J16" s="0">
+      <c r="L16" s="0">
         <v>9.4538059925565045e-16</v>
-      </c>
-      <c r="K16" s="0">
-        <v>0</v>
-      </c>
-      <c r="L16" s="0">
-        <v>0</v>
       </c>
       <c r="M16" s="0">
         <v>0</v>
@@ -1765,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="Z16" s="0">
-        <v>0.0045667075924350643</v>
+        <v>-0.65106756211470151</v>
       </c>
       <c r="AA16" s="0">
-        <v>-1.0000000000000009</v>
+        <v>0.0045667075924346861</v>
       </c>
       <c r="AB16" s="0">
-        <v>-0.65106756211470185</v>
+        <v>-0.999999999999999</v>
       </c>
       <c r="AC16" s="0">
-        <v>1.0000000000000009</v>
+        <v>0.999999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1782,40 +2478,40 @@
         <v>1.5</v>
       </c>
       <c r="B17" s="0">
+        <v>-0.6979617293578626</v>
+      </c>
+      <c r="C17" s="0">
+        <v>-0.6979617293578626</v>
+      </c>
+      <c r="D17" s="0">
+        <v>-0.69796172935783274</v>
+      </c>
+      <c r="E17" s="0">
         <v>0.051460874835589421</v>
       </c>
-      <c r="C17" s="0">
+      <c r="F17" s="0">
         <v>0.05146087483558949</v>
       </c>
-      <c r="D17" s="0">
+      <c r="G17" s="0">
         <v>0.05146087483558949</v>
       </c>
-      <c r="E17" s="0">
-        <v>-0.69796172935783274</v>
-      </c>
-      <c r="F17" s="0">
-        <v>-0.6979617293578626</v>
-      </c>
-      <c r="G17" s="0">
-        <v>-0.6979617293578626</v>
-      </c>
       <c r="H17" s="0">
-        <v>0</v>
+        <v>-2.4082289432565972e-15</v>
       </c>
       <c r="I17" s="0">
+        <v>2.4082289432565972e-15</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0">
+        <v>0</v>
+      </c>
+      <c r="L17" s="0">
         <v>-1.5246301908611683e-15</v>
       </c>
-      <c r="J17" s="0">
+      <c r="M17" s="0">
         <v>1.5246301908611683e-15</v>
-      </c>
-      <c r="K17" s="0">
-        <v>0</v>
-      </c>
-      <c r="L17" s="0">
-        <v>-2.4082289432565972e-15</v>
-      </c>
-      <c r="M17" s="0">
-        <v>2.4082289432565972e-15</v>
       </c>
       <c r="N17" s="0">
         <v>0.012457618906579511</v>
@@ -1854,16 +2550,16 @@
         <v>1.3236354357183442e-14</v>
       </c>
       <c r="Z17" s="0">
+        <v>-0.69796172935785616</v>
+      </c>
+      <c r="AA17" s="0">
         <v>0.051460874835589421</v>
       </c>
-      <c r="AA17" s="0">
-        <v>-1.0000000000000024</v>
-      </c>
       <c r="AB17" s="0">
-        <v>-0.69796172935785616</v>
+        <v>-1</v>
       </c>
       <c r="AC17" s="0">
-        <v>1.0000000000000024</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1871,37 +2567,37 @@
         <v>1.6000000000000001</v>
       </c>
       <c r="B18" s="0">
+        <v>-0.74614762025359982</v>
+      </c>
+      <c r="C18" s="0">
+        <v>-0.74614762025356651</v>
+      </c>
+      <c r="D18" s="0">
+        <v>-0.74614762025356651</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0.09964676573131806</v>
+      </c>
+      <c r="F18" s="0">
+        <v>0.09964676573131892</v>
+      </c>
+      <c r="G18" s="0">
         <v>0.09964676573131985</v>
       </c>
-      <c r="C18" s="0">
-        <v>0.09964676573131892</v>
-      </c>
-      <c r="D18" s="0">
-        <v>0.09964676573131806</v>
-      </c>
-      <c r="E18" s="0">
-        <v>-0.74614762025356651</v>
-      </c>
-      <c r="F18" s="0">
-        <v>-0.74614762025356651</v>
-      </c>
-      <c r="G18" s="0">
-        <v>-0.74614762025359982</v>
-      </c>
       <c r="H18" s="0">
         <v>0</v>
       </c>
       <c r="I18" s="0">
-        <v>0</v>
+        <v>-6.7783749486941666e-15</v>
       </c>
       <c r="J18" s="0">
-        <v>0</v>
+        <v>6.7783749486941666e-15</v>
       </c>
       <c r="K18" s="0">
-        <v>-6.7783749486941666e-15</v>
+        <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>6.7783749486941666e-15</v>
+        <v>0</v>
       </c>
       <c r="M18" s="0">
         <v>0</v>
@@ -1943,16 +2639,16 @@
         <v>0</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.09964676573131985</v>
+        <v>-0.74614762025358483</v>
       </c>
       <c r="AA18" s="0">
-        <v>-1.0000000000000069</v>
+        <v>0.09964676573131806</v>
       </c>
       <c r="AB18" s="0">
-        <v>-0.74614762025358661</v>
+        <v>-1</v>
       </c>
       <c r="AC18" s="0">
-        <v>1.0000000000000069</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1960,22 +2656,22 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="B19" s="0">
+        <v>-0.79542765239026136</v>
+      </c>
+      <c r="C19" s="0">
+        <v>-0.79542765239016</v>
+      </c>
+      <c r="D19" s="0">
+        <v>-0.79542765239012991</v>
+      </c>
+      <c r="E19" s="0">
+        <v>0.14892679786792501</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0.14892679786792798</v>
+      </c>
+      <c r="G19" s="0">
         <v>0.14892679786792851</v>
-      </c>
-      <c r="C19" s="0">
-        <v>0.14892679786792798</v>
-      </c>
-      <c r="D19" s="0">
-        <v>0.14892679786792501</v>
-      </c>
-      <c r="E19" s="0">
-        <v>-0.79542765239012991</v>
-      </c>
-      <c r="F19" s="0">
-        <v>-0.79542765239016</v>
-      </c>
-      <c r="G19" s="0">
-        <v>-0.79542765239026136</v>
       </c>
       <c r="H19" s="0">
         <v>0</v>
@@ -2032,13 +2728,13 @@
         <v>0</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.14892679786792851</v>
+        <v>-0.79542765239019175</v>
       </c>
       <c r="AA19" s="0">
+        <v>0.14892679786792501</v>
+      </c>
+      <c r="AB19" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB19" s="0">
-        <v>-0.79542765239019531</v>
       </c>
       <c r="AC19" s="0">
         <v>1</v>
@@ -2049,22 +2745,22 @@
         <v>1.8</v>
       </c>
       <c r="B20" s="0">
+        <v>-0.84558677547434258</v>
+      </c>
+      <c r="C20" s="0">
+        <v>-0.84558677547423222</v>
+      </c>
+      <c r="D20" s="0">
+        <v>-0.84558677547407479</v>
+      </c>
+      <c r="E20" s="0">
+        <v>0.19908592095197769</v>
+      </c>
+      <c r="F20" s="0">
+        <v>0.19908592095197933</v>
+      </c>
+      <c r="G20" s="0">
         <v>0.19908592095197969</v>
-      </c>
-      <c r="C20" s="0">
-        <v>0.19908592095197933</v>
-      </c>
-      <c r="D20" s="0">
-        <v>0.19908592095197769</v>
-      </c>
-      <c r="E20" s="0">
-        <v>-0.84558677547407479</v>
-      </c>
-      <c r="F20" s="0">
-        <v>-0.84558677547423222</v>
-      </c>
-      <c r="G20" s="0">
-        <v>-0.84558677547434258</v>
       </c>
       <c r="H20" s="0">
         <v>0</v>
@@ -2121,13 +2817,13 @@
         <v>0</v>
       </c>
       <c r="Z20" s="0">
-        <v>0.19908592095197969</v>
+        <v>-0.84558677547424455</v>
       </c>
       <c r="AA20" s="0">
+        <v>0.19908592095197769</v>
+      </c>
+      <c r="AB20" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB20" s="0">
-        <v>-0.84558677547424654</v>
       </c>
       <c r="AC20" s="0">
         <v>1</v>
@@ -2138,37 +2834,37 @@
         <v>1.9000000000000001</v>
       </c>
       <c r="B21" s="0">
+        <v>-0.89639018937462622</v>
+      </c>
+      <c r="C21" s="0">
+        <v>-0.8963901893744759</v>
+      </c>
+      <c r="D21" s="0">
+        <v>-0.8963901893744759</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0.24988933485209344</v>
+      </c>
+      <c r="F21" s="0">
+        <v>0.24988933485209378</v>
+      </c>
+      <c r="G21" s="0">
         <v>0.24988933485209464</v>
       </c>
-      <c r="C21" s="0">
-        <v>0.24988933485209378</v>
-      </c>
-      <c r="D21" s="0">
-        <v>0.24988933485209344</v>
-      </c>
-      <c r="E21" s="0">
-        <v>-0.8963901893744759</v>
-      </c>
-      <c r="F21" s="0">
-        <v>-0.8963901893744759</v>
-      </c>
-      <c r="G21" s="0">
-        <v>-0.89639018937462622</v>
-      </c>
       <c r="H21" s="0">
         <v>0</v>
       </c>
       <c r="I21" s="0">
-        <v>0</v>
+        <v>-8.6804248874063158e-14</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>8.6804248874063158e-14</v>
       </c>
       <c r="K21" s="0">
-        <v>-8.6804248874063158e-14</v>
+        <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>8.6804248874063158e-14</v>
+        <v>0</v>
       </c>
       <c r="M21" s="0">
         <v>0</v>
@@ -2210,16 +2906,16 @@
         <v>0</v>
       </c>
       <c r="Z21" s="0">
-        <v>0.24988933485209464</v>
+        <v>-0.89639018937436021</v>
       </c>
       <c r="AA21" s="0">
-        <v>-1.0000000000000868</v>
+        <v>0.24988933485209344</v>
       </c>
       <c r="AB21" s="0">
-        <v>-0.89639018937436143</v>
+        <v>-1</v>
       </c>
       <c r="AC21" s="0">
-        <v>1.0000000000000868</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2227,37 +2923,37 @@
         <v>2</v>
       </c>
       <c r="B22" s="0">
+        <v>-0.94758778160259871</v>
+      </c>
+      <c r="C22" s="0">
+        <v>-0.94758778160193147</v>
+      </c>
+      <c r="D22" s="0">
+        <v>-0.94758778160171775</v>
+      </c>
+      <c r="E22" s="0">
         <v>0.30108692707966128</v>
       </c>
-      <c r="C22" s="0">
+      <c r="F22" s="0">
         <v>0.30108692707966128</v>
       </c>
-      <c r="D22" s="0">
+      <c r="G22" s="0">
         <v>0.30108692707966256</v>
       </c>
-      <c r="E22" s="0">
-        <v>-0.94758778160171775</v>
-      </c>
-      <c r="F22" s="0">
-        <v>-0.94758778160193147</v>
-      </c>
-      <c r="G22" s="0">
-        <v>-0.94758778160259871</v>
-      </c>
       <c r="H22" s="0">
+        <v>0</v>
+      </c>
+      <c r="I22" s="0">
+        <v>0</v>
+      </c>
+      <c r="J22" s="0">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0">
         <v>-4.7319690716904686e-16</v>
       </c>
-      <c r="I22" s="0">
+      <c r="L22" s="0">
         <v>4.7319690716904686e-16</v>
-      </c>
-      <c r="J22" s="0">
-        <v>0</v>
-      </c>
-      <c r="K22" s="0">
-        <v>0</v>
-      </c>
-      <c r="L22" s="0">
-        <v>0</v>
       </c>
       <c r="M22" s="0">
         <v>0</v>
@@ -2299,16 +2995,16 @@
         <v>0</v>
       </c>
       <c r="Z22" s="0">
+        <v>-0.94758778160192803</v>
+      </c>
+      <c r="AA22" s="0">
         <v>0.30108692707966128</v>
       </c>
-      <c r="AA22" s="0">
-        <v>-1.0000000000000004</v>
-      </c>
       <c r="AB22" s="0">
-        <v>-0.94758778160192803</v>
+        <v>-0.99999999999999956</v>
       </c>
       <c r="AC22" s="0">
-        <v>1.0000000000000004</v>
+        <v>0.99999999999999956</v>
       </c>
     </row>
     <row r="23">
@@ -2316,28 +3012,28 @@
         <v>2.1000000000000001</v>
       </c>
       <c r="B23" s="0">
+        <v>-0.9989234703968165</v>
+      </c>
+      <c r="C23" s="0">
+        <v>-0.9989234703968165</v>
+      </c>
+      <c r="D23" s="0">
+        <v>-0.99892347039621732</v>
+      </c>
+      <c r="E23" s="0">
         <v>0.35242261587430834</v>
       </c>
-      <c r="C23" s="0">
+      <c r="F23" s="0">
         <v>0.3524226158743109</v>
       </c>
-      <c r="D23" s="0">
+      <c r="G23" s="0">
         <v>0.35242261587431234</v>
       </c>
-      <c r="E23" s="0">
-        <v>-0.99892347039621732</v>
-      </c>
-      <c r="F23" s="0">
-        <v>-0.9989234703968165</v>
-      </c>
-      <c r="G23" s="0">
-        <v>-0.9989234703968165</v>
-      </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>-2.3933695129511061e-13</v>
       </c>
       <c r="I23" s="0">
-        <v>0</v>
+        <v>2.3933695129511061e-13</v>
       </c>
       <c r="J23" s="0">
         <v>0</v>
@@ -2346,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="0">
-        <v>-2.3933695129511061e-13</v>
+        <v>0</v>
       </c>
       <c r="M23" s="0">
-        <v>2.3933695129511061e-13</v>
+        <v>0</v>
       </c>
       <c r="N23" s="0">
         <v>0.001880116995939068</v>
@@ -2388,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="Z23" s="0">
+        <v>-0.99892347039657514</v>
+      </c>
+      <c r="AA23" s="0">
         <v>0.35242261587430834</v>
       </c>
-      <c r="AA23" s="0">
-        <v>-1.0000000000002394</v>
-      </c>
       <c r="AB23" s="0">
-        <v>-0.99892347039657514</v>
+        <v>-1</v>
       </c>
       <c r="AC23" s="0">
-        <v>1.0000000000002394</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2405,37 +3101,37 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B24" s="0">
+        <v>-1.0501462430153694</v>
+      </c>
+      <c r="C24" s="0">
+        <v>-1.0501462430145814</v>
+      </c>
+      <c r="D24" s="0">
+        <v>-1.0501462430145814</v>
+      </c>
+      <c r="E24" s="0">
         <v>0.40364538849332371</v>
       </c>
-      <c r="C24" s="0">
+      <c r="F24" s="0">
         <v>0.40364538849332565</v>
       </c>
-      <c r="D24" s="0">
+      <c r="G24" s="0">
         <v>0.40364538849332809</v>
       </c>
-      <c r="E24" s="0">
-        <v>-1.0501462430145814</v>
-      </c>
-      <c r="F24" s="0">
-        <v>-1.0501462430145814</v>
-      </c>
-      <c r="G24" s="0">
-        <v>-1.0501462430153694</v>
-      </c>
       <c r="H24" s="0">
         <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>0</v>
+        <v>-1.6888026333797382e-12</v>
       </c>
       <c r="J24" s="0">
-        <v>0</v>
+        <v>1.6888026333797382e-12</v>
       </c>
       <c r="K24" s="0">
-        <v>-1.6888026333797382e-12</v>
+        <v>0</v>
       </c>
       <c r="L24" s="0">
-        <v>1.6888026333797382e-12</v>
+        <v>0</v>
       </c>
       <c r="M24" s="0">
         <v>0</v>
@@ -2477,16 +3173,16 @@
         <v>0</v>
       </c>
       <c r="Z24" s="0">
+        <v>-1.0501462430155906</v>
+      </c>
+      <c r="AA24" s="0">
         <v>0.40364538849332371</v>
       </c>
-      <c r="AA24" s="0">
-        <v>-1.0000000000016889</v>
-      </c>
       <c r="AB24" s="0">
-        <v>-1.0501462430155906</v>
+        <v>-1</v>
       </c>
       <c r="AC24" s="0">
-        <v>1.0000000000016889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2494,37 +3190,37 @@
         <v>2.3000000000000003</v>
       </c>
       <c r="B25" s="0">
+        <v>-1.1010200081549082</v>
+      </c>
+      <c r="C25" s="0">
+        <v>-1.1010200081510828</v>
+      </c>
+      <c r="D25" s="0">
+        <v>-1.1010200081510828</v>
+      </c>
+      <c r="E25" s="0">
         <v>0.4545191536290073</v>
       </c>
-      <c r="C25" s="0">
+      <c r="F25" s="0">
         <v>0.45451915362901307</v>
       </c>
-      <c r="D25" s="0">
+      <c r="G25" s="0">
         <v>0.45451915362901457</v>
       </c>
-      <c r="E25" s="0">
-        <v>-1.1010200081510828</v>
-      </c>
-      <c r="F25" s="0">
-        <v>-1.1010200081510828</v>
-      </c>
-      <c r="G25" s="0">
-        <v>-1.1010200081549082</v>
-      </c>
       <c r="H25" s="0">
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>0</v>
+        <v>-1.1649987651869048e-12</v>
       </c>
       <c r="J25" s="0">
-        <v>0</v>
+        <v>1.1649987651869048e-12</v>
       </c>
       <c r="K25" s="0">
-        <v>-1.1649987651869048e-12</v>
+        <v>0</v>
       </c>
       <c r="L25" s="0">
-        <v>1.1649987651869048e-12</v>
+        <v>0</v>
       </c>
       <c r="M25" s="0">
         <v>0</v>
@@ -2566,16 +3262,16 @@
         <v>0</v>
       </c>
       <c r="Z25" s="0">
+        <v>-1.101020008151274</v>
+      </c>
+      <c r="AA25" s="0">
         <v>0.4545191536290073</v>
       </c>
-      <c r="AA25" s="0">
-        <v>-1.0000000000011651</v>
-      </c>
       <c r="AB25" s="0">
-        <v>-1.101020008151274</v>
+        <v>-1</v>
       </c>
       <c r="AC25" s="0">
-        <v>1.0000000000011651</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2583,22 +3279,22 @@
         <v>2.4000000000000004</v>
       </c>
       <c r="B26" s="0">
+        <v>-1.1513305481165277</v>
+      </c>
+      <c r="C26" s="0">
+        <v>-1.1513305481135976</v>
+      </c>
+      <c r="D26" s="0">
+        <v>-1.1513305481125411</v>
+      </c>
+      <c r="E26" s="0">
         <v>0.50482969359076713</v>
       </c>
-      <c r="C26" s="0">
+      <c r="F26" s="0">
         <v>0.50482969359077146</v>
       </c>
-      <c r="D26" s="0">
+      <c r="G26" s="0">
         <v>0.5048296935907719</v>
-      </c>
-      <c r="E26" s="0">
-        <v>-1.1513305481125411</v>
-      </c>
-      <c r="F26" s="0">
-        <v>-1.1513305481135976</v>
-      </c>
-      <c r="G26" s="0">
-        <v>-1.1513305481165277</v>
       </c>
       <c r="H26" s="0">
         <v>0</v>
@@ -2655,13 +3351,13 @@
         <v>0</v>
       </c>
       <c r="Z26" s="0">
+        <v>-1.1513305481130338</v>
+      </c>
+      <c r="AA26" s="0">
         <v>0.50482969359076713</v>
       </c>
-      <c r="AA26" s="0">
+      <c r="AB26" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB26" s="0">
-        <v>-1.1513305481130338</v>
       </c>
       <c r="AC26" s="0">
         <v>1</v>
@@ -2672,37 +3368,37 @@
         <v>2.5</v>
       </c>
       <c r="B27" s="0">
+        <v>-1.2008890769586276</v>
+      </c>
+      <c r="C27" s="0">
+        <v>-1.200889076953237</v>
+      </c>
+      <c r="D27" s="0">
+        <v>-1.200889076953237</v>
+      </c>
+      <c r="E27" s="0">
         <v>0.55438822243372765</v>
       </c>
-      <c r="C27" s="0">
+      <c r="F27" s="0">
         <v>0.55438822243373442</v>
       </c>
-      <c r="D27" s="0">
+      <c r="G27" s="0">
         <v>0.55438822243373576</v>
       </c>
-      <c r="E27" s="0">
-        <v>-1.200889076953237</v>
-      </c>
-      <c r="F27" s="0">
-        <v>-1.200889076953237</v>
-      </c>
-      <c r="G27" s="0">
-        <v>-1.2008890769586276</v>
-      </c>
       <c r="H27" s="0">
         <v>0</v>
       </c>
       <c r="I27" s="0">
-        <v>0</v>
+        <v>-2.1096257561757415e-12</v>
       </c>
       <c r="J27" s="0">
-        <v>0</v>
+        <v>2.1096257561757415e-12</v>
       </c>
       <c r="K27" s="0">
-        <v>-2.1096257561757415e-12</v>
+        <v>0</v>
       </c>
       <c r="L27" s="0">
-        <v>2.1096257561757415e-12</v>
+        <v>0</v>
       </c>
       <c r="M27" s="0">
         <v>0</v>
@@ -2744,16 +3440,16 @@
         <v>0</v>
       </c>
       <c r="Z27" s="0">
+        <v>-1.2008890769559946</v>
+      </c>
+      <c r="AA27" s="0">
         <v>0.55438822243372765</v>
       </c>
-      <c r="AA27" s="0">
-        <v>-1.0000000000021096</v>
-      </c>
       <c r="AB27" s="0">
-        <v>-1.2008890769559946</v>
+        <v>-1</v>
       </c>
       <c r="AC27" s="0">
-        <v>1.0000000000021096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2761,22 +3457,22 @@
         <v>2.6000000000000001</v>
       </c>
       <c r="B28" s="0">
+        <v>-1.2495327633619868</v>
+      </c>
+      <c r="C28" s="0">
+        <v>-1.2495327633478925</v>
+      </c>
+      <c r="D28" s="0">
+        <v>-1.2495327633386208</v>
+      </c>
+      <c r="E28" s="0">
         <v>0.60303190882759206</v>
       </c>
-      <c r="C28" s="0">
+      <c r="F28" s="0">
         <v>0.60303190882759394</v>
       </c>
-      <c r="D28" s="0">
+      <c r="G28" s="0">
         <v>0.60303190882759861</v>
-      </c>
-      <c r="E28" s="0">
-        <v>-1.2495327633386208</v>
-      </c>
-      <c r="F28" s="0">
-        <v>-1.2495327633478925</v>
-      </c>
-      <c r="G28" s="0">
-        <v>-1.2495327633619868</v>
       </c>
       <c r="H28" s="0">
         <v>0</v>
@@ -2833,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Z28" s="0">
+        <v>-1.2495327633498587</v>
+      </c>
+      <c r="AA28" s="0">
         <v>0.60303190882759206</v>
       </c>
-      <c r="AA28" s="0">
+      <c r="AB28" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB28" s="0">
-        <v>-1.2495327633498587</v>
       </c>
       <c r="AC28" s="0">
         <v>1</v>
@@ -2850,37 +3546,37 @@
         <v>2.7000000000000002</v>
       </c>
       <c r="B29" s="0">
+        <v>-1.2971229790773871</v>
+      </c>
+      <c r="C29" s="0">
+        <v>-1.2971229790266068</v>
+      </c>
+      <c r="D29" s="0">
+        <v>-1.2971229790137655</v>
+      </c>
+      <c r="E29" s="0">
         <v>0.65062212449617207</v>
       </c>
-      <c r="C29" s="0">
+      <c r="F29" s="0">
         <v>0.65062212449617207</v>
       </c>
-      <c r="D29" s="0">
+      <c r="G29" s="0">
         <v>0.65062212449617518</v>
       </c>
-      <c r="E29" s="0">
-        <v>-1.2971229790137655</v>
-      </c>
-      <c r="F29" s="0">
-        <v>-1.2971229790266068</v>
-      </c>
-      <c r="G29" s="0">
-        <v>-1.2971229790773871</v>
-      </c>
       <c r="H29" s="0">
+        <v>0</v>
+      </c>
+      <c r="I29" s="0">
+        <v>0</v>
+      </c>
+      <c r="J29" s="0">
+        <v>0</v>
+      </c>
+      <c r="K29" s="0">
         <v>-1.0669505774367521e-15</v>
       </c>
-      <c r="I29" s="0">
+      <c r="L29" s="0">
         <v>1.0669505774367521e-15</v>
-      </c>
-      <c r="J29" s="0">
-        <v>0</v>
-      </c>
-      <c r="K29" s="0">
-        <v>0</v>
-      </c>
-      <c r="L29" s="0">
-        <v>0</v>
       </c>
       <c r="M29" s="0">
         <v>0</v>
@@ -2922,16 +3618,16 @@
         <v>0</v>
       </c>
       <c r="Z29" s="0">
+        <v>-1.2971229790184389</v>
+      </c>
+      <c r="AA29" s="0">
         <v>0.65062212449617207</v>
       </c>
-      <c r="AA29" s="0">
-        <v>-1.0000000000000011</v>
-      </c>
       <c r="AB29" s="0">
-        <v>-1.2971229790184389</v>
+        <v>-0.99999999999999889</v>
       </c>
       <c r="AC29" s="0">
-        <v>1.0000000000000011</v>
+        <v>0.99999999999999889</v>
       </c>
     </row>
     <row r="30">
@@ -2939,40 +3635,40 @@
         <v>2.8000000000000003</v>
       </c>
       <c r="B30" s="0">
+        <v>-1.3435420908552882</v>
+      </c>
+      <c r="C30" s="0">
+        <v>-1.3435420908390394</v>
+      </c>
+      <c r="D30" s="0">
+        <v>-1.3435420908390394</v>
+      </c>
+      <c r="E30" s="0">
         <v>0.69704123631988169</v>
       </c>
-      <c r="C30" s="0">
+      <c r="F30" s="0">
         <v>0.69704123631989789</v>
       </c>
-      <c r="D30" s="0">
+      <c r="G30" s="0">
         <v>0.69704123631989789</v>
       </c>
-      <c r="E30" s="0">
-        <v>-1.3435420908390394</v>
-      </c>
-      <c r="F30" s="0">
-        <v>-1.3435420908390394</v>
-      </c>
-      <c r="G30" s="0">
-        <v>-1.3435420908552882</v>
-      </c>
       <c r="H30" s="0">
         <v>0</v>
       </c>
       <c r="I30" s="0">
+        <v>-2.6115400231465049e-11</v>
+      </c>
+      <c r="J30" s="0">
+        <v>2.6115400231465049e-11</v>
+      </c>
+      <c r="K30" s="0">
+        <v>0</v>
+      </c>
+      <c r="L30" s="0">
         <v>-8.5017518550670204e-16</v>
       </c>
-      <c r="J30" s="0">
+      <c r="M30" s="0">
         <v>8.5017518550670204e-16</v>
-      </c>
-      <c r="K30" s="0">
-        <v>-2.6115400231465049e-11</v>
-      </c>
-      <c r="L30" s="0">
-        <v>2.6115400231465049e-11</v>
-      </c>
-      <c r="M30" s="0">
-        <v>0</v>
       </c>
       <c r="N30" s="0">
         <v>0.00021567801691801418</v>
@@ -3011,16 +3707,16 @@
         <v>4.2632564145606016e-13</v>
       </c>
       <c r="Z30" s="0">
+        <v>-1.3435420908421485</v>
+      </c>
+      <c r="AA30" s="0">
         <v>0.69704123631988169</v>
       </c>
-      <c r="AA30" s="0">
-        <v>-1.0000000000261153</v>
-      </c>
       <c r="AB30" s="0">
-        <v>-1.3435420908421485</v>
+        <v>-1</v>
       </c>
       <c r="AC30" s="0">
-        <v>1.0000000000261153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3028,37 +3724,37 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="B31" s="0">
+        <v>-1.388689480474772</v>
+      </c>
+      <c r="C31" s="0">
+        <v>-1.3886894804226888</v>
+      </c>
+      <c r="D31" s="0">
+        <v>-1.3886894803059469</v>
+      </c>
+      <c r="E31" s="0">
         <v>0.742188625865153</v>
       </c>
-      <c r="C31" s="0">
+      <c r="F31" s="0">
         <v>0.742188625865153</v>
       </c>
-      <c r="D31" s="0">
+      <c r="G31" s="0">
         <v>0.7421886258651561</v>
       </c>
-      <c r="E31" s="0">
-        <v>-1.3886894803059469</v>
-      </c>
-      <c r="F31" s="0">
-        <v>-1.3886894804226888</v>
-      </c>
-      <c r="G31" s="0">
-        <v>-1.388689480474772</v>
-      </c>
       <c r="H31" s="0">
+        <v>0</v>
+      </c>
+      <c r="I31" s="0">
+        <v>0</v>
+      </c>
+      <c r="J31" s="0">
+        <v>0</v>
+      </c>
+      <c r="K31" s="0">
         <v>-1.4214638618534403e-15</v>
       </c>
-      <c r="I31" s="0">
+      <c r="L31" s="0">
         <v>1.4214638618534403e-15</v>
-      </c>
-      <c r="J31" s="0">
-        <v>0</v>
-      </c>
-      <c r="K31" s="0">
-        <v>0</v>
-      </c>
-      <c r="L31" s="0">
-        <v>0</v>
       </c>
       <c r="M31" s="0">
         <v>0</v>
@@ -3100,16 +3796,16 @@
         <v>0</v>
       </c>
       <c r="Z31" s="0">
+        <v>-1.3886894803874199</v>
+      </c>
+      <c r="AA31" s="0">
         <v>0.742188625865153</v>
       </c>
-      <c r="AA31" s="0">
-        <v>-1.0000000000000013</v>
-      </c>
       <c r="AB31" s="0">
-        <v>-1.3886894803874199</v>
+        <v>-0.99999999999999856</v>
       </c>
       <c r="AC31" s="0">
-        <v>1.0000000000000013</v>
+        <v>0.99999999999999856</v>
       </c>
     </row>
     <row r="32">
@@ -3117,37 +3813,37 @@
         <v>3</v>
       </c>
       <c r="B32" s="0">
+        <v>-1.4324772723607269</v>
+      </c>
+      <c r="C32" s="0">
+        <v>-1.4324772721846426</v>
+      </c>
+      <c r="D32" s="0">
+        <v>-1.4324772721403547</v>
+      </c>
+      <c r="E32" s="0">
         <v>0.78597641764576809</v>
       </c>
-      <c r="C32" s="0">
+      <c r="F32" s="0">
         <v>0.78597641764576809</v>
       </c>
-      <c r="D32" s="0">
+      <c r="G32" s="0">
         <v>0.78597641764577919</v>
       </c>
-      <c r="E32" s="0">
-        <v>-1.4324772721403547</v>
-      </c>
-      <c r="F32" s="0">
-        <v>-1.4324772721846426</v>
-      </c>
-      <c r="G32" s="0">
-        <v>-1.4324772723607269</v>
-      </c>
       <c r="H32" s="0">
+        <v>0</v>
+      </c>
+      <c r="I32" s="0">
+        <v>0</v>
+      </c>
+      <c r="J32" s="0">
+        <v>0</v>
+      </c>
+      <c r="K32" s="0">
         <v>-7.4270218336664744e-16</v>
       </c>
-      <c r="I32" s="0">
+      <c r="L32" s="0">
         <v>7.4270218336664744e-16</v>
-      </c>
-      <c r="J32" s="0">
-        <v>0</v>
-      </c>
-      <c r="K32" s="0">
-        <v>0</v>
-      </c>
-      <c r="L32" s="0">
-        <v>0</v>
       </c>
       <c r="M32" s="0">
         <v>0</v>
@@ -3189,16 +3885,16 @@
         <v>0</v>
       </c>
       <c r="Z32" s="0">
+        <v>-1.4324772721680348</v>
+      </c>
+      <c r="AA32" s="0">
         <v>0.78597641764576809</v>
       </c>
-      <c r="AA32" s="0">
-        <v>-1.0000000000000007</v>
-      </c>
       <c r="AB32" s="0">
-        <v>-1.4324772721680348</v>
+        <v>-0.99999999999999922</v>
       </c>
       <c r="AC32" s="0">
-        <v>1.0000000000000007</v>
+        <v>0.99999999999999922</v>
       </c>
     </row>
     <row r="33">
@@ -3206,22 +3902,22 @@
         <v>3.1000000000000001</v>
       </c>
       <c r="B33" s="0">
+        <v>-1.4748260542331457</v>
+      </c>
+      <c r="C33" s="0">
+        <v>-1.4748260541244289</v>
+      </c>
+      <c r="D33" s="0">
+        <v>-1.4748260538537852</v>
+      </c>
+      <c r="E33" s="0">
         <v>0.82832519966899321</v>
       </c>
-      <c r="C33" s="0">
+      <c r="F33" s="0">
         <v>0.82832519966901852</v>
       </c>
-      <c r="D33" s="0">
+      <c r="G33" s="0">
         <v>0.82832519966902118</v>
-      </c>
-      <c r="E33" s="0">
-        <v>-1.4748260538537852</v>
-      </c>
-      <c r="F33" s="0">
-        <v>-1.4748260541244289</v>
-      </c>
-      <c r="G33" s="0">
-        <v>-1.4748260542331457</v>
       </c>
       <c r="H33" s="0">
         <v>0</v>
@@ -3278,13 +3974,13 @@
         <v>0</v>
       </c>
       <c r="Z33" s="0">
+        <v>-1.4748260541912601</v>
+      </c>
+      <c r="AA33" s="0">
         <v>0.82832519966899321</v>
       </c>
-      <c r="AA33" s="0">
+      <c r="AB33" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB33" s="0">
-        <v>-1.4748260541912601</v>
       </c>
       <c r="AC33" s="0">
         <v>1</v>
@@ -3295,40 +3991,40 @@
         <v>3.2000000000000002</v>
       </c>
       <c r="B34" s="0">
+        <v>-1.5156607118791605</v>
+      </c>
+      <c r="C34" s="0">
+        <v>-1.5156607118791605</v>
+      </c>
+      <c r="D34" s="0">
+        <v>-1.5156607115483614</v>
+      </c>
+      <c r="E34" s="0">
         <v>0.86915985723394773</v>
       </c>
-      <c r="C34" s="0">
+      <c r="F34" s="0">
         <v>0.86915985723394773</v>
       </c>
-      <c r="D34" s="0">
+      <c r="G34" s="0">
         <v>0.86915985723395084</v>
       </c>
-      <c r="E34" s="0">
-        <v>-1.5156607115483614</v>
-      </c>
-      <c r="F34" s="0">
-        <v>-1.5156607118791605</v>
-      </c>
-      <c r="G34" s="0">
-        <v>-1.5156607118791605</v>
-      </c>
       <c r="H34" s="0">
+        <v>-6.8582396882345221e-11</v>
+      </c>
+      <c r="I34" s="0">
+        <v>6.8582396882345221e-11</v>
+      </c>
+      <c r="J34" s="0">
+        <v>0</v>
+      </c>
+      <c r="K34" s="0">
         <v>-5.0530067415672807e-15</v>
       </c>
-      <c r="I34" s="0">
+      <c r="L34" s="0">
         <v>5.0530067415672807e-15</v>
       </c>
-      <c r="J34" s="0">
-        <v>0</v>
-      </c>
-      <c r="K34" s="0">
-        <v>0</v>
-      </c>
-      <c r="L34" s="0">
-        <v>-6.8582396882345221e-11</v>
-      </c>
       <c r="M34" s="0">
-        <v>6.8582396882345221e-11</v>
+        <v>0</v>
       </c>
       <c r="N34" s="0">
         <v>7.3136930356276406e-05</v>
@@ -3367,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="Z34" s="0">
+        <v>-1.5156607117562144</v>
+      </c>
+      <c r="AA34" s="0">
         <v>0.86915985723394773</v>
       </c>
-      <c r="AA34" s="0">
-        <v>-1.0000000000685825</v>
-      </c>
       <c r="AB34" s="0">
-        <v>-1.5156607117562144</v>
+        <v>-0.99999999999999489</v>
       </c>
       <c r="AC34" s="0">
-        <v>1.0000000000685825</v>
+        <v>0.99999999999999489</v>
       </c>
     </row>
     <row r="35">
@@ -3384,37 +4080,37 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="B35" s="0">
+        <v>-1.5549063731343036</v>
+      </c>
+      <c r="C35" s="0">
+        <v>-1.554906372127886</v>
+      </c>
+      <c r="D35" s="0">
+        <v>-1.5549063717759588</v>
+      </c>
+      <c r="E35" s="0">
         <v>0.90840551754532617</v>
       </c>
-      <c r="C35" s="0">
+      <c r="F35" s="0">
         <v>0.90840551754532617</v>
       </c>
-      <c r="D35" s="0">
+      <c r="G35" s="0">
         <v>0.90840551754535126</v>
       </c>
-      <c r="E35" s="0">
-        <v>-1.5549063717759588</v>
-      </c>
-      <c r="F35" s="0">
-        <v>-1.554906372127886</v>
-      </c>
-      <c r="G35" s="0">
-        <v>-1.5549063731343036</v>
-      </c>
       <c r="H35" s="0">
+        <v>0</v>
+      </c>
+      <c r="I35" s="0">
+        <v>0</v>
+      </c>
+      <c r="J35" s="0">
+        <v>0</v>
+      </c>
+      <c r="K35" s="0">
         <v>-6.5317684639028409e-16</v>
       </c>
-      <c r="I35" s="0">
+      <c r="L35" s="0">
         <v>6.5317684639028409e-16</v>
-      </c>
-      <c r="J35" s="0">
-        <v>0</v>
-      </c>
-      <c r="K35" s="0">
-        <v>0</v>
-      </c>
-      <c r="L35" s="0">
-        <v>0</v>
       </c>
       <c r="M35" s="0">
         <v>0</v>
@@ -3456,16 +4152,16 @@
         <v>0</v>
       </c>
       <c r="Z35" s="0">
+        <v>-1.5549063720675931</v>
+      </c>
+      <c r="AA35" s="0">
         <v>0.90840551754532617</v>
       </c>
-      <c r="AA35" s="0">
-        <v>-1.0000000000000007</v>
-      </c>
       <c r="AB35" s="0">
-        <v>-1.5549063720675931</v>
+        <v>-0.99999999999999933</v>
       </c>
       <c r="AC35" s="0">
-        <v>1.0000000000000007</v>
+        <v>0.99999999999999933</v>
       </c>
     </row>
     <row r="36">
@@ -3473,37 +4169,37 @@
         <v>3.4000000000000004</v>
       </c>
       <c r="B36" s="0">
+        <v>-1.5924843646040305</v>
+      </c>
+      <c r="C36" s="0">
+        <v>-1.5924843637154713</v>
+      </c>
+      <c r="D36" s="0">
+        <v>-1.5924843637154713</v>
+      </c>
+      <c r="E36" s="0">
         <v>0.94598350925260288</v>
       </c>
-      <c r="C36" s="0">
+      <c r="F36" s="0">
         <v>0.94598350925263852</v>
       </c>
-      <c r="D36" s="0">
+      <c r="G36" s="0">
         <v>0.94598350925263908</v>
       </c>
-      <c r="E36" s="0">
-        <v>-1.5924843637154713</v>
-      </c>
-      <c r="F36" s="0">
-        <v>-1.5924843637154713</v>
-      </c>
-      <c r="G36" s="0">
-        <v>-1.5924843646040305</v>
-      </c>
       <c r="H36" s="0">
         <v>0</v>
       </c>
       <c r="I36" s="0">
-        <v>0</v>
+        <v>-1.1999474990478922e-10</v>
       </c>
       <c r="J36" s="0">
-        <v>0</v>
+        <v>1.1999474990478922e-10</v>
       </c>
       <c r="K36" s="0">
-        <v>-1.1999474990478922e-10</v>
+        <v>0</v>
       </c>
       <c r="L36" s="0">
-        <v>1.1999474990478922e-10</v>
+        <v>0</v>
       </c>
       <c r="M36" s="0">
         <v>0</v>
@@ -3545,16 +4241,16 @@
         <v>0</v>
       </c>
       <c r="Z36" s="0">
+        <v>-1.5924843637748696</v>
+      </c>
+      <c r="AA36" s="0">
         <v>0.94598350925260288</v>
       </c>
-      <c r="AA36" s="0">
-        <v>-1.0000000001199947</v>
-      </c>
       <c r="AB36" s="0">
-        <v>-1.5924843637748696</v>
+        <v>-1</v>
       </c>
       <c r="AC36" s="0">
-        <v>1.0000000001199947</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3562,40 +4258,40 @@
         <v>3.5</v>
       </c>
       <c r="B37" s="0">
+        <v>-1.6283080179336096</v>
+      </c>
+      <c r="C37" s="0">
+        <v>-1.6283080179336096</v>
+      </c>
+      <c r="D37" s="0">
+        <v>-1.628308016838008</v>
+      </c>
+      <c r="E37" s="0">
         <v>0.98180716281774816</v>
       </c>
-      <c r="C37" s="0">
+      <c r="F37" s="0">
         <v>0.98180716281778335</v>
       </c>
-      <c r="D37" s="0">
+      <c r="G37" s="0">
         <v>0.98180716281778335</v>
       </c>
-      <c r="E37" s="0">
-        <v>-1.628308016838008</v>
-      </c>
-      <c r="F37" s="0">
-        <v>-1.6283080179336096</v>
-      </c>
-      <c r="G37" s="0">
-        <v>-1.6283080179336096</v>
-      </c>
       <c r="H37" s="0">
-        <v>0</v>
+        <v>-4.5181776933206777e-10</v>
       </c>
       <c r="I37" s="0">
+        <v>4.5181776933206777e-10</v>
+      </c>
+      <c r="J37" s="0">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0">
+        <v>0</v>
+      </c>
+      <c r="L37" s="0">
         <v>-4.1690610918236763e-16</v>
       </c>
-      <c r="J37" s="0">
+      <c r="M37" s="0">
         <v>4.1690610918236763e-16</v>
-      </c>
-      <c r="K37" s="0">
-        <v>0</v>
-      </c>
-      <c r="L37" s="0">
-        <v>-4.5181776933206777e-10</v>
-      </c>
-      <c r="M37" s="0">
-        <v>4.5181776933206777e-10</v>
       </c>
       <c r="N37" s="0">
         <v>3.6037120929174132e-05</v>
@@ -3634,16 +4330,16 @@
         <v>1.2512009961400927e-12</v>
       </c>
       <c r="Z37" s="0">
+        <v>-1.6283080173400148</v>
+      </c>
+      <c r="AA37" s="0">
         <v>0.98180716281774816</v>
       </c>
-      <c r="AA37" s="0">
-        <v>-1.0000000004518177</v>
-      </c>
       <c r="AB37" s="0">
-        <v>-1.6283080173400148</v>
+        <v>-1</v>
       </c>
       <c r="AC37" s="0">
-        <v>1.0000000004518177</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3651,28 +4347,28 @@
         <v>3.6000000000000001</v>
       </c>
       <c r="B38" s="0">
+        <v>-1.6622780538063333</v>
+      </c>
+      <c r="C38" s="0">
+        <v>-1.6622780538063333</v>
+      </c>
+      <c r="D38" s="0">
+        <v>-1.662278052570243</v>
+      </c>
+      <c r="E38" s="0">
         <v>1.0157771974151251</v>
       </c>
-      <c r="C38" s="0">
+      <c r="F38" s="0">
         <v>1.0157771974151286</v>
       </c>
-      <c r="D38" s="0">
+      <c r="G38" s="0">
         <v>1.0157771974151915</v>
       </c>
-      <c r="E38" s="0">
-        <v>-1.662278052570243</v>
-      </c>
-      <c r="F38" s="0">
-        <v>-1.6622780538063333</v>
-      </c>
-      <c r="G38" s="0">
-        <v>-1.6622780538063333</v>
-      </c>
       <c r="H38" s="0">
-        <v>0</v>
+        <v>-6.5247873371260862e-10</v>
       </c>
       <c r="I38" s="0">
-        <v>0</v>
+        <v>6.5247873371260862e-10</v>
       </c>
       <c r="J38" s="0">
         <v>0</v>
@@ -3681,10 +4377,10 @@
         <v>0</v>
       </c>
       <c r="L38" s="0">
-        <v>-6.5247873371260862e-10</v>
+        <v>0</v>
       </c>
       <c r="M38" s="0">
-        <v>6.5247873371260862e-10</v>
+        <v>0</v>
       </c>
       <c r="N38" s="0">
         <v>2.9110807990810107e-05</v>
@@ -3723,16 +4419,16 @@
         <v>0</v>
       </c>
       <c r="Z38" s="0">
+        <v>-1.6622780519373919</v>
+      </c>
+      <c r="AA38" s="0">
         <v>1.0157771974151251</v>
       </c>
-      <c r="AA38" s="0">
-        <v>-1.0000000006524787</v>
-      </c>
       <c r="AB38" s="0">
-        <v>-1.6622780519373919</v>
+        <v>-1</v>
       </c>
       <c r="AC38" s="0">
-        <v>1.0000000006524787</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3740,37 +4436,37 @@
         <v>3.7000000000000002</v>
       </c>
       <c r="B39" s="0">
+        <v>-1.6942771974260011</v>
+      </c>
+      <c r="C39" s="0">
+        <v>-1.6942771925384057</v>
+      </c>
+      <c r="D39" s="0">
+        <v>-1.6942771867007258</v>
+      </c>
+      <c r="E39" s="0">
         <v>1.0477763372947344</v>
       </c>
-      <c r="C39" s="0">
+      <c r="F39" s="0">
         <v>1.0477763372947344</v>
       </c>
-      <c r="D39" s="0">
+      <c r="G39" s="0">
         <v>1.0477763372947495</v>
       </c>
-      <c r="E39" s="0">
-        <v>-1.6942771867007258</v>
-      </c>
-      <c r="F39" s="0">
-        <v>-1.6942771925384057</v>
-      </c>
-      <c r="G39" s="0">
-        <v>-1.6942771974260011</v>
-      </c>
       <c r="H39" s="0">
+        <v>0</v>
+      </c>
+      <c r="I39" s="0">
+        <v>0</v>
+      </c>
+      <c r="J39" s="0">
+        <v>0</v>
+      </c>
+      <c r="K39" s="0">
         <v>-1.2807096289507061e-14</v>
       </c>
-      <c r="I39" s="0">
+      <c r="L39" s="0">
         <v>1.2807096289507061e-14</v>
-      </c>
-      <c r="J39" s="0">
-        <v>0</v>
-      </c>
-      <c r="K39" s="0">
-        <v>0</v>
-      </c>
-      <c r="L39" s="0">
-        <v>0</v>
       </c>
       <c r="M39" s="0">
         <v>0</v>
@@ -3812,16 +4508,16 @@
         <v>0</v>
       </c>
       <c r="Z39" s="0">
+        <v>-1.6942771918170012</v>
+      </c>
+      <c r="AA39" s="0">
         <v>1.0477763372947344</v>
       </c>
-      <c r="AA39" s="0">
-        <v>-1.0000000000000129</v>
-      </c>
       <c r="AB39" s="0">
-        <v>-1.6942771918170012</v>
+        <v>-0.99999999999998723</v>
       </c>
       <c r="AC39" s="0">
-        <v>1.0000000000000129</v>
+        <v>0.99999999999998723</v>
       </c>
     </row>
     <row r="40">
@@ -3829,28 +4525,28 @@
         <v>3.8000000000000003</v>
       </c>
       <c r="B40" s="0">
+        <v>-1.7241635050452973</v>
+      </c>
+      <c r="C40" s="0">
+        <v>-1.7241635050452973</v>
+      </c>
+      <c r="D40" s="0">
+        <v>-1.7241635019942119</v>
+      </c>
+      <c r="E40" s="0">
         <v>1.0776626470568729</v>
       </c>
-      <c r="C40" s="0">
+      <c r="F40" s="0">
         <v>1.0776626470568815</v>
       </c>
-      <c r="D40" s="0">
+      <c r="G40" s="0">
         <v>1.0776626470570017</v>
       </c>
-      <c r="E40" s="0">
-        <v>-1.7241635019942119</v>
-      </c>
-      <c r="F40" s="0">
-        <v>-1.7241635050452973</v>
-      </c>
-      <c r="G40" s="0">
-        <v>-1.7241635050452973</v>
-      </c>
       <c r="H40" s="0">
-        <v>0</v>
+        <v>-8.9992421979266746e-09</v>
       </c>
       <c r="I40" s="0">
-        <v>0</v>
+        <v>8.9992421979266746e-09</v>
       </c>
       <c r="J40" s="0">
         <v>0</v>
@@ -3859,10 +4555,10 @@
         <v>0</v>
       </c>
       <c r="L40" s="0">
-        <v>-8.9992421979266746e-09</v>
+        <v>0</v>
       </c>
       <c r="M40" s="0">
-        <v>8.9992421979266746e-09</v>
+        <v>0</v>
       </c>
       <c r="N40" s="0">
         <v>1.9732593399826191e-05</v>
@@ -3901,16 +4597,16 @@
         <v>0</v>
       </c>
       <c r="Z40" s="0">
+        <v>-1.7241635015791397</v>
+      </c>
+      <c r="AA40" s="0">
         <v>1.0776626470568729</v>
       </c>
-      <c r="AA40" s="0">
-        <v>-1.0000000089992422</v>
-      </c>
       <c r="AB40" s="0">
-        <v>-1.7241635015791397</v>
+        <v>-1</v>
       </c>
       <c r="AC40" s="0">
-        <v>1.0000000089992422</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3918,37 +4614,37 @@
         <v>3.9000000000000004</v>
       </c>
       <c r="B41" s="0">
+        <v>-1.7517616913166469</v>
+      </c>
+      <c r="C41" s="0">
+        <v>-1.7517616820400235</v>
+      </c>
+      <c r="D41" s="0">
+        <v>-1.7517616703462908</v>
+      </c>
+      <c r="E41" s="0">
         <v>1.1052608263772854</v>
       </c>
-      <c r="C41" s="0">
+      <c r="F41" s="0">
         <v>1.1052608263772854</v>
       </c>
-      <c r="D41" s="0">
+      <c r="G41" s="0">
         <v>1.1052608263773243</v>
       </c>
-      <c r="E41" s="0">
-        <v>-1.7517616703462908</v>
-      </c>
-      <c r="F41" s="0">
-        <v>-1.7517616820400235</v>
-      </c>
-      <c r="G41" s="0">
-        <v>-1.7517616913166469</v>
-      </c>
       <c r="H41" s="0">
+        <v>0</v>
+      </c>
+      <c r="I41" s="0">
+        <v>0</v>
+      </c>
+      <c r="J41" s="0">
+        <v>0</v>
+      </c>
+      <c r="K41" s="0">
         <v>-1.3001294058148744e-15</v>
       </c>
-      <c r="I41" s="0">
+      <c r="L41" s="0">
         <v>1.3001294058148744e-15</v>
-      </c>
-      <c r="J41" s="0">
-        <v>0</v>
-      </c>
-      <c r="K41" s="0">
-        <v>0</v>
-      </c>
-      <c r="L41" s="0">
-        <v>0</v>
       </c>
       <c r="M41" s="0">
         <v>0</v>
@@ -3990,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="Z41" s="0">
+        <v>-1.7517616808995522</v>
+      </c>
+      <c r="AA41" s="0">
         <v>1.1052608263772854</v>
       </c>
-      <c r="AA41" s="0">
-        <v>-1.0000000000000013</v>
-      </c>
       <c r="AB41" s="0">
-        <v>-1.7517616808995522</v>
+        <v>-0.99999999999999867</v>
       </c>
       <c r="AC41" s="0">
-        <v>1.0000000000000013</v>
+        <v>0.99999999999999867</v>
       </c>
     </row>
     <row r="42">
@@ -4007,28 +4703,28 @@
         <v>4</v>
       </c>
       <c r="B42" s="0">
+        <v>-1.7768511435084386</v>
+      </c>
+      <c r="C42" s="0">
+        <v>-1.7768511435084386</v>
+      </c>
+      <c r="D42" s="0">
+        <v>-1.7768511350253198</v>
+      </c>
+      <c r="E42" s="0">
         <v>1.1303502807949439</v>
       </c>
-      <c r="C42" s="0">
+      <c r="F42" s="0">
         <v>1.130350280795076</v>
       </c>
-      <c r="D42" s="0">
+      <c r="G42" s="0">
         <v>1.1303502807950918</v>
       </c>
-      <c r="E42" s="0">
-        <v>-1.7768511350253198</v>
-      </c>
-      <c r="F42" s="0">
-        <v>-1.7768511435084386</v>
-      </c>
-      <c r="G42" s="0">
-        <v>-1.7768511435084386</v>
-      </c>
       <c r="H42" s="0">
-        <v>0</v>
+        <v>-1.4651881172181967e-08</v>
       </c>
       <c r="I42" s="0">
-        <v>0</v>
+        <v>1.4651881172181967e-08</v>
       </c>
       <c r="J42" s="0">
         <v>0</v>
@@ -4037,10 +4733,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="0">
-        <v>-1.4651881172181967e-08</v>
+        <v>0</v>
       </c>
       <c r="M42" s="0">
-        <v>1.4651881172181967e-08</v>
+        <v>0</v>
       </c>
       <c r="N42" s="0">
         <v>1.417139590336563e-05</v>
@@ -4079,16 +4775,16 @@
         <v>0</v>
       </c>
       <c r="Z42" s="0">
+        <v>-1.7768511353172107</v>
+      </c>
+      <c r="AA42" s="0">
         <v>1.1303502807949439</v>
       </c>
-      <c r="AA42" s="0">
-        <v>-1.0000000146518813</v>
-      </c>
       <c r="AB42" s="0">
-        <v>-1.7768511353172107</v>
+        <v>-1</v>
       </c>
       <c r="AC42" s="0">
-        <v>1.0000000146518813</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -4096,37 +4792,37 @@
         <v>4.1000000000000005</v>
       </c>
       <c r="B43" s="0">
+        <v>-1.7991488944433969</v>
+      </c>
+      <c r="C43" s="0">
+        <v>-1.799148890979922</v>
+      </c>
+      <c r="D43" s="0">
+        <v>-1.7991488763998871</v>
+      </c>
+      <c r="E43" s="0">
         <v>1.1526480327604569</v>
       </c>
-      <c r="C43" s="0">
+      <c r="F43" s="0">
         <v>1.1526480327604569</v>
       </c>
-      <c r="D43" s="0">
+      <c r="G43" s="0">
         <v>1.1526480327605819</v>
       </c>
-      <c r="E43" s="0">
-        <v>-1.7991488763998871</v>
-      </c>
-      <c r="F43" s="0">
-        <v>-1.799148890979922</v>
-      </c>
-      <c r="G43" s="0">
-        <v>-1.7991488944433969</v>
-      </c>
       <c r="H43" s="0">
+        <v>0</v>
+      </c>
+      <c r="I43" s="0">
+        <v>0</v>
+      </c>
+      <c r="J43" s="0">
+        <v>0</v>
+      </c>
+      <c r="K43" s="0">
         <v>-5.3107555447543546e-15</v>
       </c>
-      <c r="I43" s="0">
+      <c r="L43" s="0">
         <v>5.3107555447543546e-15</v>
-      </c>
-      <c r="J43" s="0">
-        <v>0</v>
-      </c>
-      <c r="K43" s="0">
-        <v>0</v>
-      </c>
-      <c r="L43" s="0">
-        <v>0</v>
       </c>
       <c r="M43" s="0">
         <v>0</v>
@@ -4168,16 +4864,16 @@
         <v>0</v>
       </c>
       <c r="Z43" s="0">
+        <v>-1.7991488872827237</v>
+      </c>
+      <c r="AA43" s="0">
         <v>1.1526480327604569</v>
       </c>
-      <c r="AA43" s="0">
-        <v>-1.0000000000000053</v>
-      </c>
       <c r="AB43" s="0">
-        <v>-1.7991488872827237</v>
+        <v>-0.99999999999999467</v>
       </c>
       <c r="AC43" s="0">
-        <v>1.0000000000000053</v>
+        <v>0.99999999999999467</v>
       </c>
     </row>
     <row r="44">
@@ -4185,28 +4881,28 @@
         <v>4.2000000000000002</v>
       </c>
       <c r="B44" s="0">
+        <v>-1.8182840238675335</v>
+      </c>
+      <c r="C44" s="0">
+        <v>-1.8182840238675335</v>
+      </c>
+      <c r="D44" s="0">
+        <v>-1.8182839971775988</v>
+      </c>
+      <c r="E44" s="0">
         <v>1.1717831401302858</v>
       </c>
-      <c r="C44" s="0">
+      <c r="F44" s="0">
         <v>1.171783140130314</v>
       </c>
-      <c r="D44" s="0">
+      <c r="G44" s="0">
         <v>1.1717831401303413</v>
       </c>
-      <c r="E44" s="0">
-        <v>-1.8182839971775988</v>
-      </c>
-      <c r="F44" s="0">
-        <v>-1.8182840238675335</v>
-      </c>
-      <c r="G44" s="0">
-        <v>-1.8182840238675335</v>
-      </c>
       <c r="H44" s="0">
-        <v>0</v>
+        <v>-7.2237892221017346e-09</v>
       </c>
       <c r="I44" s="0">
-        <v>0</v>
+        <v>7.2237892221017346e-09</v>
       </c>
       <c r="J44" s="0">
         <v>0</v>
@@ -4215,10 +4911,10 @@
         <v>0</v>
       </c>
       <c r="L44" s="0">
-        <v>-7.2237892221017346e-09</v>
+        <v>0</v>
       </c>
       <c r="M44" s="0">
-        <v>7.2237892221017346e-09</v>
+        <v>0</v>
       </c>
       <c r="N44" s="0">
         <v>1.0923266929256974e-05</v>
@@ -4257,16 +4953,16 @@
         <v>0</v>
       </c>
       <c r="Z44" s="0">
+        <v>-1.8182839946525526</v>
+      </c>
+      <c r="AA44" s="0">
         <v>1.1717831401302858</v>
       </c>
-      <c r="AA44" s="0">
-        <v>-1.0000000072237891</v>
-      </c>
       <c r="AB44" s="0">
-        <v>-1.8182839946525526</v>
+        <v>-1</v>
       </c>
       <c r="AC44" s="0">
-        <v>1.0000000072237891</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4274,37 +4970,37 @@
         <v>4.2999999999999998</v>
       </c>
       <c r="B45" s="0">
+        <v>-1.8337574785802255</v>
+      </c>
+      <c r="C45" s="0">
+        <v>-1.8337574096245173</v>
+      </c>
+      <c r="D45" s="0">
+        <v>-1.8337574096245173</v>
+      </c>
+      <c r="E45" s="0">
         <v>1.187256551567847</v>
       </c>
-      <c r="C45" s="0">
+      <c r="F45" s="0">
         <v>1.1872565515678952</v>
       </c>
-      <c r="D45" s="0">
+      <c r="G45" s="0">
         <v>1.1872565515683782</v>
       </c>
-      <c r="E45" s="0">
-        <v>-1.8337574096245173</v>
-      </c>
-      <c r="F45" s="0">
-        <v>-1.8337574096245173</v>
-      </c>
-      <c r="G45" s="0">
-        <v>-1.8337574785802255</v>
-      </c>
       <c r="H45" s="0">
         <v>0</v>
       </c>
       <c r="I45" s="0">
-        <v>0</v>
+        <v>-7.0380156199548074e-09</v>
       </c>
       <c r="J45" s="0">
-        <v>0</v>
+        <v>7.0380156199548074e-09</v>
       </c>
       <c r="K45" s="0">
-        <v>-7.0380156199548074e-09</v>
+        <v>0</v>
       </c>
       <c r="L45" s="0">
-        <v>7.0380156199548074e-09</v>
+        <v>0</v>
       </c>
       <c r="M45" s="0">
         <v>0</v>
@@ -4346,16 +5042,16 @@
         <v>0</v>
       </c>
       <c r="Z45" s="0">
+        <v>-1.8337574060901138</v>
+      </c>
+      <c r="AA45" s="0">
         <v>1.187256551567847</v>
       </c>
-      <c r="AA45" s="0">
-        <v>-1.0000000070380157</v>
-      </c>
       <c r="AB45" s="0">
-        <v>-1.8337574060901138</v>
+        <v>-1</v>
       </c>
       <c r="AC45" s="0">
-        <v>1.0000000070380157</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4363,40 +5059,40 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="B46" s="0">
+        <v>-1.8448754687071127</v>
+      </c>
+      <c r="C46" s="0">
+        <v>-1.8448754641763883</v>
+      </c>
+      <c r="D46" s="0">
+        <v>-1.8448754641763883</v>
+      </c>
+      <c r="E46" s="0">
         <v>1.1983745956456902</v>
       </c>
-      <c r="C46" s="0">
+      <c r="F46" s="0">
         <v>1.1983745956458978</v>
       </c>
-      <c r="D46" s="0">
+      <c r="G46" s="0">
         <v>1.1983745956458978</v>
       </c>
-      <c r="E46" s="0">
-        <v>-1.8448754641763883</v>
-      </c>
-      <c r="F46" s="0">
-        <v>-1.8448754641763883</v>
-      </c>
-      <c r="G46" s="0">
-        <v>-1.8448754687071127</v>
-      </c>
       <c r="H46" s="0">
         <v>0</v>
       </c>
       <c r="I46" s="0">
+        <v>-2.7957813491627579e-08</v>
+      </c>
+      <c r="J46" s="0">
+        <v>2.7957813491627579e-08</v>
+      </c>
+      <c r="K46" s="0">
+        <v>0</v>
+      </c>
+      <c r="L46" s="0">
         <v>-2.925790958879369e-15</v>
       </c>
-      <c r="J46" s="0">
+      <c r="M46" s="0">
         <v>2.925790958879369e-15</v>
-      </c>
-      <c r="K46" s="0">
-        <v>-2.7957813491627579e-08</v>
-      </c>
-      <c r="L46" s="0">
-        <v>2.7957813491627579e-08</v>
-      </c>
-      <c r="M46" s="0">
-        <v>0</v>
       </c>
       <c r="N46" s="0">
         <v>9.242534267362807e-06</v>
@@ -4435,16 +5131,16 @@
         <v>3.4236635928933178e-11</v>
       </c>
       <c r="Z46" s="0">
+        <v>-1.844875450167957</v>
+      </c>
+      <c r="AA46" s="0">
         <v>1.1983745956456902</v>
       </c>
-      <c r="AA46" s="0">
-        <v>-1.0000000279578134</v>
-      </c>
       <c r="AB46" s="0">
-        <v>-1.844875450167957</v>
+        <v>-1</v>
       </c>
       <c r="AC46" s="0">
-        <v>1.0000000279578134</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4452,22 +5148,22 @@
         <v>4.5</v>
       </c>
       <c r="B47" s="0">
+        <v>-1.8506322560116761</v>
+      </c>
+      <c r="C47" s="0">
+        <v>-1.8506321168421691</v>
+      </c>
+      <c r="D47" s="0">
+        <v>-1.8506320562740737</v>
+      </c>
+      <c r="E47" s="0">
         <v>1.2041312637741497</v>
       </c>
-      <c r="C47" s="0">
+      <c r="F47" s="0">
         <v>1.2041312637741515</v>
       </c>
-      <c r="D47" s="0">
+      <c r="G47" s="0">
         <v>1.2041312637753985</v>
-      </c>
-      <c r="E47" s="0">
-        <v>-1.8506320562740737</v>
-      </c>
-      <c r="F47" s="0">
-        <v>-1.8506321168421691</v>
-      </c>
-      <c r="G47" s="0">
-        <v>-1.8506322560116761</v>
       </c>
       <c r="H47" s="0">
         <v>0</v>
@@ -4524,13 +5220,13 @@
         <v>0</v>
       </c>
       <c r="Z47" s="0">
+        <v>-1.8506321182964165</v>
+      </c>
+      <c r="AA47" s="0">
         <v>1.2041312637741497</v>
       </c>
-      <c r="AA47" s="0">
+      <c r="AB47" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB47" s="0">
-        <v>-1.8506321182964165</v>
       </c>
       <c r="AC47" s="0">
         <v>1</v>
@@ -4541,22 +5237,22 @@
         <v>4.6000000000000005</v>
       </c>
       <c r="B48" s="0">
+        <v>-1.8494823926577912</v>
+      </c>
+      <c r="C48" s="0">
+        <v>-1.8494823664191911</v>
+      </c>
+      <c r="D48" s="0">
+        <v>-1.8494822787104055</v>
+      </c>
+      <c r="E48" s="0">
         <v>1.2029815119870522</v>
       </c>
-      <c r="C48" s="0">
+      <c r="F48" s="0">
         <v>1.2029815119870684</v>
       </c>
-      <c r="D48" s="0">
+      <c r="G48" s="0">
         <v>1.2029815119875473</v>
-      </c>
-      <c r="E48" s="0">
-        <v>-1.8494822787104055</v>
-      </c>
-      <c r="F48" s="0">
-        <v>-1.8494823664191911</v>
-      </c>
-      <c r="G48" s="0">
-        <v>-1.8494823926577912</v>
       </c>
       <c r="H48" s="0">
         <v>0</v>
@@ -4613,13 +5309,13 @@
         <v>0</v>
       </c>
       <c r="Z48" s="0">
+        <v>-1.849482366509319</v>
+      </c>
+      <c r="AA48" s="0">
         <v>1.2029815119870522</v>
       </c>
-      <c r="AA48" s="0">
+      <c r="AB48" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB48" s="0">
-        <v>-1.849482366509319</v>
       </c>
       <c r="AC48" s="0">
         <v>1</v>
@@ -4630,22 +5326,22 @@
         <v>4.7000000000000002</v>
       </c>
       <c r="B49" s="0">
+        <v>-1.8388531177422081</v>
+      </c>
+      <c r="C49" s="0">
+        <v>-1.8388530730984711</v>
+      </c>
+      <c r="D49" s="0">
+        <v>-1.8388529282402728</v>
+      </c>
+      <c r="E49" s="0">
         <v>1.1923521959003804</v>
       </c>
-      <c r="C49" s="0">
+      <c r="F49" s="0">
         <v>1.1923521959004599</v>
       </c>
-      <c r="D49" s="0">
+      <c r="G49" s="0">
         <v>1.1923521959009822</v>
-      </c>
-      <c r="E49" s="0">
-        <v>-1.8388529282402728</v>
-      </c>
-      <c r="F49" s="0">
-        <v>-1.8388530730984711</v>
-      </c>
-      <c r="G49" s="0">
-        <v>-1.8388531177422081</v>
       </c>
       <c r="H49" s="0">
         <v>0</v>
@@ -4702,13 +5398,13 @@
         <v>0</v>
       </c>
       <c r="Z49" s="0">
+        <v>-1.8388530504226472</v>
+      </c>
+      <c r="AA49" s="0">
         <v>1.1923521959003804</v>
       </c>
-      <c r="AA49" s="0">
+      <c r="AB49" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB49" s="0">
-        <v>-1.8388530504226472</v>
       </c>
       <c r="AC49" s="0">
         <v>1</v>
@@ -4719,37 +5415,37 @@
         <v>4.8000000000000007</v>
       </c>
       <c r="B50" s="0">
+        <v>-1.8139010928324197</v>
+      </c>
+      <c r="C50" s="0">
+        <v>-1.8139009727401618</v>
+      </c>
+      <c r="D50" s="0">
+        <v>-1.8139008128296614</v>
+      </c>
+      <c r="E50" s="0">
         <v>1.1674001212897382</v>
       </c>
-      <c r="C50" s="0">
+      <c r="F50" s="0">
         <v>1.1674001212897382</v>
       </c>
-      <c r="D50" s="0">
+      <c r="G50" s="0">
         <v>1.1674001212916241</v>
       </c>
-      <c r="E50" s="0">
-        <v>-1.8139008128296614</v>
-      </c>
-      <c r="F50" s="0">
-        <v>-1.8139009727401618</v>
-      </c>
-      <c r="G50" s="0">
-        <v>-1.8139010928324197</v>
-      </c>
       <c r="H50" s="0">
+        <v>0</v>
+      </c>
+      <c r="I50" s="0">
+        <v>0</v>
+      </c>
+      <c r="J50" s="0">
+        <v>0</v>
+      </c>
+      <c r="K50" s="0">
         <v>-4.0143313415115668e-15</v>
       </c>
-      <c r="I50" s="0">
+      <c r="L50" s="0">
         <v>4.0143313415115668e-15</v>
-      </c>
-      <c r="J50" s="0">
-        <v>0</v>
-      </c>
-      <c r="K50" s="0">
-        <v>0</v>
-      </c>
-      <c r="L50" s="0">
-        <v>0</v>
       </c>
       <c r="M50" s="0">
         <v>0</v>
@@ -4791,16 +5487,16 @@
         <v>0</v>
       </c>
       <c r="Z50" s="0">
+        <v>-1.813900975812005</v>
+      </c>
+      <c r="AA50" s="0">
         <v>1.1674001212897382</v>
       </c>
-      <c r="AA50" s="0">
-        <v>-1.000000000000004</v>
-      </c>
       <c r="AB50" s="0">
-        <v>-1.813900975812005</v>
+        <v>-0.999999999999996</v>
       </c>
       <c r="AC50" s="0">
-        <v>1.000000000000004</v>
+        <v>0.999999999999996</v>
       </c>
     </row>
     <row r="51">
@@ -4808,40 +5504,40 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="B51" s="0">
+        <v>-1.7634223824974105</v>
+      </c>
+      <c r="C51" s="0">
+        <v>-1.7634222454635693</v>
+      </c>
+      <c r="D51" s="0">
+        <v>-1.7634221158177599</v>
+      </c>
+      <c r="E51" s="0">
         <v>1.116921392530188</v>
       </c>
-      <c r="C51" s="0">
+      <c r="F51" s="0">
         <v>1.1169213925307098</v>
       </c>
-      <c r="D51" s="0">
+      <c r="G51" s="0">
         <v>1.1169213925307098</v>
       </c>
-      <c r="E51" s="0">
-        <v>-1.7634221158177599</v>
-      </c>
-      <c r="F51" s="0">
-        <v>-1.7634222454635693</v>
-      </c>
-      <c r="G51" s="0">
-        <v>-1.7634223824974105</v>
-      </c>
       <c r="H51" s="0">
         <v>0</v>
       </c>
       <c r="I51" s="0">
+        <v>0</v>
+      </c>
+      <c r="J51" s="0">
+        <v>0</v>
+      </c>
+      <c r="K51" s="0">
+        <v>0</v>
+      </c>
+      <c r="L51" s="0">
         <v>-5.7126206054699346e-13</v>
       </c>
-      <c r="J51" s="0">
+      <c r="M51" s="0">
         <v>5.7126206054699346e-13</v>
-      </c>
-      <c r="K51" s="0">
-        <v>0</v>
-      </c>
-      <c r="L51" s="0">
-        <v>0</v>
-      </c>
-      <c r="M51" s="0">
-        <v>0</v>
       </c>
       <c r="N51" s="0">
         <v>1.5419006764559008e-05</v>
@@ -4880,16 +5576,16 @@
         <v>4.0069832273543578e-09</v>
       </c>
       <c r="Z51" s="0">
+        <v>-1.7634222470524548</v>
+      </c>
+      <c r="AA51" s="0">
         <v>1.116921392530188</v>
       </c>
-      <c r="AA51" s="0">
-        <v>-1.0000000000005713</v>
-      </c>
       <c r="AB51" s="0">
-        <v>-1.7634222470524548</v>
+        <v>-1</v>
       </c>
       <c r="AC51" s="0">
-        <v>1.0000000000005713</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4897,22 +5593,22 @@
         <v>5</v>
       </c>
       <c r="B52" s="0">
+        <v>-1.6471785833989585</v>
+      </c>
+      <c r="C52" s="0">
+        <v>-1.6471783636532376</v>
+      </c>
+      <c r="D52" s="0">
+        <v>-1.6471783222900571</v>
+      </c>
+      <c r="E52" s="0">
         <v>1.0006774657390904</v>
       </c>
-      <c r="C52" s="0">
+      <c r="F52" s="0">
         <v>1.0006774657394617</v>
       </c>
-      <c r="D52" s="0">
+      <c r="G52" s="0">
         <v>1.0006774657469013</v>
-      </c>
-      <c r="E52" s="0">
-        <v>-1.6471783222900571</v>
-      </c>
-      <c r="F52" s="0">
-        <v>-1.6471783636532376</v>
-      </c>
-      <c r="G52" s="0">
-        <v>-1.6471785833989585</v>
       </c>
       <c r="H52" s="0">
         <v>0</v>
@@ -4969,13 +5665,13 @@
         <v>0</v>
       </c>
       <c r="Z52" s="0">
+        <v>-1.6471783202613572</v>
+      </c>
+      <c r="AA52" s="0">
         <v>1.0006774657390904</v>
       </c>
-      <c r="AA52" s="0">
+      <c r="AB52" s="0">
         <v>-1</v>
-      </c>
-      <c r="AB52" s="0">
-        <v>-1.6471783202613572</v>
       </c>
       <c r="AC52" s="0">
         <v>1</v>
@@ -4986,13 +5682,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B53" s="0">
-        <v>0.82741773167875388</v>
+        <v>0.82741773168747845</v>
       </c>
       <c r="C53" s="0">
         <v>0.82741773168598287</v>
       </c>
       <c r="D53" s="0">
-        <v>0.82741773168747845</v>
+        <v>0.82741773167875388</v>
       </c>
       <c r="E53" s="0">
         <v>-1.4739184829402825</v>
@@ -5022,52 +5718,52 @@
         <v>-0</v>
       </c>
       <c r="N53" s="0">
+        <v>-181.05827388925434</v>
+      </c>
+      <c r="O53" s="0">
+        <v>-181.05827388755284</v>
+      </c>
+      <c r="P53" s="0">
+        <v>-181.05827387932905</v>
+      </c>
+      <c r="Q53" s="0">
+        <v>-9.5069442853613651e-05</v>
+      </c>
+      <c r="R53" s="0">
+        <v>-9.5069442853613651e-05</v>
+      </c>
+      <c r="S53" s="0">
         <v>-9.5069379374660993e-05</v>
       </c>
-      <c r="O53" s="0">
-        <v>-9.5069442853613651e-05</v>
-      </c>
-      <c r="P53" s="0">
-        <v>-9.5069442853613651e-05</v>
-      </c>
-      <c r="Q53" s="0">
-        <v>-181.05827387932905</v>
-      </c>
-      <c r="R53" s="0">
-        <v>-181.05827388755284</v>
-      </c>
-      <c r="S53" s="0">
-        <v>-181.05827388925434</v>
-      </c>
       <c r="T53" s="0">
         <v>0</v>
       </c>
       <c r="U53" s="0">
+        <v>0</v>
+      </c>
+      <c r="V53" s="0">
+        <v>0</v>
+      </c>
+      <c r="W53" s="0">
         <v>-7.6924863820776555e-11</v>
       </c>
-      <c r="V53" s="0">
+      <c r="X53" s="0">
         <v>7.6924863820776555e-11</v>
       </c>
-      <c r="W53" s="0">
-        <v>0</v>
-      </c>
-      <c r="X53" s="0">
-        <v>0</v>
-      </c>
       <c r="Y53" s="0">
         <v>0</v>
       </c>
       <c r="Z53" s="0">
-        <v>0.82741773167875388</v>
+        <v>0.82741773168747845</v>
       </c>
       <c r="AA53" s="0">
-        <v>-1.0000001287792581</v>
+        <v>-1.4739185862097453</v>
       </c>
       <c r="AB53" s="0">
-        <v>-1.4739185862010207</v>
+        <v>-1.5</v>
       </c>
       <c r="AC53" s="0">
-        <v>1.0000001287792581</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="54">
@@ -5075,13 +5771,13 @@
         <v>5.1999999999999993</v>
       </c>
       <c r="B54" s="0">
-        <v>1.0950867184307844</v>
+        <v>1.0950867184563373</v>
       </c>
       <c r="C54" s="0">
         <v>1.0950867184307844</v>
       </c>
       <c r="D54" s="0">
-        <v>1.0950867184563373</v>
+        <v>1.0950867184307844</v>
       </c>
       <c r="E54" s="0">
         <v>-1.7415871991717837</v>
@@ -5093,13 +5789,13 @@
         <v>-1.7415877970960685</v>
       </c>
       <c r="H54" s="0">
+        <v>-0</v>
+      </c>
+      <c r="I54" s="0">
         <v>6.9501926887805836e-14</v>
       </c>
-      <c r="I54" s="0">
+      <c r="J54" s="0">
         <v>-6.9501926887805836e-14</v>
-      </c>
-      <c r="J54" s="0">
-        <v>-0</v>
       </c>
       <c r="K54" s="0">
         <v>-0</v>
@@ -5111,52 +5807,52 @@
         <v>-0</v>
       </c>
       <c r="N54" s="0">
+        <v>-973.24201257178038</v>
+      </c>
+      <c r="O54" s="0">
+        <v>-973.24201241552214</v>
+      </c>
+      <c r="P54" s="0">
+        <v>-973.24201241552214</v>
+      </c>
+      <c r="Q54" s="0">
+        <v>-1.7686390702249036e-05</v>
+      </c>
+      <c r="R54" s="0">
+        <v>-1.7686347691345797e-05</v>
+      </c>
+      <c r="S54" s="0">
         <v>-1.7686324256919461e-05</v>
       </c>
-      <c r="O54" s="0">
-        <v>-1.7686347691345797e-05</v>
-      </c>
-      <c r="P54" s="0">
-        <v>-1.7686390702249036e-05</v>
-      </c>
-      <c r="Q54" s="0">
-        <v>-973.24201241552214</v>
-      </c>
-      <c r="R54" s="0">
-        <v>-973.24201241552214</v>
-      </c>
-      <c r="S54" s="0">
-        <v>-973.24201257178038</v>
-      </c>
       <c r="T54" s="0">
         <v>0</v>
       </c>
       <c r="U54" s="0">
-        <v>0</v>
+        <v>-4.250084469697453e-10</v>
       </c>
       <c r="V54" s="0">
-        <v>0</v>
+        <v>4.250084469697453e-10</v>
       </c>
       <c r="W54" s="0">
-        <v>-4.250084469697453e-10</v>
+        <v>0</v>
       </c>
       <c r="X54" s="0">
-        <v>4.250084469697453e-10</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="0">
         <v>0</v>
       </c>
       <c r="Z54" s="0">
-        <v>1.0950867184307844</v>
+        <v>1.0950867184563373</v>
       </c>
       <c r="AA54" s="0">
-        <v>-1.0000000000000695</v>
+        <v>-1.7415875729786041</v>
       </c>
       <c r="AB54" s="0">
-        <v>-1.7415875729530512</v>
+        <v>-1.5</v>
       </c>
       <c r="AC54" s="0">
-        <v>1.0000000000000695</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="55">
@@ -5239,10 +5935,10 @@
         <v>1.1839662703976523</v>
       </c>
       <c r="AA55" s="0">
+        <v>-1.8304671249199191</v>
+      </c>
+      <c r="AB55" s="0">
         <v>-1.5</v>
-      </c>
-      <c r="AB55" s="0">
-        <v>-1.8304671249199191</v>
       </c>
       <c r="AC55" s="0">
         <v>1.5</v>
@@ -5253,13 +5949,13 @@
         <v>5.3999999999999995</v>
       </c>
       <c r="B56" s="0">
-        <v>1.2191267919793605</v>
+        <v>1.2191267919915465</v>
       </c>
       <c r="C56" s="0">
         <v>1.2191267919915465</v>
       </c>
       <c r="D56" s="0">
-        <v>1.2191267919915465</v>
+        <v>1.2191267919793605</v>
       </c>
       <c r="E56" s="0">
         <v>-1.8656270303777183</v>
@@ -5271,13 +5967,13 @@
         <v>-1.8656279877171362</v>
       </c>
       <c r="H56" s="0">
+        <v>3.3898994248003862e-14</v>
+      </c>
+      <c r="I56" s="0">
+        <v>-3.3898994248003862e-14</v>
+      </c>
+      <c r="J56" s="0">
         <v>-0</v>
-      </c>
-      <c r="I56" s="0">
-        <v>3.3898994248003862e-14</v>
-      </c>
-      <c r="J56" s="0">
-        <v>-3.3898994248003862e-14</v>
       </c>
       <c r="K56" s="0">
         <v>-0</v>
@@ -5289,28 +5985,28 @@
         <v>-0</v>
       </c>
       <c r="N56" s="0">
+        <v>-2121.7564674867972</v>
+      </c>
+      <c r="O56" s="0">
+        <v>-2121.7564674867972</v>
+      </c>
+      <c r="P56" s="0">
+        <v>-2121.7564673243382</v>
+      </c>
+      <c r="Q56" s="0">
+        <v>-8.1126957568870346e-06</v>
+      </c>
+      <c r="R56" s="0">
+        <v>-8.112662836130746e-06</v>
+      </c>
+      <c r="S56" s="0">
         <v>-8.1126469580252208e-06</v>
       </c>
-      <c r="O56" s="0">
-        <v>-8.112662836130746e-06</v>
-      </c>
-      <c r="P56" s="0">
-        <v>-8.1126957568870346e-06</v>
-      </c>
-      <c r="Q56" s="0">
-        <v>-2121.7564673243382</v>
-      </c>
-      <c r="R56" s="0">
-        <v>-2121.7564674867972</v>
-      </c>
-      <c r="S56" s="0">
-        <v>-2121.7564674867972</v>
-      </c>
       <c r="T56" s="0">
-        <v>0</v>
+        <v>-4.5192068112814144e-10</v>
       </c>
       <c r="U56" s="0">
-        <v>0</v>
+        <v>4.5192068112814144e-10</v>
       </c>
       <c r="V56" s="0">
         <v>0</v>
@@ -5319,22 +6015,22 @@
         <v>0</v>
       </c>
       <c r="X56" s="0">
-        <v>-4.5192068112814144e-10</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="0">
-        <v>4.5192068112814144e-10</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="0">
-        <v>1.2191267919793605</v>
+        <v>1.2191267919915465</v>
       </c>
       <c r="AA56" s="0">
-        <v>-2.0000000000000338</v>
+        <v>-1.8656276465138133</v>
       </c>
       <c r="AB56" s="0">
-        <v>-1.8656276465016273</v>
+        <v>-1.499999999999966</v>
       </c>
       <c r="AC56" s="0">
-        <v>2.0000000000000338</v>
+        <v>1.499999999999966</v>
       </c>
     </row>
     <row r="57">
@@ -5342,13 +6038,13 @@
         <v>5.5</v>
       </c>
       <c r="B57" s="0">
-        <v>1.1964182271942112</v>
+        <v>1.1964182271993626</v>
       </c>
       <c r="C57" s="0">
         <v>1.1964182271942436</v>
       </c>
       <c r="D57" s="0">
-        <v>1.1964182271993626</v>
+        <v>1.1964182271942112</v>
       </c>
       <c r="E57" s="0">
         <v>-1.8429189095512979</v>
@@ -5378,52 +6074,52 @@
         <v>-5.4340983416431608e-07</v>
       </c>
       <c r="N57" s="0">
+        <v>-1839.6257374995657</v>
+      </c>
+      <c r="O57" s="0">
+        <v>-1839.6257374403967</v>
+      </c>
+      <c r="P57" s="0">
+        <v>-1839.6257374400241</v>
+      </c>
+      <c r="Q57" s="0">
+        <v>-9.356857932384755e-06</v>
+      </c>
+      <c r="R57" s="0">
         <v>-9.3568491148182592e-06</v>
       </c>
-      <c r="O57" s="0">
+      <c r="S57" s="0">
         <v>-9.3568491148182592e-06</v>
       </c>
-      <c r="P57" s="0">
-        <v>-9.356857932384755e-06</v>
-      </c>
-      <c r="Q57" s="0">
-        <v>-1839.6257374400241</v>
-      </c>
-      <c r="R57" s="0">
-        <v>-1839.6257374403967</v>
-      </c>
-      <c r="S57" s="0">
-        <v>-1839.6257374995657</v>
-      </c>
       <c r="T57" s="0">
+        <v>0</v>
+      </c>
+      <c r="U57" s="0">
+        <v>0</v>
+      </c>
+      <c r="V57" s="0">
+        <v>0</v>
+      </c>
+      <c r="W57" s="0">
+        <v>0</v>
+      </c>
+      <c r="X57" s="0">
         <v>-3.1947508051118773e-11</v>
       </c>
-      <c r="U57" s="0">
+      <c r="Y57" s="0">
         <v>3.1947508051118773e-11</v>
       </c>
-      <c r="V57" s="0">
-        <v>0</v>
-      </c>
-      <c r="W57" s="0">
-        <v>0</v>
-      </c>
-      <c r="X57" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="0">
-        <v>0</v>
-      </c>
       <c r="Z57" s="0">
-        <v>1.1964182271942112</v>
+        <v>1.1964182271993626</v>
       </c>
       <c r="AA57" s="0">
-        <v>-2.000000543409834</v>
+        <v>-1.8429190817216294</v>
       </c>
       <c r="AB57" s="0">
-        <v>-1.842919081716478</v>
+        <v>-1.5</v>
       </c>
       <c r="AC57" s="0">
-        <v>2.000000543409834</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="58">
@@ -5467,37 +6163,37 @@
         <v>-0</v>
       </c>
       <c r="N58" s="0">
+        <v>-246.00629296315807</v>
+      </c>
+      <c r="O58" s="0">
+        <v>-246.00629295845019</v>
+      </c>
+      <c r="P58" s="0">
+        <v>-246.00629295579262</v>
+      </c>
+      <c r="Q58" s="0">
+        <v>-6.9970158704430141e-05</v>
+      </c>
+      <c r="R58" s="0">
+        <v>-6.9970158704430141e-05</v>
+      </c>
+      <c r="S58" s="0">
         <v>-6.996931188455191e-05</v>
       </c>
-      <c r="O58" s="0">
-        <v>-6.9970158704430141e-05</v>
-      </c>
-      <c r="P58" s="0">
-        <v>-6.9970158704430141e-05</v>
-      </c>
-      <c r="Q58" s="0">
-        <v>-246.00629295579262</v>
-      </c>
-      <c r="R58" s="0">
-        <v>-246.00629295845019</v>
-      </c>
-      <c r="S58" s="0">
-        <v>-246.00629296315807</v>
-      </c>
       <c r="T58" s="0">
         <v>0</v>
       </c>
       <c r="U58" s="0">
+        <v>0</v>
+      </c>
+      <c r="V58" s="0">
+        <v>0</v>
+      </c>
+      <c r="W58" s="0">
         <v>-1.5659448974121337e-11</v>
       </c>
-      <c r="V58" s="0">
+      <c r="X58" s="0">
         <v>1.5659448974121337e-11</v>
-      </c>
-      <c r="W58" s="0">
-        <v>0</v>
-      </c>
-      <c r="X58" s="0">
-        <v>0</v>
       </c>
       <c r="Y58" s="0">
         <v>0</v>
@@ -5506,13 +6202,13 @@
         <v>0.87620479861789724</v>
       </c>
       <c r="AA58" s="0">
-        <v>-2.0000000356191663</v>
+        <v>-1.5227056531401639</v>
       </c>
       <c r="AB58" s="0">
-        <v>-1.5227056531401639</v>
+        <v>-1.5</v>
       </c>
       <c r="AC58" s="0">
-        <v>2.0000000356191663</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="59">
@@ -5520,40 +6216,40 @@
         <v>5.7000000000000002</v>
       </c>
       <c r="B59" s="0">
+        <v>-1.9480207549998405</v>
+      </c>
+      <c r="C59" s="0">
+        <v>-1.9479992856913393</v>
+      </c>
+      <c r="D59" s="0">
+        <v>-1.9479992856913393</v>
+      </c>
+      <c r="E59" s="0">
         <v>1.3014986275277607</v>
       </c>
-      <c r="C59" s="0">
+      <c r="F59" s="0">
         <v>1.3014986275320897</v>
       </c>
-      <c r="D59" s="0">
+      <c r="G59" s="0">
         <v>1.3014986275320897</v>
       </c>
-      <c r="E59" s="0">
-        <v>-1.9479992856913393</v>
-      </c>
-      <c r="F59" s="0">
-        <v>-1.9479992856913393</v>
-      </c>
-      <c r="G59" s="0">
-        <v>-1.9480207549998405</v>
-      </c>
       <c r="H59" s="0">
         <v>0</v>
       </c>
       <c r="I59" s="0">
+        <v>-4.7453887983984984e-09</v>
+      </c>
+      <c r="J59" s="0">
+        <v>4.7453887983984984e-09</v>
+      </c>
+      <c r="K59" s="0">
+        <v>0</v>
+      </c>
+      <c r="L59" s="0">
         <v>-3.755737082236538e-14</v>
       </c>
-      <c r="J59" s="0">
+      <c r="M59" s="0">
         <v>3.755737082236538e-14</v>
-      </c>
-      <c r="K59" s="0">
-        <v>-4.7453887983984984e-09</v>
-      </c>
-      <c r="L59" s="0">
-        <v>4.7453887983984984e-09</v>
-      </c>
-      <c r="M59" s="0">
-        <v>0</v>
       </c>
       <c r="N59" s="0">
         <v>4.8342943501922168e-06</v>
@@ -5592,16 +6288,16 @@
         <v>8.4012315462255819e-10</v>
       </c>
       <c r="Z59" s="0">
+        <v>-1.9479994820500275</v>
+      </c>
+      <c r="AA59" s="0">
         <v>1.3014986275277607</v>
       </c>
-      <c r="AA59" s="0">
-        <v>-2.000000004745389</v>
-      </c>
       <c r="AB59" s="0">
-        <v>-1.9479994820500275</v>
+        <v>-2</v>
       </c>
       <c r="AC59" s="0">
-        <v>2.000000004745389</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -5609,22 +6305,22 @@
         <v>5.7999999999999998</v>
       </c>
       <c r="B60" s="0">
+        <v>-2.125681111720727</v>
+      </c>
+      <c r="C60" s="0">
+        <v>-2.1256779019073346</v>
+      </c>
+      <c r="D60" s="0">
+        <v>-2.1256744399507186</v>
+      </c>
+      <c r="E60" s="0">
         <v>1.4791723962868284</v>
       </c>
-      <c r="C60" s="0">
+      <c r="F60" s="0">
         <v>1.4791723962891477</v>
       </c>
-      <c r="D60" s="0">
+      <c r="G60" s="0">
         <v>1.479172396289272</v>
-      </c>
-      <c r="E60" s="0">
-        <v>-2.1256744399507186</v>
-      </c>
-      <c r="F60" s="0">
-        <v>-2.1256779019073346</v>
-      </c>
-      <c r="G60" s="0">
-        <v>-2.125681111720727</v>
       </c>
       <c r="H60" s="0">
         <v>0</v>
@@ -5681,13 +6377,13 @@
         <v>0</v>
       </c>
       <c r="Z60" s="0">
+        <v>-2.1256732508090952</v>
+      </c>
+      <c r="AA60" s="0">
         <v>1.4791723962868284</v>
       </c>
-      <c r="AA60" s="0">
+      <c r="AB60" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB60" s="0">
-        <v>-2.1256732508090952</v>
       </c>
       <c r="AC60" s="0">
         <v>2</v>
@@ -5698,28 +6394,28 @@
         <v>5.8999999999999995</v>
       </c>
       <c r="B61" s="0">
+        <v>-2.2483314983130112</v>
+      </c>
+      <c r="C61" s="0">
+        <v>-2.2483314983130112</v>
+      </c>
+      <c r="D61" s="0">
+        <v>-2.2483268254935158</v>
+      </c>
+      <c r="E61" s="0">
         <v>1.6018312981751603</v>
       </c>
-      <c r="C61" s="0">
+      <c r="F61" s="0">
         <v>1.6018312981759129</v>
       </c>
-      <c r="D61" s="0">
+      <c r="G61" s="0">
         <v>1.6018312981773102</v>
       </c>
-      <c r="E61" s="0">
-        <v>-2.2483268254935158</v>
-      </c>
-      <c r="F61" s="0">
-        <v>-2.2483314983130112</v>
-      </c>
-      <c r="G61" s="0">
-        <v>-2.2483314983130112</v>
-      </c>
       <c r="H61" s="0">
-        <v>0</v>
+        <v>-6.874570113585136e-06</v>
       </c>
       <c r="I61" s="0">
-        <v>0</v>
+        <v>6.874570113585136e-06</v>
       </c>
       <c r="J61" s="0">
         <v>0</v>
@@ -5728,10 +6424,10 @@
         <v>0</v>
       </c>
       <c r="L61" s="0">
-        <v>-6.874570113585136e-06</v>
+        <v>0</v>
       </c>
       <c r="M61" s="0">
-        <v>6.874570113585136e-06</v>
+        <v>0</v>
       </c>
       <c r="N61" s="0">
         <v>7.3258721609461896e-07</v>
@@ -5770,16 +6466,16 @@
         <v>0</v>
       </c>
       <c r="Z61" s="0">
+        <v>-2.2483321526974271</v>
+      </c>
+      <c r="AA61" s="0">
         <v>1.6018312981751603</v>
       </c>
-      <c r="AA61" s="0">
-        <v>-2.0000068745701136</v>
-      </c>
       <c r="AB61" s="0">
-        <v>-2.2483321526974271</v>
+        <v>-2</v>
       </c>
       <c r="AC61" s="0">
-        <v>2.0000068745701136</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -5787,22 +6483,22 @@
         <v>6</v>
       </c>
       <c r="B62" s="0">
+        <v>-2.3478752775868079</v>
+      </c>
+      <c r="C62" s="0">
+        <v>-2.347843037009758</v>
+      </c>
+      <c r="D62" s="0">
+        <v>-2.3478347295459714</v>
+      </c>
+      <c r="E62" s="0">
         <v>1.701339560881076</v>
       </c>
-      <c r="C62" s="0">
+      <c r="F62" s="0">
         <v>1.701339560882474</v>
       </c>
-      <c r="D62" s="0">
+      <c r="G62" s="0">
         <v>1.7013395608824942</v>
-      </c>
-      <c r="E62" s="0">
-        <v>-2.3478347295459714</v>
-      </c>
-      <c r="F62" s="0">
-        <v>-2.347843037009758</v>
-      </c>
-      <c r="G62" s="0">
-        <v>-2.3478752775868079</v>
       </c>
       <c r="H62" s="0">
         <v>0</v>
@@ -5859,13 +6555,13 @@
         <v>0</v>
       </c>
       <c r="Z62" s="0">
+        <v>-2.347840415403343</v>
+      </c>
+      <c r="AA62" s="0">
         <v>1.701339560881076</v>
       </c>
-      <c r="AA62" s="0">
+      <c r="AB62" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB62" s="0">
-        <v>-2.347840415403343</v>
       </c>
       <c r="AC62" s="0">
         <v>2</v>
@@ -5876,22 +6572,22 @@
         <v>6.0999999999999996</v>
       </c>
       <c r="B63" s="0">
+        <v>-2.4339648875730955</v>
+      </c>
+      <c r="C63" s="0">
+        <v>-2.4339364580586373</v>
+      </c>
+      <c r="D63" s="0">
+        <v>-2.4335533671538365</v>
+      </c>
+      <c r="E63" s="0">
         <v>1.7874404946620253</v>
       </c>
-      <c r="C63" s="0">
+      <c r="F63" s="0">
         <v>1.787440494662067</v>
       </c>
-      <c r="D63" s="0">
+      <c r="G63" s="0">
         <v>1.7874404946645663</v>
-      </c>
-      <c r="E63" s="0">
-        <v>-2.4335533671538365</v>
-      </c>
-      <c r="F63" s="0">
-        <v>-2.4339364580586373</v>
-      </c>
-      <c r="G63" s="0">
-        <v>-2.4339648875730955</v>
       </c>
       <c r="H63" s="0">
         <v>0</v>
@@ -5948,13 +6644,13 @@
         <v>0</v>
       </c>
       <c r="Z63" s="0">
+        <v>-2.4339413491842921</v>
+      </c>
+      <c r="AA63" s="0">
         <v>1.7874404946620253</v>
       </c>
-      <c r="AA63" s="0">
+      <c r="AB63" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB63" s="0">
-        <v>-2.4339413491842921</v>
       </c>
       <c r="AC63" s="0">
         <v>2</v>
@@ -5965,37 +6661,37 @@
         <v>6.1999999999999993</v>
       </c>
       <c r="B64" s="0">
+        <v>-2.5110378950866572</v>
+      </c>
+      <c r="C64" s="0">
+        <v>-2.5109754675201588</v>
+      </c>
+      <c r="D64" s="0">
+        <v>-2.5109754675201588</v>
+      </c>
+      <c r="E64" s="0">
         <v>1.8645063066759897</v>
       </c>
-      <c r="C64" s="0">
+      <c r="F64" s="0">
         <v>1.8645063066760332</v>
       </c>
-      <c r="D64" s="0">
+      <c r="G64" s="0">
         <v>1.8645063067001602</v>
       </c>
-      <c r="E64" s="0">
-        <v>-2.5109754675201588</v>
-      </c>
-      <c r="F64" s="0">
-        <v>-2.5109754675201588</v>
-      </c>
-      <c r="G64" s="0">
-        <v>-2.5110378950866572</v>
-      </c>
       <c r="H64" s="0">
         <v>0</v>
       </c>
       <c r="I64" s="0">
-        <v>0</v>
+        <v>-0.00022270023991580775</v>
       </c>
       <c r="J64" s="0">
-        <v>0</v>
+        <v>0.00022270023991580775</v>
       </c>
       <c r="K64" s="0">
-        <v>-0.00022270023991580775</v>
+        <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>0.00022270023991580775</v>
+        <v>0</v>
       </c>
       <c r="M64" s="0">
         <v>0</v>
@@ -6037,16 +6733,16 @@
         <v>0</v>
       </c>
       <c r="Z64" s="0">
+        <v>-2.5110071611982563</v>
+      </c>
+      <c r="AA64" s="0">
         <v>1.8645063066759897</v>
       </c>
-      <c r="AA64" s="0">
-        <v>-2.0002227002399158</v>
-      </c>
       <c r="AB64" s="0">
-        <v>-2.5110071611982563</v>
+        <v>-2</v>
       </c>
       <c r="AC64" s="0">
-        <v>2.0002227002399158</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -6054,22 +6750,22 @@
         <v>6.2999999999999998</v>
       </c>
       <c r="B65" s="0">
+        <v>-2.5824256196557043</v>
+      </c>
+      <c r="C65" s="0">
+        <v>-2.5813740845311646</v>
+      </c>
+      <c r="D65" s="0">
+        <v>-2.5812770853220739</v>
+      </c>
+      <c r="E65" s="0">
         <v>1.9349063703151375</v>
       </c>
-      <c r="C65" s="0">
+      <c r="F65" s="0">
         <v>1.9349063703151999</v>
       </c>
-      <c r="D65" s="0">
+      <c r="G65" s="0">
         <v>1.9349063703247951</v>
-      </c>
-      <c r="E65" s="0">
-        <v>-2.5812770853220739</v>
-      </c>
-      <c r="F65" s="0">
-        <v>-2.5813740845311646</v>
-      </c>
-      <c r="G65" s="0">
-        <v>-2.5824256196557043</v>
       </c>
       <c r="H65" s="0">
         <v>0</v>
@@ -6126,13 +6822,13 @@
         <v>0</v>
       </c>
       <c r="Z65" s="0">
+        <v>-2.5814072248374043</v>
+      </c>
+      <c r="AA65" s="0">
         <v>1.9349063703151375</v>
       </c>
-      <c r="AA65" s="0">
+      <c r="AB65" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB65" s="0">
-        <v>-2.5814072248374043</v>
       </c>
       <c r="AC65" s="0">
         <v>2</v>
@@ -6143,28 +6839,28 @@
         <v>6.4000000000000004</v>
       </c>
       <c r="B66" s="0">
+        <v>-2.6467017011652363</v>
+      </c>
+      <c r="C66" s="0">
+        <v>-2.6467017011652363</v>
+      </c>
+      <c r="D66" s="0">
+        <v>-2.6456334687805718</v>
+      </c>
+      <c r="E66" s="0">
         <v>2.0000788719782761</v>
       </c>
-      <c r="C66" s="0">
+      <c r="F66" s="0">
         <v>2.00007887198143</v>
       </c>
-      <c r="D66" s="0">
+      <c r="G66" s="0">
         <v>2.0000788719815121</v>
       </c>
-      <c r="E66" s="0">
-        <v>-2.6456334687805718</v>
-      </c>
-      <c r="F66" s="0">
-        <v>-2.6467017011652363</v>
-      </c>
-      <c r="G66" s="0">
-        <v>-2.6467017011652363</v>
-      </c>
       <c r="H66" s="0">
-        <v>0</v>
+        <v>-6.671320409504941e-05</v>
       </c>
       <c r="I66" s="0">
-        <v>0</v>
+        <v>6.671320409504941e-05</v>
       </c>
       <c r="J66" s="0">
         <v>0</v>
@@ -6173,10 +6869,10 @@
         <v>0</v>
       </c>
       <c r="L66" s="0">
-        <v>-6.671320409504941e-05</v>
+        <v>0</v>
       </c>
       <c r="M66" s="0">
-        <v>6.671320409504941e-05</v>
+        <v>0</v>
       </c>
       <c r="N66" s="0">
         <v>5.9952255743433861e-08</v>
@@ -6215,16 +6911,16 @@
         <v>0</v>
       </c>
       <c r="Z66" s="0">
+        <v>-2.6465797265005429</v>
+      </c>
+      <c r="AA66" s="0">
         <v>2.0000788719782761</v>
       </c>
-      <c r="AA66" s="0">
-        <v>-2.0000667132040952</v>
-      </c>
       <c r="AB66" s="0">
-        <v>-2.6465797265005429</v>
+        <v>-2</v>
       </c>
       <c r="AC66" s="0">
-        <v>2.0000667132040952</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -6232,22 +6928,22 @@
         <v>6.5</v>
       </c>
       <c r="B67" s="0">
+        <v>-2.7075228589670983</v>
+      </c>
+      <c r="C67" s="0">
+        <v>-2.7074493349748296</v>
+      </c>
+      <c r="D67" s="0">
+        <v>-2.7053744973258014</v>
+      </c>
+      <c r="E67" s="0">
         <v>2.0609644878138189</v>
       </c>
-      <c r="C67" s="0">
+      <c r="F67" s="0">
         <v>2.0609644878142834</v>
       </c>
-      <c r="D67" s="0">
+      <c r="G67" s="0">
         <v>2.0609644878167304</v>
-      </c>
-      <c r="E67" s="0">
-        <v>-2.7053744973258014</v>
-      </c>
-      <c r="F67" s="0">
-        <v>-2.7074493349748296</v>
-      </c>
-      <c r="G67" s="0">
-        <v>-2.7075228589670983</v>
       </c>
       <c r="H67" s="0">
         <v>0</v>
@@ -6304,13 +7000,13 @@
         <v>0</v>
       </c>
       <c r="Z67" s="0">
+        <v>-2.7074653423360857</v>
+      </c>
+      <c r="AA67" s="0">
         <v>2.0609644878138189</v>
       </c>
-      <c r="AA67" s="0">
+      <c r="AB67" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB67" s="0">
-        <v>-2.7074653423360857</v>
       </c>
       <c r="AC67" s="0">
         <v>2</v>
@@ -6321,22 +7017,22 @@
         <v>6.5999999999999996</v>
       </c>
       <c r="B68" s="0">
+        <v>-2.7665942193134465</v>
+      </c>
+      <c r="C68" s="0">
+        <v>-2.7650345630145954</v>
+      </c>
+      <c r="D68" s="0">
+        <v>-2.764120737104423</v>
+      </c>
+      <c r="E68" s="0">
         <v>2.1182109429930658</v>
       </c>
-      <c r="C68" s="0">
+      <c r="F68" s="0">
         <v>2.1182109430535885</v>
       </c>
-      <c r="D68" s="0">
+      <c r="G68" s="0">
         <v>2.1182109430536045</v>
-      </c>
-      <c r="E68" s="0">
-        <v>-2.764120737104423</v>
-      </c>
-      <c r="F68" s="0">
-        <v>-2.7650345630145954</v>
-      </c>
-      <c r="G68" s="0">
-        <v>-2.7665942193134465</v>
       </c>
       <c r="H68" s="0">
         <v>0</v>
@@ -6393,13 +7089,13 @@
         <v>0</v>
       </c>
       <c r="Z68" s="0">
+        <v>-2.7647117975153326</v>
+      </c>
+      <c r="AA68" s="0">
         <v>2.1182109429930658</v>
       </c>
-      <c r="AA68" s="0">
+      <c r="AB68" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB68" s="0">
-        <v>-2.7647117975153326</v>
       </c>
       <c r="AC68" s="0">
         <v>2</v>
@@ -6410,22 +7106,22 @@
         <v>6.6999999999999993</v>
       </c>
       <c r="B69" s="0">
+        <v>-2.8217960020049278</v>
+      </c>
+      <c r="C69" s="0">
+        <v>-2.8180548538972006</v>
+      </c>
+      <c r="D69" s="0">
+        <v>-2.8025129373926108</v>
+      </c>
+      <c r="E69" s="0">
         <v>2.1722803778990225</v>
       </c>
-      <c r="C69" s="0">
+      <c r="F69" s="0">
         <v>2.1722803779054418</v>
       </c>
-      <c r="D69" s="0">
+      <c r="G69" s="0">
         <v>2.1722803779055533</v>
-      </c>
-      <c r="E69" s="0">
-        <v>-2.8025129373926108</v>
-      </c>
-      <c r="F69" s="0">
-        <v>-2.8180548538972006</v>
-      </c>
-      <c r="G69" s="0">
-        <v>-2.8217960020049278</v>
       </c>
       <c r="H69" s="0">
         <v>0</v>
@@ -6482,13 +7178,13 @@
         <v>0</v>
       </c>
       <c r="Z69" s="0">
+        <v>-2.8187812324212893</v>
+      </c>
+      <c r="AA69" s="0">
         <v>2.1722803778990225</v>
       </c>
-      <c r="AA69" s="0">
+      <c r="AB69" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB69" s="0">
-        <v>-2.8187812324212893</v>
       </c>
       <c r="AC69" s="0">
         <v>2</v>
@@ -6499,22 +7195,22 @@
         <v>6.7999999999999998</v>
       </c>
       <c r="B70" s="0">
+        <v>-2.8744589995347858</v>
+      </c>
+      <c r="C70" s="0">
+        <v>-2.8695110824469401</v>
+      </c>
+      <c r="D70" s="0">
+        <v>-2.864855118421723</v>
+      </c>
+      <c r="E70" s="0">
         <v>2.2235102815244732</v>
       </c>
-      <c r="C70" s="0">
+      <c r="F70" s="0">
         <v>2.2235102815701842</v>
       </c>
-      <c r="D70" s="0">
+      <c r="G70" s="0">
         <v>2.2235102815703121</v>
-      </c>
-      <c r="E70" s="0">
-        <v>-2.864855118421723</v>
-      </c>
-      <c r="F70" s="0">
-        <v>-2.8695110824469401</v>
-      </c>
-      <c r="G70" s="0">
-        <v>-2.8744589995347858</v>
       </c>
       <c r="H70" s="0">
         <v>0</v>
@@ -6571,13 +7267,13 @@
         <v>0</v>
       </c>
       <c r="Z70" s="0">
+        <v>-2.87001113604674</v>
+      </c>
+      <c r="AA70" s="0">
         <v>2.2235102815244732</v>
       </c>
-      <c r="AA70" s="0">
+      <c r="AB70" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB70" s="0">
-        <v>-2.87001113604674</v>
       </c>
       <c r="AC70" s="0">
         <v>2</v>
@@ -6588,22 +7284,22 @@
         <v>6.9000000000000004</v>
       </c>
       <c r="B71" s="0">
+        <v>-2.9231904375996112</v>
+      </c>
+      <c r="C71" s="0">
+        <v>-2.9196826982675343</v>
+      </c>
+      <c r="D71" s="0">
+        <v>-2.9060629007932395</v>
+      </c>
+      <c r="E71" s="0">
         <v>2.2721501487327509</v>
       </c>
-      <c r="C71" s="0">
+      <c r="F71" s="0">
         <v>2.2721501487328708</v>
       </c>
-      <c r="D71" s="0">
+      <c r="G71" s="0">
         <v>2.272150148742158</v>
-      </c>
-      <c r="E71" s="0">
-        <v>-2.9060629007932395</v>
-      </c>
-      <c r="F71" s="0">
-        <v>-2.9196826982675343</v>
-      </c>
-      <c r="G71" s="0">
-        <v>-2.9231904375996112</v>
       </c>
       <c r="H71" s="0">
         <v>0</v>
@@ -6660,13 +7356,13 @@
         <v>0</v>
       </c>
       <c r="Z71" s="0">
+        <v>-2.9186510032550177</v>
+      </c>
+      <c r="AA71" s="0">
         <v>2.2721501487327509</v>
       </c>
-      <c r="AA71" s="0">
+      <c r="AB71" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB71" s="0">
-        <v>-2.9186510032550177</v>
       </c>
       <c r="AC71" s="0">
         <v>2</v>
@@ -6677,40 +7373,40 @@
         <v>7</v>
       </c>
       <c r="B72" s="0">
+        <v>-3.0000162773167092</v>
+      </c>
+      <c r="C72" s="0">
+        <v>-2.9805162353281416</v>
+      </c>
+      <c r="D72" s="0">
+        <v>-2.9612706418198891</v>
+      </c>
+      <c r="E72" s="0">
         <v>2.3183844888925331</v>
       </c>
-      <c r="C72" s="0">
+      <c r="F72" s="0">
         <v>2.3183844889319505</v>
       </c>
-      <c r="D72" s="0">
+      <c r="G72" s="0">
         <v>2.3183844889319505</v>
       </c>
-      <c r="E72" s="0">
-        <v>-2.9612706418198891</v>
-      </c>
-      <c r="F72" s="0">
-        <v>-2.9805162353281416</v>
-      </c>
-      <c r="G72" s="0">
-        <v>-3.0000162773167092</v>
-      </c>
       <c r="H72" s="0">
         <v>0</v>
       </c>
       <c r="I72" s="0">
+        <v>0</v>
+      </c>
+      <c r="J72" s="0">
+        <v>0</v>
+      </c>
+      <c r="K72" s="0">
+        <v>0</v>
+      </c>
+      <c r="L72" s="0">
         <v>-8.0041547144951902e-14</v>
       </c>
-      <c r="J72" s="0">
+      <c r="M72" s="0">
         <v>8.0041547144951902e-14</v>
-      </c>
-      <c r="K72" s="0">
-        <v>0</v>
-      </c>
-      <c r="L72" s="0">
-        <v>0</v>
-      </c>
-      <c r="M72" s="0">
-        <v>0</v>
       </c>
       <c r="N72" s="0">
         <v>6.5117461236251278e-09</v>
@@ -6749,16 +7445,16 @@
         <v>1.0660885884357571e-06</v>
       </c>
       <c r="Z72" s="0">
+        <v>-2.9648853434147999</v>
+      </c>
+      <c r="AA72" s="0">
         <v>2.3183844888925331</v>
       </c>
-      <c r="AA72" s="0">
-        <v>-2.0000000000000799</v>
-      </c>
       <c r="AB72" s="0">
-        <v>-2.9648853434147999</v>
+        <v>-2</v>
       </c>
       <c r="AC72" s="0">
-        <v>2.0000000000000799</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -6766,28 +7462,28 @@
         <v>7.0999999999999996</v>
       </c>
       <c r="B73" s="0">
+        <v>-3.0153925042115937</v>
+      </c>
+      <c r="C73" s="0">
+        <v>-3.0153925042115937</v>
+      </c>
+      <c r="D73" s="0">
+        <v>-2.9409208232839807</v>
+      </c>
+      <c r="E73" s="0">
         <v>2.3623476757677984</v>
       </c>
-      <c r="C73" s="0">
+      <c r="F73" s="0">
         <v>2.3623476758350406</v>
       </c>
-      <c r="D73" s="0">
+      <c r="G73" s="0">
         <v>2.3623476758351925</v>
       </c>
-      <c r="E73" s="0">
-        <v>-2.9409208232839807</v>
-      </c>
-      <c r="F73" s="0">
-        <v>-3.0153925042115937</v>
-      </c>
-      <c r="G73" s="0">
-        <v>-3.0153925042115937</v>
-      </c>
       <c r="H73" s="0">
-        <v>0</v>
+        <v>-0.0076481237150659255</v>
       </c>
       <c r="I73" s="0">
-        <v>0</v>
+        <v>0.0076481237150659255</v>
       </c>
       <c r="J73" s="0">
         <v>0</v>
@@ -6796,10 +7492,10 @@
         <v>0</v>
       </c>
       <c r="L73" s="0">
-        <v>-0.0076481237150659255</v>
+        <v>0</v>
       </c>
       <c r="M73" s="0">
-        <v>0.0076481237150659255</v>
+        <v>0</v>
       </c>
       <c r="N73" s="0">
         <v>5.905244729163552e-09</v>
@@ -6838,16 +7534,16 @@
         <v>0</v>
       </c>
       <c r="Z73" s="0">
+        <v>-3.0088485302900652</v>
+      </c>
+      <c r="AA73" s="0">
         <v>2.3623476757677984</v>
       </c>
-      <c r="AA73" s="0">
-        <v>-2.0076481237150658</v>
-      </c>
       <c r="AB73" s="0">
-        <v>-3.0088485302900652</v>
+        <v>-2</v>
       </c>
       <c r="AC73" s="0">
-        <v>2.0076481237150658</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -6855,40 +7551,40 @@
         <v>7.1999999999999993</v>
       </c>
       <c r="B74" s="0">
+        <v>-3.0560318864467515</v>
+      </c>
+      <c r="C74" s="0">
+        <v>-3.0560318864467515</v>
+      </c>
+      <c r="D74" s="0">
+        <v>-3.0546882059625573</v>
+      </c>
+      <c r="E74" s="0">
         <v>2.4041336297509313</v>
       </c>
-      <c r="C74" s="0">
+      <c r="F74" s="0">
         <v>2.4041336297509313</v>
       </c>
-      <c r="D74" s="0">
+      <c r="G74" s="0">
         <v>2.404133629822967</v>
       </c>
-      <c r="E74" s="0">
-        <v>-3.0546882059625573</v>
-      </c>
-      <c r="F74" s="0">
-        <v>-3.0560318864467515</v>
-      </c>
-      <c r="G74" s="0">
-        <v>-3.0560318864467515</v>
-      </c>
       <c r="H74" s="0">
+        <v>-0.067479058481168058</v>
+      </c>
+      <c r="I74" s="0">
+        <v>0.067479058481168058</v>
+      </c>
+      <c r="J74" s="0">
+        <v>0</v>
+      </c>
+      <c r="K74" s="0">
         <v>-1.6727277936536954e-14</v>
       </c>
-      <c r="I74" s="0">
+      <c r="L74" s="0">
         <v>1.6727277936536954e-14</v>
       </c>
-      <c r="J74" s="0">
-        <v>0</v>
-      </c>
-      <c r="K74" s="0">
-        <v>0</v>
-      </c>
-      <c r="L74" s="0">
-        <v>-0.067479058481168058</v>
-      </c>
       <c r="M74" s="0">
-        <v>0.067479058481168058</v>
+        <v>0</v>
       </c>
       <c r="N74" s="0">
         <v>4.1742753932471092e-09</v>
@@ -6927,16 +7623,16 @@
         <v>0</v>
       </c>
       <c r="Z74" s="0">
+        <v>-3.0506344842731981</v>
+      </c>
+      <c r="AA74" s="0">
         <v>2.4041336297509313</v>
       </c>
-      <c r="AA74" s="0">
-        <v>-2.067479058481168</v>
-      </c>
       <c r="AB74" s="0">
-        <v>-3.0506344842731981</v>
+        <v>-1.9999999999999833</v>
       </c>
       <c r="AC74" s="0">
-        <v>2.067479058481168</v>
+        <v>1.9999999999999833</v>
       </c>
     </row>
     <row r="75">
@@ -6944,40 +7640,40 @@
         <v>7.2999999999999998</v>
       </c>
       <c r="B75" s="0">
+        <v>-3.1276062579470563</v>
+      </c>
+      <c r="C75" s="0">
+        <v>-3.0767446382845312</v>
+      </c>
+      <c r="D75" s="0">
+        <v>-3.0767446382845312</v>
+      </c>
+      <c r="E75" s="0">
         <v>2.4438020283815916</v>
       </c>
-      <c r="C75" s="0">
+      <c r="F75" s="0">
         <v>2.4438020283815916</v>
       </c>
-      <c r="D75" s="0">
+      <c r="G75" s="0">
         <v>2.4438020284125486</v>
       </c>
-      <c r="E75" s="0">
-        <v>-3.0767446382845312</v>
-      </c>
-      <c r="F75" s="0">
-        <v>-3.0767446382845312</v>
-      </c>
-      <c r="G75" s="0">
-        <v>-3.1276062579470563</v>
-      </c>
       <c r="H75" s="0">
+        <v>-0</v>
+      </c>
+      <c r="I75" s="0">
+        <v>-0.0073320915293203287</v>
+      </c>
+      <c r="J75" s="0">
+        <v>0.0073320915293203287</v>
+      </c>
+      <c r="K75" s="0">
         <v>-7.9559531379784758e-14</v>
       </c>
-      <c r="I75" s="0">
+      <c r="L75" s="0">
         <v>7.9559531379784758e-14</v>
       </c>
-      <c r="J75" s="0">
-        <v>0</v>
-      </c>
-      <c r="K75" s="0">
-        <v>-0.0073320915293203287</v>
-      </c>
-      <c r="L75" s="0">
-        <v>0.0073320915293203287</v>
-      </c>
       <c r="M75" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N75" s="0">
         <v>-2.921029581014367e-09</v>
@@ -7016,16 +7712,16 @@
         <v>0</v>
       </c>
       <c r="Z75" s="0">
+        <v>-3.0903028829038584</v>
+      </c>
+      <c r="AA75" s="0">
         <v>2.4438020283815916</v>
       </c>
-      <c r="AA75" s="0">
-        <v>-2.0073320915293205</v>
-      </c>
       <c r="AB75" s="0">
-        <v>-3.0903028829038584</v>
+        <v>-1.9999999999999205</v>
       </c>
       <c r="AC75" s="0">
-        <v>2.0073320915293205</v>
+        <v>1.9999999999999205</v>
       </c>
     </row>
     <row r="76">
@@ -7033,40 +7729,40 @@
         <v>7.4000000000000004</v>
       </c>
       <c r="B76" s="0">
+        <v>-3.3335963425893</v>
+      </c>
+      <c r="C76" s="0">
+        <v>-3.0780686169294582</v>
+      </c>
+      <c r="D76" s="0">
+        <v>-3.0780686169294582</v>
+      </c>
+      <c r="E76" s="0">
         <v>2.481382016891498</v>
       </c>
-      <c r="C76" s="0">
+      <c r="F76" s="0">
         <v>2.4813820169028231</v>
       </c>
-      <c r="D76" s="0">
+      <c r="G76" s="0">
         <v>2.4813820169035168</v>
       </c>
-      <c r="E76" s="0">
-        <v>-3.0780686169294582</v>
-      </c>
-      <c r="F76" s="0">
-        <v>-3.0780686169294582</v>
-      </c>
-      <c r="G76" s="0">
-        <v>-3.3335963425893</v>
-      </c>
       <c r="H76" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I76" s="0">
-        <v>0</v>
+        <v>-0.035317847805084422</v>
       </c>
       <c r="J76" s="0">
-        <v>0</v>
+        <v>0.035317847805084422</v>
       </c>
       <c r="K76" s="0">
-        <v>-0.035317847805084422</v>
+        <v>0</v>
       </c>
       <c r="L76" s="0">
-        <v>0.035317847805084422</v>
+        <v>0</v>
       </c>
       <c r="M76" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N76" s="0">
         <v>-8.0064492256231079e-10</v>
@@ -7105,16 +7801,16 @@
         <v>0</v>
       </c>
       <c r="Z76" s="0">
+        <v>-3.1278828714137648</v>
+      </c>
+      <c r="AA76" s="0">
         <v>2.481382016891498</v>
       </c>
-      <c r="AA76" s="0">
-        <v>-2.0353178478050844</v>
-      </c>
       <c r="AB76" s="0">
-        <v>-3.1278828714137648</v>
+        <v>-2</v>
       </c>
       <c r="AC76" s="0">
-        <v>2.0353178478050844</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -7122,22 +7818,22 @@
         <v>7.5</v>
       </c>
       <c r="B77" s="0">
+        <v>-3.6142009299396127</v>
+      </c>
+      <c r="C77" s="0">
+        <v>-3.1180092862121103</v>
+      </c>
+      <c r="D77" s="0">
+        <v>-3.0210849644490718</v>
+      </c>
+      <c r="E77" s="0">
         <v>2.5168739514078844</v>
       </c>
-      <c r="C77" s="0">
+      <c r="F77" s="0">
         <v>2.5168739515753442</v>
       </c>
-      <c r="D77" s="0">
+      <c r="G77" s="0">
         <v>2.5168739515754228</v>
-      </c>
-      <c r="E77" s="0">
-        <v>-3.0210849644490718</v>
-      </c>
-      <c r="F77" s="0">
-        <v>-3.1180092862121103</v>
-      </c>
-      <c r="G77" s="0">
-        <v>-3.6142009299396127</v>
       </c>
       <c r="H77" s="0">
         <v>0</v>
@@ -7194,13 +7890,13 @@
         <v>0</v>
       </c>
       <c r="Z77" s="0">
+        <v>-3.1633748059301512</v>
+      </c>
+      <c r="AA77" s="0">
         <v>2.5168739514078844</v>
       </c>
-      <c r="AA77" s="0">
+      <c r="AB77" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB77" s="0">
-        <v>-3.1633748059301512</v>
       </c>
       <c r="AC77" s="0">
         <v>2</v>
@@ -7211,40 +7907,40 @@
         <v>7.5999999999999996</v>
       </c>
       <c r="B78" s="0">
+        <v>-3.2321791723220863</v>
+      </c>
+      <c r="C78" s="0">
+        <v>-3.0234461767500984</v>
+      </c>
+      <c r="D78" s="0">
+        <v>-3.0234461767500984</v>
+      </c>
+      <c r="E78" s="0">
         <v>2.5502494162451566</v>
       </c>
-      <c r="C78" s="0">
+      <c r="F78" s="0">
         <v>2.5502494163984477</v>
       </c>
-      <c r="D78" s="0">
+      <c r="G78" s="0">
         <v>2.5502494163984477</v>
       </c>
-      <c r="E78" s="0">
-        <v>-3.0234461767500984</v>
-      </c>
-      <c r="F78" s="0">
-        <v>-3.0234461767500984</v>
-      </c>
-      <c r="G78" s="0">
-        <v>-3.2321791723220863</v>
-      </c>
       <c r="H78" s="0">
         <v>0</v>
       </c>
       <c r="I78" s="0">
+        <v>-0.013309068486988273</v>
+      </c>
+      <c r="J78" s="0">
+        <v>0.013309068486988273</v>
+      </c>
+      <c r="K78" s="0">
+        <v>0</v>
+      </c>
+      <c r="L78" s="0">
         <v>-6.0026984608420785e-14</v>
       </c>
-      <c r="J78" s="0">
+      <c r="M78" s="0">
         <v>6.0026984608420785e-14</v>
-      </c>
-      <c r="K78" s="0">
-        <v>-0.013309068486988273</v>
-      </c>
-      <c r="L78" s="0">
-        <v>0.013309068486988273</v>
-      </c>
-      <c r="M78" s="0">
-        <v>0</v>
       </c>
       <c r="N78" s="0">
         <v>1.5141968270779834e-09</v>
@@ -7283,16 +7979,16 @@
         <v>3.4318349768885318e-06</v>
       </c>
       <c r="Z78" s="0">
+        <v>-3.1967502707674234</v>
+      </c>
+      <c r="AA78" s="0">
         <v>2.5502494162451566</v>
       </c>
-      <c r="AA78" s="0">
-        <v>-2.0133090684869881</v>
-      </c>
       <c r="AB78" s="0">
-        <v>-3.1967502707674234</v>
+        <v>-2</v>
       </c>
       <c r="AC78" s="0">
-        <v>2.0133090684869881</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -7300,49 +7996,49 @@
         <v>7.6999999999999993</v>
       </c>
       <c r="B79" s="0">
+        <v>-2.9120201044786054</v>
+      </c>
+      <c r="C79" s="0">
+        <v>-3.2740196030790378</v>
+      </c>
+      <c r="D79" s="0">
+        <v>-3.1116168116770297</v>
+      </c>
+      <c r="E79" s="0">
         <v>2.5814495174497245</v>
       </c>
-      <c r="C79" s="0">
+      <c r="F79" s="0">
         <v>2.5814495174497245</v>
       </c>
-      <c r="D79" s="0">
+      <c r="G79" s="0">
         <v>2.5814495175933048</v>
       </c>
-      <c r="E79" s="0">
-        <v>-2.9120201044786054</v>
-      </c>
-      <c r="F79" s="0">
-        <v>-3.1116168116770297</v>
-      </c>
-      <c r="G79" s="0">
-        <v>-3.2740196030790378</v>
-      </c>
       <c r="H79" s="0">
+        <v>-0</v>
+      </c>
+      <c r="I79" s="0">
+        <v>0</v>
+      </c>
+      <c r="J79" s="0">
+        <v>0</v>
+      </c>
+      <c r="K79" s="0">
         <v>-9.0024151451137695e-14</v>
       </c>
-      <c r="I79" s="0">
+      <c r="L79" s="0">
         <v>9.0024151451137695e-14</v>
       </c>
-      <c r="J79" s="0">
-        <v>0</v>
-      </c>
-      <c r="K79" s="0">
-        <v>-0</v>
-      </c>
-      <c r="L79" s="0">
-        <v>0</v>
-      </c>
       <c r="M79" s="0">
         <v>0</v>
       </c>
       <c r="N79" s="0">
+        <v>-1.1319239655474809e-08</v>
+      </c>
+      <c r="O79" s="0">
         <v>1.1641532182693481e-09</v>
       </c>
-      <c r="O79" s="0">
+      <c r="P79" s="0">
         <v>3.2297373051245018e-09</v>
-      </c>
-      <c r="P79" s="0">
-        <v>-1.1319239655474809e-08</v>
       </c>
       <c r="Q79" s="0">
         <v>11069738.469702408</v>
@@ -7372,16 +8068,16 @@
         <v>0</v>
       </c>
       <c r="Z79" s="0">
+        <v>-3.2279503719719913</v>
+      </c>
+      <c r="AA79" s="0">
         <v>2.5814495174497245</v>
       </c>
-      <c r="AA79" s="0">
-        <v>-2.0000000000000902</v>
-      </c>
       <c r="AB79" s="0">
-        <v>-3.2279503719719913</v>
+        <v>-1.9999999999999101</v>
       </c>
       <c r="AC79" s="0">
-        <v>2.0000000000000902</v>
+        <v>1.9999999999999101</v>
       </c>
     </row>
     <row r="80">
@@ -7389,40 +8085,40 @@
         <v>7.7999999999999998</v>
       </c>
       <c r="B80" s="0">
+        <v>-2.8943011707036939</v>
+      </c>
+      <c r="C80" s="0">
+        <v>-3.3013803856780313</v>
+      </c>
+      <c r="D80" s="0">
+        <v>-2.9862718084899567</v>
+      </c>
+      <c r="E80" s="0">
         <v>2.6103812260676249</v>
       </c>
-      <c r="C80" s="0">
+      <c r="F80" s="0">
         <v>2.6103812260679811</v>
       </c>
-      <c r="D80" s="0">
+      <c r="G80" s="0">
         <v>2.6103812262979549</v>
       </c>
-      <c r="E80" s="0">
-        <v>-2.8943011707036939</v>
-      </c>
-      <c r="F80" s="0">
-        <v>-2.9862718084899567</v>
-      </c>
-      <c r="G80" s="0">
-        <v>-3.3013803856780313</v>
-      </c>
       <c r="H80" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I80" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J80" s="0">
         <v>0</v>
       </c>
       <c r="K80" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L80" s="0">
         <v>0</v>
       </c>
       <c r="M80" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N80" s="0">
         <v>-1.2652252298386702e-08</v>
@@ -7461,13 +8157,13 @@
         <v>0</v>
       </c>
       <c r="Z80" s="0">
+        <v>-3.2568820805898917</v>
+      </c>
+      <c r="AA80" s="0">
         <v>2.6103812260676249</v>
       </c>
-      <c r="AA80" s="0">
+      <c r="AB80" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB80" s="0">
-        <v>-3.2568820805898917</v>
       </c>
       <c r="AC80" s="0">
         <v>2</v>
@@ -7478,28 +8174,28 @@
         <v>7.9000000000000004</v>
       </c>
       <c r="B81" s="0">
+        <v>-2.9781343964942435</v>
+      </c>
+      <c r="C81" s="0">
+        <v>-3.3198298477838337</v>
+      </c>
+      <c r="D81" s="0">
+        <v>-2.7896258938603413</v>
+      </c>
+      <c r="E81" s="0">
         <v>2.6369112522369953</v>
       </c>
-      <c r="C81" s="0">
+      <c r="F81" s="0">
         <v>2.6369112524758984</v>
       </c>
-      <c r="D81" s="0">
+      <c r="G81" s="0">
         <v>2.636911252476001</v>
       </c>
-      <c r="E81" s="0">
-        <v>-2.7896258938603413</v>
-      </c>
-      <c r="F81" s="0">
-        <v>-2.9781343964942435</v>
-      </c>
-      <c r="G81" s="0">
-        <v>-3.3198298477838337</v>
-      </c>
       <c r="H81" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I81" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J81" s="0">
         <v>0</v>
@@ -7508,10 +8204,10 @@
         <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M81" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N81" s="0">
         <v>-7.4714982956638228e-09</v>
@@ -7550,13 +8246,13 @@
         <v>0</v>
       </c>
       <c r="Z81" s="0">
+        <v>-3.2834121067592621</v>
+      </c>
+      <c r="AA81" s="0">
         <v>2.6369112522369953</v>
       </c>
-      <c r="AA81" s="0">
+      <c r="AB81" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB81" s="0">
-        <v>-3.2834121067592621</v>
       </c>
       <c r="AC81" s="0">
         <v>2</v>
@@ -7567,28 +8263,28 @@
         <v>8</v>
       </c>
       <c r="B82" s="0">
+        <v>-3.0419160298916319</v>
+      </c>
+      <c r="C82" s="0">
+        <v>-3.3107261062887199</v>
+      </c>
+      <c r="D82" s="0">
+        <v>-2.969043210919335</v>
+      </c>
+      <c r="E82" s="0">
         <v>2.660856504677112</v>
       </c>
-      <c r="C82" s="0">
+      <c r="F82" s="0">
         <v>2.6608565055932472</v>
       </c>
-      <c r="D82" s="0">
+      <c r="G82" s="0">
         <v>2.6608565055935363</v>
       </c>
-      <c r="E82" s="0">
-        <v>-2.969043210919335</v>
-      </c>
-      <c r="F82" s="0">
-        <v>-3.0419160298916319</v>
-      </c>
-      <c r="G82" s="0">
-        <v>-3.3107261062887199</v>
-      </c>
       <c r="H82" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I82" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J82" s="0">
         <v>0</v>
@@ -7597,10 +8293,10 @@
         <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M82" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N82" s="0">
         <v>-5.0045311510091283e-09</v>
@@ -7639,13 +8335,13 @@
         <v>0</v>
       </c>
       <c r="Z82" s="0">
+        <v>-3.3073573591993788</v>
+      </c>
+      <c r="AA82" s="0">
         <v>2.660856504677112</v>
       </c>
-      <c r="AA82" s="0">
+      <c r="AB82" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB82" s="0">
-        <v>-3.3073573591993788</v>
       </c>
       <c r="AC82" s="0">
         <v>2</v>
@@ -7656,49 +8352,49 @@
         <v>8.0999999999999996</v>
       </c>
       <c r="B83" s="0">
+        <v>-2.9188899396003269</v>
+      </c>
+      <c r="C83" s="0">
+        <v>-2.9188899396003269</v>
+      </c>
+      <c r="D83" s="0">
+        <v>-3.1405689042654328</v>
+      </c>
+      <c r="E83" s="0">
         <v>2.6819694930747775</v>
       </c>
-      <c r="C83" s="0">
+      <c r="F83" s="0">
         <v>2.6819694936673026</v>
       </c>
-      <c r="D83" s="0">
+      <c r="G83" s="0">
         <v>2.6819694936673026</v>
       </c>
-      <c r="E83" s="0">
-        <v>-2.9188899396003269</v>
-      </c>
-      <c r="F83" s="0">
-        <v>-2.9188899396003269</v>
-      </c>
-      <c r="G83" s="0">
-        <v>-3.1405689042654328</v>
-      </c>
       <c r="H83" s="0">
-        <v>0</v>
+        <v>0.19448171564144848</v>
       </c>
       <c r="I83" s="0">
+        <v>-0.19448171564144848</v>
+      </c>
+      <c r="J83" s="0">
+        <v>-0</v>
+      </c>
+      <c r="K83" s="0">
+        <v>0</v>
+      </c>
+      <c r="L83" s="0">
         <v>-1.2358951646977497e-13</v>
       </c>
-      <c r="J83" s="0">
+      <c r="M83" s="0">
         <v>1.2358951646977497e-13</v>
       </c>
-      <c r="K83" s="0">
-        <v>0.19448171564144848</v>
-      </c>
-      <c r="L83" s="0">
-        <v>-0.19448171564144848</v>
-      </c>
-      <c r="M83" s="0">
-        <v>-0</v>
-      </c>
       <c r="N83" s="0">
-        <v>-2.6925519965336479e-09</v>
+        <v>-3.7054702223729758e-09</v>
       </c>
       <c r="O83" s="0">
         <v>-3.7054702223729758e-09</v>
       </c>
       <c r="P83" s="0">
-        <v>-3.7054702223729758e-09</v>
+        <v>-2.6925519965336479e-09</v>
       </c>
       <c r="Q83" s="0">
         <v>20817641.061923325</v>
@@ -7710,13 +8406,13 @@
         <v>20817641.139426224</v>
       </c>
       <c r="T83" s="0">
-        <v>0</v>
+        <v>-1.0188118648785039e-08</v>
       </c>
       <c r="U83" s="0">
-        <v>-1.0188118648785039e-08</v>
+        <v>1.0188118648785039e-08</v>
       </c>
       <c r="V83" s="0">
-        <v>1.0188118648785039e-08</v>
+        <v>0</v>
       </c>
       <c r="W83" s="0">
         <v>0</v>
@@ -7728,16 +8424,16 @@
         <v>1.6165644324206977e-05</v>
       </c>
       <c r="Z83" s="0">
+        <v>-3.3284703475970443</v>
+      </c>
+      <c r="AA83" s="0">
         <v>2.6819694930747775</v>
       </c>
-      <c r="AA83" s="0">
-        <v>-2.1944817156414484</v>
-      </c>
       <c r="AB83" s="0">
-        <v>-3.3284703475970443</v>
+        <v>-2</v>
       </c>
       <c r="AC83" s="0">
-        <v>2.1944817156414484</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -7745,40 +8441,40 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B84" s="0">
+        <v>-3.1081767884561886</v>
+      </c>
+      <c r="C84" s="0">
+        <v>-2.7683451147982638</v>
+      </c>
+      <c r="D84" s="0">
+        <v>-2.7683451147982638</v>
+      </c>
+      <c r="E84" s="0">
         <v>2.6999157698867795</v>
       </c>
-      <c r="C84" s="0">
+      <c r="F84" s="0">
         <v>2.699915769957542</v>
       </c>
-      <c r="D84" s="0">
+      <c r="G84" s="0">
         <v>2.6999157699579834</v>
       </c>
-      <c r="E84" s="0">
-        <v>-2.7683451147982638</v>
-      </c>
-      <c r="F84" s="0">
-        <v>-2.7683451147982638</v>
-      </c>
-      <c r="G84" s="0">
-        <v>-3.1081767884561886</v>
-      </c>
       <c r="H84" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I84" s="0">
-        <v>0</v>
+        <v>0.23224652955926858</v>
       </c>
       <c r="J84" s="0">
-        <v>0</v>
+        <v>-0.23224652955926858</v>
       </c>
       <c r="K84" s="0">
-        <v>0.23224652955926858</v>
+        <v>0</v>
       </c>
       <c r="L84" s="0">
-        <v>-0.23224652955926858</v>
+        <v>0</v>
       </c>
       <c r="M84" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N84" s="0">
         <v>-3.3003057232878387e-09</v>
@@ -7817,16 +8513,16 @@
         <v>0</v>
       </c>
       <c r="Z84" s="0">
+        <v>-3.3464166244090463</v>
+      </c>
+      <c r="AA84" s="0">
         <v>2.6999157698867795</v>
       </c>
-      <c r="AA84" s="0">
-        <v>-2.2322465295592684</v>
-      </c>
       <c r="AB84" s="0">
-        <v>-3.3464166244090463</v>
+        <v>-2</v>
       </c>
       <c r="AC84" s="0">
-        <v>2.2322465295592684</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -7834,46 +8530,46 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="B85" s="0">
+        <v>-2.7462267516164682</v>
+      </c>
+      <c r="C85" s="0">
+        <v>-3.2616820625215688</v>
+      </c>
+      <c r="D85" s="0">
+        <v>-2.7254384090985306</v>
+      </c>
+      <c r="E85" s="0">
         <v>2.7142381398651025</v>
       </c>
-      <c r="C85" s="0">
+      <c r="F85" s="0">
         <v>2.7142381398651025</v>
       </c>
-      <c r="D85" s="0">
+      <c r="G85" s="0">
         <v>2.7142381406864131</v>
       </c>
-      <c r="E85" s="0">
-        <v>-2.7254384090985306</v>
-      </c>
-      <c r="F85" s="0">
-        <v>-2.7462267516164682</v>
-      </c>
-      <c r="G85" s="0">
-        <v>-3.2616820625215688</v>
-      </c>
       <c r="H85" s="0">
+        <v>-0</v>
+      </c>
+      <c r="I85" s="0">
+        <v>-0</v>
+      </c>
+      <c r="J85" s="0">
+        <v>0</v>
+      </c>
+      <c r="K85" s="0">
         <v>-2.5480199599845424e-13</v>
       </c>
-      <c r="I85" s="0">
+      <c r="L85" s="0">
         <v>2.5480199599845424e-13</v>
       </c>
-      <c r="J85" s="0">
-        <v>0</v>
-      </c>
-      <c r="K85" s="0">
-        <v>0</v>
-      </c>
-      <c r="L85" s="0">
-        <v>-0</v>
-      </c>
       <c r="M85" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N85" s="0">
+        <v>-3.2079405819998738e-08</v>
+      </c>
+      <c r="O85" s="0">
         <v>-1.2579872524253112e-09</v>
-      </c>
-      <c r="O85" s="0">
-        <v>-3.2079405819998738e-08</v>
       </c>
       <c r="P85" s="0">
         <v>3.6555485948231538e-08</v>
@@ -7906,16 +8602,16 @@
         <v>0</v>
       </c>
       <c r="Z85" s="0">
+        <v>-3.3607389943873693</v>
+      </c>
+      <c r="AA85" s="0">
         <v>2.7142381398651025</v>
       </c>
-      <c r="AA85" s="0">
-        <v>-2.0000000000002549</v>
-      </c>
       <c r="AB85" s="0">
-        <v>-3.3607389943873693</v>
+        <v>-1.9999999999997451</v>
       </c>
       <c r="AC85" s="0">
-        <v>2.0000000000002549</v>
+        <v>1.9999999999997451</v>
       </c>
     </row>
     <row r="86">
@@ -7923,46 +8619,46 @@
         <v>8.4000000000000004</v>
       </c>
       <c r="B86" s="0">
+        <v>-2.8213201681736448</v>
+      </c>
+      <c r="C86" s="0">
+        <v>-3.1042255597324142</v>
+      </c>
+      <c r="D86" s="0">
+        <v>-2.7441040202580371</v>
+      </c>
+      <c r="E86" s="0">
         <v>2.7242974527227171</v>
       </c>
-      <c r="C86" s="0">
+      <c r="F86" s="0">
         <v>2.7242974527227171</v>
       </c>
-      <c r="D86" s="0">
+      <c r="G86" s="0">
         <v>2.7242974539357139</v>
       </c>
-      <c r="E86" s="0">
-        <v>-2.7441040202580371</v>
-      </c>
-      <c r="F86" s="0">
-        <v>-2.8213201681736448</v>
-      </c>
-      <c r="G86" s="0">
-        <v>-3.1042255597324142</v>
-      </c>
       <c r="H86" s="0">
+        <v>-0</v>
+      </c>
+      <c r="I86" s="0">
+        <v>0</v>
+      </c>
+      <c r="J86" s="0">
+        <v>0</v>
+      </c>
+      <c r="K86" s="0">
         <v>-7.4991713668824162e-14</v>
       </c>
-      <c r="I86" s="0">
+      <c r="L86" s="0">
         <v>7.4991713668824162e-14</v>
       </c>
-      <c r="J86" s="0">
-        <v>0</v>
-      </c>
-      <c r="K86" s="0">
-        <v>0</v>
-      </c>
-      <c r="L86" s="0">
-        <v>-0</v>
-      </c>
       <c r="M86" s="0">
         <v>0</v>
       </c>
       <c r="N86" s="0">
+        <v>-2.0013127023571338e-08</v>
+      </c>
+      <c r="O86" s="0">
         <v>3.3832656438116752e-09</v>
-      </c>
-      <c r="O86" s="0">
-        <v>-2.0013127023571338e-08</v>
       </c>
       <c r="P86" s="0">
         <v>3.2510131378795295e-08</v>
@@ -7995,16 +8691,16 @@
         <v>0</v>
       </c>
       <c r="Z86" s="0">
+        <v>-3.3707983072449839</v>
+      </c>
+      <c r="AA86" s="0">
         <v>2.7242974527227171</v>
       </c>
-      <c r="AA86" s="0">
-        <v>-2.0000000000000751</v>
-      </c>
       <c r="AB86" s="0">
-        <v>-3.3707983072449839</v>
+        <v>-1.9999999999999249</v>
       </c>
       <c r="AC86" s="0">
-        <v>2.0000000000000751</v>
+        <v>1.9999999999999249</v>
       </c>
     </row>
     <row r="87">
@@ -8012,22 +8708,22 @@
         <v>8.5</v>
       </c>
       <c r="B87" s="0">
+        <v>-3.5252965835689629</v>
+      </c>
+      <c r="C87" s="0">
+        <v>-2.9912550997384435</v>
+      </c>
+      <c r="D87" s="0">
+        <v>-2.5803452347004936</v>
+      </c>
+      <c r="E87" s="0">
         <v>2.7291689198873845</v>
       </c>
-      <c r="C87" s="0">
+      <c r="F87" s="0">
         <v>2.7291689220486277</v>
       </c>
-      <c r="D87" s="0">
+      <c r="G87" s="0">
         <v>2.7291689220488791</v>
-      </c>
-      <c r="E87" s="0">
-        <v>-2.5803452347004936</v>
-      </c>
-      <c r="F87" s="0">
-        <v>-2.9912550997384435</v>
-      </c>
-      <c r="G87" s="0">
-        <v>-3.5252965835689629</v>
       </c>
       <c r="H87" s="0">
         <v>0</v>
@@ -8084,13 +8780,13 @@
         <v>0</v>
       </c>
       <c r="Z87" s="0">
+        <v>-3.3756697744096513</v>
+      </c>
+      <c r="AA87" s="0">
         <v>2.7291689198873845</v>
       </c>
-      <c r="AA87" s="0">
+      <c r="AB87" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB87" s="0">
-        <v>-3.3756697744096513</v>
       </c>
       <c r="AC87" s="0">
         <v>2</v>
@@ -8101,28 +8797,28 @@
         <v>8.5999999999999996</v>
       </c>
       <c r="B88" s="0">
+        <v>-2.7440799267746159</v>
+      </c>
+      <c r="C88" s="0">
+        <v>-3.2258573346214838</v>
+      </c>
+      <c r="D88" s="0">
+        <v>-2.675780821287538</v>
+      </c>
+      <c r="E88" s="0">
         <v>2.7274461650195452</v>
       </c>
-      <c r="C88" s="0">
+      <c r="F88" s="0">
         <v>2.7274461650235646</v>
       </c>
-      <c r="D88" s="0">
+      <c r="G88" s="0">
         <v>2.7274461652247295</v>
       </c>
-      <c r="E88" s="0">
-        <v>-2.675780821287538</v>
-      </c>
-      <c r="F88" s="0">
-        <v>-2.7440799267746159</v>
-      </c>
-      <c r="G88" s="0">
-        <v>-3.2258573346214838</v>
-      </c>
       <c r="H88" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I88" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J88" s="0">
         <v>0</v>
@@ -8131,10 +8827,10 @@
         <v>0</v>
       </c>
       <c r="L88" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M88" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N88" s="0">
         <v>-3.2515053259242822e-08</v>
@@ -8173,13 +8869,13 @@
         <v>0</v>
       </c>
       <c r="Z88" s="0">
+        <v>-3.373947019541812</v>
+      </c>
+      <c r="AA88" s="0">
         <v>2.7274461650195452</v>
       </c>
-      <c r="AA88" s="0">
+      <c r="AB88" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB88" s="0">
-        <v>-3.373947019541812</v>
       </c>
       <c r="AC88" s="0">
         <v>2</v>
@@ -8190,49 +8886,49 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="B89" s="0">
+        <v>-2.4842282543972698</v>
+      </c>
+      <c r="C89" s="0">
+        <v>-2.9732058196873887</v>
+      </c>
+      <c r="D89" s="0">
+        <v>-2.9052403782865746</v>
+      </c>
+      <c r="E89" s="0">
         <v>2.7168301655071807</v>
       </c>
-      <c r="C89" s="0">
+      <c r="F89" s="0">
         <v>2.7168301725457753</v>
       </c>
-      <c r="D89" s="0">
+      <c r="G89" s="0">
         <v>2.7168301725457753</v>
       </c>
-      <c r="E89" s="0">
-        <v>-2.4842282543972698</v>
-      </c>
-      <c r="F89" s="0">
-        <v>-2.9052403782865746</v>
-      </c>
-      <c r="G89" s="0">
-        <v>-2.9732058196873887</v>
-      </c>
       <c r="H89" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I89" s="0">
+        <v>-0</v>
+      </c>
+      <c r="J89" s="0">
+        <v>0</v>
+      </c>
+      <c r="K89" s="0">
+        <v>0</v>
+      </c>
+      <c r="L89" s="0">
         <v>-1.2680766681334439e-13</v>
       </c>
-      <c r="J89" s="0">
+      <c r="M89" s="0">
         <v>1.2680766681334439e-13</v>
       </c>
-      <c r="K89" s="0">
-        <v>-0</v>
-      </c>
-      <c r="L89" s="0">
-        <v>0</v>
-      </c>
-      <c r="M89" s="0">
-        <v>-0</v>
-      </c>
       <c r="N89" s="0">
+        <v>-1.6640080551938752e-07</v>
+      </c>
+      <c r="O89" s="0">
         <v>-7.7064891096530208e-09</v>
       </c>
-      <c r="O89" s="0">
+      <c r="P89" s="0">
         <v>1.181183716549311e-08</v>
-      </c>
-      <c r="P89" s="0">
-        <v>-1.6640080551938752e-07</v>
       </c>
       <c r="Q89" s="0">
         <v>25915385.317737058</v>
@@ -8262,16 +8958,16 @@
         <v>2.0648241444490739e-05</v>
       </c>
       <c r="Z89" s="0">
+        <v>-3.3633310200294475</v>
+      </c>
+      <c r="AA89" s="0">
         <v>2.7168301655071807</v>
       </c>
-      <c r="AA89" s="0">
-        <v>-2.000000000000127</v>
-      </c>
       <c r="AB89" s="0">
-        <v>-3.3633310200294475</v>
+        <v>-2</v>
       </c>
       <c r="AC89" s="0">
-        <v>2.000000000000127</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -8279,37 +8975,37 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="B90" s="0">
+        <v>-2.4804913712961594</v>
+      </c>
+      <c r="C90" s="0">
+        <v>-2.8676494474898271</v>
+      </c>
+      <c r="D90" s="0">
+        <v>-2.8800041075413989</v>
+      </c>
+      <c r="E90" s="0">
         <v>2.6931288722217088</v>
       </c>
-      <c r="C90" s="0">
+      <c r="F90" s="0">
         <v>2.6931288722235611</v>
       </c>
-      <c r="D90" s="0">
+      <c r="G90" s="0">
         <v>2.6931288848239952</v>
       </c>
-      <c r="E90" s="0">
-        <v>-2.4804913712961594</v>
-      </c>
-      <c r="F90" s="0">
-        <v>-2.8676494474898271</v>
-      </c>
-      <c r="G90" s="0">
-        <v>-2.8800041075413989</v>
-      </c>
       <c r="H90" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I90" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J90" s="0">
         <v>0</v>
       </c>
       <c r="K90" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L90" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M90" s="0">
         <v>0</v>
@@ -8351,13 +9047,13 @@
         <v>0</v>
       </c>
       <c r="Z90" s="0">
+        <v>-3.3396297267439756</v>
+      </c>
+      <c r="AA90" s="0">
         <v>2.6931288722217088</v>
       </c>
-      <c r="AA90" s="0">
+      <c r="AB90" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB90" s="0">
-        <v>-3.3396297267439756</v>
       </c>
       <c r="AC90" s="0">
         <v>2</v>
@@ -8368,40 +9064,40 @@
         <v>8.9000000000000004</v>
       </c>
       <c r="B91" s="0">
+        <v>-3.0172704517238151</v>
+      </c>
+      <c r="C91" s="0">
+        <v>-2.617298063643684</v>
+      </c>
+      <c r="D91" s="0">
+        <v>-2.617298063643684</v>
+      </c>
+      <c r="E91" s="0">
         <v>2.647187183419538</v>
       </c>
-      <c r="C91" s="0">
+      <c r="F91" s="0">
         <v>2.6471871839290491</v>
       </c>
-      <c r="D91" s="0">
+      <c r="G91" s="0">
         <v>2.6471871839822922</v>
       </c>
-      <c r="E91" s="0">
-        <v>-2.617298063643684</v>
-      </c>
-      <c r="F91" s="0">
-        <v>-2.617298063643684</v>
-      </c>
-      <c r="G91" s="0">
-        <v>-3.0172704517238151</v>
-      </c>
       <c r="H91" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I91" s="0">
-        <v>0</v>
+        <v>-0.24545632617517626</v>
       </c>
       <c r="J91" s="0">
-        <v>0</v>
+        <v>0.24545632617517626</v>
       </c>
       <c r="K91" s="0">
-        <v>-0.24545632617517626</v>
+        <v>0</v>
       </c>
       <c r="L91" s="0">
-        <v>0.24545632617517626</v>
+        <v>0</v>
       </c>
       <c r="M91" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N91" s="0">
         <v>-5.8427201463770332e-09</v>
@@ -8440,16 +9136,16 @@
         <v>0</v>
       </c>
       <c r="Z91" s="0">
+        <v>-3.2936880379418048</v>
+      </c>
+      <c r="AA91" s="0">
         <v>2.647187183419538</v>
       </c>
-      <c r="AA91" s="0">
-        <v>-2.2454563261751761</v>
-      </c>
       <c r="AB91" s="0">
-        <v>-3.2936880379418048</v>
+        <v>-2</v>
       </c>
       <c r="AC91" s="0">
-        <v>2.2454563261751761</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -8457,37 +9153,37 @@
         <v>9</v>
       </c>
       <c r="B92" s="0">
+        <v>-2.4518120140254771</v>
+      </c>
+      <c r="C92" s="0">
+        <v>-2.7110766326382518</v>
+      </c>
+      <c r="D92" s="0">
+        <v>-3.0019578161369651</v>
+      </c>
+      <c r="E92" s="0">
         <v>2.5503677268770737</v>
       </c>
-      <c r="C92" s="0">
+      <c r="F92" s="0">
         <v>2.55036772688223</v>
       </c>
-      <c r="D92" s="0">
+      <c r="G92" s="0">
         <v>2.5503677415636834</v>
       </c>
-      <c r="E92" s="0">
-        <v>-2.4518120140254771</v>
-      </c>
-      <c r="F92" s="0">
-        <v>-2.7110766326382518</v>
-      </c>
-      <c r="G92" s="0">
-        <v>-3.0019578161369651</v>
-      </c>
       <c r="H92" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I92" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J92" s="0">
         <v>0</v>
       </c>
       <c r="K92" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L92" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M92" s="0">
         <v>0</v>
@@ -8529,13 +9225,13 @@
         <v>0</v>
       </c>
       <c r="Z92" s="0">
+        <v>-3.1968685813993405</v>
+      </c>
+      <c r="AA92" s="0">
         <v>2.5503677268770737</v>
       </c>
-      <c r="AA92" s="0">
+      <c r="AB92" s="0">
         <v>-2</v>
-      </c>
-      <c r="AB92" s="0">
-        <v>-3.1968685813993405</v>
       </c>
       <c r="AC92" s="0">
         <v>2</v>
@@ -8546,22 +9242,22 @@
         <v>9.0999999999999996</v>
       </c>
       <c r="B93" s="0">
-        <v>1.9455516272616304</v>
+        <v>1.9455534128708272</v>
       </c>
       <c r="C93" s="0">
         <v>1.9455534127978424</v>
       </c>
       <c r="D93" s="0">
-        <v>1.9455534128708272</v>
+        <v>1.9455516272616304</v>
       </c>
       <c r="E93" s="0">
-        <v>-1.8809483247293137</v>
+        <v>-2.5877181650857044</v>
       </c>
       <c r="F93" s="0">
         <v>-2.2163196744224787</v>
       </c>
       <c r="G93" s="0">
-        <v>-2.5877181650857044</v>
+        <v>-1.8809483247293137</v>
       </c>
       <c r="H93" s="0">
         <v>-0</v>
@@ -8573,13 +9269,13 @@
         <v>-0</v>
       </c>
       <c r="K93" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L93" s="0">
         <v>0</v>
       </c>
       <c r="M93" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N93" s="0">
         <v>-203673.32027969716</v>
@@ -8618,13 +9314,13 @@
         <v>0</v>
       </c>
       <c r="Z93" s="0">
-        <v>1.9455516272616304</v>
+        <v>1.9455534128708272</v>
       </c>
       <c r="AA93" s="0">
+        <v>-2.592054267393094</v>
+      </c>
+      <c r="AB93" s="0">
         <v>-2.5</v>
-      </c>
-      <c r="AB93" s="0">
-        <v>-2.5920524817838975</v>
       </c>
       <c r="AC93" s="0">
         <v>2.5</v>
@@ -8635,22 +9331,22 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="B94" s="0">
-        <v>2.5697609709440297</v>
+        <v>2.5697609729212672</v>
       </c>
       <c r="C94" s="0">
         <v>2.5697609709809472</v>
       </c>
       <c r="D94" s="0">
-        <v>2.5697609729212672</v>
+        <v>2.5697609709440297</v>
       </c>
       <c r="E94" s="0">
         <v>-2.351616496989589</v>
       </c>
       <c r="F94" s="0">
+        <v>-2.9612786811956822</v>
+      </c>
+      <c r="G94" s="0">
         <v>-2.4774175246303298</v>
-      </c>
-      <c r="G94" s="0">
-        <v>-2.9612786811956822</v>
       </c>
       <c r="H94" s="0">
         <v>-0</v>
@@ -8665,10 +9361,10 @@
         <v>-0</v>
       </c>
       <c r="L94" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M94" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N94" s="0">
         <v>-10285897.991213834</v>
@@ -8707,13 +9403,13 @@
         <v>0</v>
       </c>
       <c r="Z94" s="0">
-        <v>2.5697609709440297</v>
+        <v>2.5697609729212672</v>
       </c>
       <c r="AA94" s="0">
+        <v>-3.2162618274435339</v>
+      </c>
+      <c r="AB94" s="0">
         <v>-2.5</v>
-      </c>
-      <c r="AB94" s="0">
-        <v>-3.2162618254662965</v>
       </c>
       <c r="AC94" s="0">
         <v>2.5</v>
@@ -8724,31 +9420,31 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="B95" s="0">
-        <v>2.6704400272579978</v>
+        <v>2.6704400377403026</v>
       </c>
       <c r="C95" s="0">
         <v>2.6704400377403026</v>
       </c>
       <c r="D95" s="0">
-        <v>2.6704400377403026</v>
+        <v>2.6704400272579978</v>
       </c>
       <c r="E95" s="0">
         <v>-2.3947248861837687</v>
       </c>
       <c r="F95" s="0">
+        <v>-2.8153762304100356</v>
+      </c>
+      <c r="G95" s="0">
         <v>-2.4602382788638968</v>
       </c>
-      <c r="G95" s="0">
-        <v>-2.8153762304100356</v>
-      </c>
       <c r="H95" s="0">
+        <v>1.6944786729217149e-12</v>
+      </c>
+      <c r="I95" s="0">
+        <v>-1.6944786729217149e-12</v>
+      </c>
+      <c r="J95" s="0">
         <v>-0</v>
-      </c>
-      <c r="I95" s="0">
-        <v>1.6944786729217149e-12</v>
-      </c>
-      <c r="J95" s="0">
-        <v>-1.6944786729217149e-12</v>
       </c>
       <c r="K95" s="0">
         <v>-0</v>
@@ -8760,28 +9456,28 @@
         <v>0</v>
       </c>
       <c r="N95" s="0">
+        <v>-19362903.61797262</v>
+      </c>
+      <c r="O95" s="0">
+        <v>-19362903.61797262</v>
+      </c>
+      <c r="P95" s="0">
+        <v>-19362902.342688009</v>
+      </c>
+      <c r="Q95" s="0">
+        <v>-2.9200345002110366e-07</v>
+      </c>
+      <c r="R95" s="0">
         <v>2.077468694616719e-08</v>
       </c>
-      <c r="O95" s="0">
+      <c r="S95" s="0">
         <v>1.9347200616614389e-07</v>
       </c>
-      <c r="P95" s="0">
-        <v>-2.9200345002110366e-07</v>
-      </c>
-      <c r="Q95" s="0">
-        <v>-19362902.342688009</v>
-      </c>
-      <c r="R95" s="0">
-        <v>-19362903.61797262</v>
-      </c>
-      <c r="S95" s="0">
-        <v>-19362903.61797262</v>
-      </c>
       <c r="T95" s="0">
-        <v>0</v>
+        <v>-0.000206151480997665</v>
       </c>
       <c r="U95" s="0">
-        <v>0</v>
+        <v>0.000206151480997665</v>
       </c>
       <c r="V95" s="0">
         <v>0</v>
@@ -8790,22 +9486,22 @@
         <v>0</v>
       </c>
       <c r="X95" s="0">
-        <v>-0.000206151480997665</v>
+        <v>0</v>
       </c>
       <c r="Y95" s="0">
-        <v>0.000206151480997665</v>
+        <v>0</v>
       </c>
       <c r="Z95" s="0">
-        <v>2.6704400272579978</v>
+        <v>2.6704400377403026</v>
       </c>
       <c r="AA95" s="0">
-        <v>-3.0000000000016946</v>
+        <v>-3.3169408922625694</v>
       </c>
       <c r="AB95" s="0">
-        <v>-3.3169408817802646</v>
+        <v>-2.4999999999983054</v>
       </c>
       <c r="AC95" s="0">
-        <v>3.0000000000016946</v>
+        <v>2.4999999999983054</v>
       </c>
     </row>
     <row r="96">
@@ -8813,64 +9509,64 @@
         <v>9.4000000000000004</v>
       </c>
       <c r="B96" s="0">
-        <v>2.7072081519319631</v>
+        <v>2.7072081594808739</v>
       </c>
       <c r="C96" s="0">
         <v>2.7072081594808739</v>
       </c>
       <c r="D96" s="0">
-        <v>2.7072081594808739</v>
+        <v>2.7072081519319631</v>
       </c>
       <c r="E96" s="0">
         <v>-2.2605647044006543</v>
       </c>
       <c r="F96" s="0">
+        <v>-2.9230859267942915</v>
+      </c>
+      <c r="G96" s="0">
         <v>-2.586072337642475</v>
       </c>
-      <c r="G96" s="0">
-        <v>-2.9230859267942915</v>
-      </c>
       <c r="H96" s="0">
+        <v>2.6002683546036111e-12</v>
+      </c>
+      <c r="I96" s="0">
+        <v>-2.6002683546036111e-12</v>
+      </c>
+      <c r="J96" s="0">
         <v>-0</v>
-      </c>
-      <c r="I96" s="0">
-        <v>2.6002683546036111e-12</v>
-      </c>
-      <c r="J96" s="0">
-        <v>-2.6002683546036111e-12</v>
       </c>
       <c r="K96" s="0">
         <v>-0</v>
       </c>
       <c r="L96" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M96" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N96" s="0">
+        <v>-24395043.420573317</v>
+      </c>
+      <c r="O96" s="0">
+        <v>-24395043.420573317</v>
+      </c>
+      <c r="P96" s="0">
+        <v>-24395042.263487004</v>
+      </c>
+      <c r="Q96" s="0">
+        <v>-6.7838766398463956e-07</v>
+      </c>
+      <c r="R96" s="0">
         <v>-1.0558965295419222e-08</v>
       </c>
-      <c r="O96" s="0">
+      <c r="S96" s="0">
         <v>8.7750198264475587e-08</v>
       </c>
-      <c r="P96" s="0">
-        <v>-6.7838766398463956e-07</v>
-      </c>
-      <c r="Q96" s="0">
-        <v>-24395042.263487004</v>
-      </c>
-      <c r="R96" s="0">
-        <v>-24395043.420573317</v>
-      </c>
-      <c r="S96" s="0">
-        <v>-24395043.420573317</v>
-      </c>
       <c r="T96" s="0">
-        <v>0</v>
+        <v>-0.00039856543682134659</v>
       </c>
       <c r="U96" s="0">
-        <v>0</v>
+        <v>0.00039856543682134659</v>
       </c>
       <c r="V96" s="0">
         <v>0</v>
@@ -8879,22 +9575,22 @@
         <v>0</v>
       </c>
       <c r="X96" s="0">
-        <v>-0.00039856543682134659</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="0">
-        <v>0.00039856543682134659</v>
+        <v>0</v>
       </c>
       <c r="Z96" s="0">
-        <v>2.7072081519319631</v>
+        <v>2.7072081594808739</v>
       </c>
       <c r="AA96" s="0">
-        <v>-3.0000000000026001</v>
+        <v>-3.3537090140031407</v>
       </c>
       <c r="AB96" s="0">
-        <v>-3.3537090064542299</v>
+        <v>-2.4999999999973999</v>
       </c>
       <c r="AC96" s="0">
-        <v>3.0000000000026001</v>
+        <v>2.4999999999973999</v>
       </c>
     </row>
     <row r="97">
@@ -8902,64 +9598,64 @@
         <v>9.5</v>
       </c>
       <c r="B97" s="0">
-        <v>2.6800054641217574</v>
+        <v>2.6800055029813241</v>
       </c>
       <c r="C97" s="0">
         <v>2.6800055029813241</v>
       </c>
       <c r="D97" s="0">
-        <v>2.6800055029813241</v>
+        <v>2.6800054641217574</v>
       </c>
       <c r="E97" s="0">
-        <v>-2.0340710192077842</v>
+        <v>-2.8058884659276564</v>
       </c>
       <c r="F97" s="0">
         <v>-2.6063527263585402</v>
       </c>
       <c r="G97" s="0">
-        <v>-2.8058884659276564</v>
+        <v>-2.0340710192077842</v>
       </c>
       <c r="H97" s="0">
+        <v>2.8185706564452445e-12</v>
+      </c>
+      <c r="I97" s="0">
+        <v>-2.8185706564452445e-12</v>
+      </c>
+      <c r="J97" s="0">
         <v>-0</v>
       </c>
-      <c r="I97" s="0">
-        <v>2.8185706564452445e-12</v>
-      </c>
-      <c r="J97" s="0">
-        <v>-2.8185706564452445e-12</v>
-      </c>
       <c r="K97" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L97" s="0">
         <v>0</v>
       </c>
       <c r="M97" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N97" s="0">
+        <v>-20562327.543093871</v>
+      </c>
+      <c r="O97" s="0">
+        <v>-20562327.543093871</v>
+      </c>
+      <c r="P97" s="0">
+        <v>-20562322.522558302</v>
+      </c>
+      <c r="Q97" s="0">
         <v>-2.2050794968697012e-08</v>
       </c>
-      <c r="O97" s="0">
+      <c r="R97" s="0">
         <v>7.7251681409748843e-08</v>
       </c>
-      <c r="P97" s="0">
+      <c r="S97" s="0">
         <v>2.8152903955325804e-06</v>
       </c>
-      <c r="Q97" s="0">
-        <v>-20562322.522558302</v>
-      </c>
-      <c r="R97" s="0">
-        <v>-20562327.543093871</v>
-      </c>
-      <c r="S97" s="0">
-        <v>-20562327.543093871</v>
-      </c>
       <c r="T97" s="0">
-        <v>0</v>
+        <v>-0.00036415063154976262</v>
       </c>
       <c r="U97" s="0">
-        <v>0</v>
+        <v>0.00036415063154976262</v>
       </c>
       <c r="V97" s="0">
         <v>0</v>
@@ -8968,22 +9664,22 @@
         <v>0</v>
       </c>
       <c r="X97" s="0">
-        <v>-0.00036415063154976262</v>
+        <v>0</v>
       </c>
       <c r="Y97" s="0">
-        <v>0.00036415063154976262</v>
+        <v>0</v>
       </c>
       <c r="Z97" s="0">
-        <v>2.6800054641217574</v>
+        <v>2.6800055029813241</v>
       </c>
       <c r="AA97" s="0">
-        <v>-3.0000000000028186</v>
+        <v>-3.3265063575035909</v>
       </c>
       <c r="AB97" s="0">
-        <v>-3.3265063186440242</v>
+        <v>-2.4999999999971814</v>
       </c>
       <c r="AC97" s="0">
-        <v>3.0000000000028186</v>
+        <v>2.4999999999971814</v>
       </c>
     </row>
     <row r="98">
@@ -8991,22 +9687,22 @@
         <v>9.5999999999999996</v>
       </c>
       <c r="B98" s="0">
-        <v>2.1171725685721601</v>
+        <v>2.1171725715070551</v>
       </c>
       <c r="C98" s="0">
         <v>2.1171725700884991</v>
       </c>
       <c r="D98" s="0">
-        <v>2.1171725715070551</v>
+        <v>2.1171725685721601</v>
       </c>
       <c r="E98" s="0">
+        <v>-2.7302458300995416</v>
+      </c>
+      <c r="F98" s="0">
+        <v>-2.8187137493238521</v>
+      </c>
+      <c r="G98" s="0">
         <v>-1.5329853865653418</v>
-      </c>
-      <c r="F98" s="0">
-        <v>-2.7302458300995416</v>
-      </c>
-      <c r="G98" s="0">
-        <v>-2.8187137493238521</v>
       </c>
       <c r="H98" s="0">
         <v>-0</v>
@@ -9018,13 +9714,13 @@
         <v>-0</v>
       </c>
       <c r="K98" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L98" s="0">
         <v>-0</v>
       </c>
       <c r="M98" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N98" s="0">
         <v>-598742.91464368009</v>
@@ -9063,16 +9759,16 @@
         <v>0</v>
       </c>
       <c r="Z98" s="0">
-        <v>2.1171725685721601</v>
+        <v>2.1171725715070551</v>
       </c>
       <c r="AA98" s="0">
-        <v>-3.5</v>
+        <v>-2.7636734260293219</v>
       </c>
       <c r="AB98" s="0">
-        <v>-2.7636734230944269</v>
+        <v>-2.5</v>
       </c>
       <c r="AC98" s="0">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="99">
@@ -9080,25 +9776,25 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="B99" s="0">
+        <v>-2.9640158658279638</v>
+      </c>
+      <c r="C99" s="0">
+        <v>-2.4940237924556876</v>
+      </c>
+      <c r="D99" s="0">
+        <v>-1.9360737608082321</v>
+      </c>
+      <c r="E99" s="0">
         <v>2.8083117050310231</v>
       </c>
-      <c r="C99" s="0">
+      <c r="F99" s="0">
         <v>2.8083117050509476</v>
       </c>
-      <c r="D99" s="0">
+      <c r="G99" s="0">
         <v>2.8083117128567978</v>
       </c>
-      <c r="E99" s="0">
-        <v>-1.9360737608082321</v>
-      </c>
-      <c r="F99" s="0">
-        <v>-2.4940237924556876</v>
-      </c>
-      <c r="G99" s="0">
-        <v>-2.9640158658279638</v>
-      </c>
       <c r="H99" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I99" s="0">
         <v>0</v>
@@ -9113,7 +9809,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N99" s="0">
         <v>-8.164576836215848e-09</v>
@@ -9152,16 +9848,16 @@
         <v>0</v>
       </c>
       <c r="Z99" s="0">
+        <v>-3.4548125595532899</v>
+      </c>
+      <c r="AA99" s="0">
         <v>2.8083117050310231</v>
       </c>
-      <c r="AA99" s="0">
-        <v>-4</v>
-      </c>
       <c r="AB99" s="0">
-        <v>-3.4548125595532899</v>
+        <v>-3</v>
       </c>
       <c r="AC99" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -9169,49 +9865,49 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="B100" s="0">
+        <v>-2.0285791743376378</v>
+      </c>
+      <c r="C100" s="0">
+        <v>-2.5828509790706451</v>
+      </c>
+      <c r="D100" s="0">
+        <v>-2.5828509790706451</v>
+      </c>
+      <c r="E100" s="0">
         <v>2.978605127798041</v>
       </c>
-      <c r="C100" s="0">
+      <c r="F100" s="0">
         <v>2.9786051725513771</v>
       </c>
-      <c r="D100" s="0">
+      <c r="G100" s="0">
         <v>2.9786051725555724</v>
       </c>
-      <c r="E100" s="0">
-        <v>-2.0285791743376378</v>
-      </c>
-      <c r="F100" s="0">
-        <v>-2.5828509790706451</v>
-      </c>
-      <c r="G100" s="0">
-        <v>-2.5828509790706451</v>
-      </c>
       <c r="H100" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I100" s="0">
-        <v>0</v>
+        <v>0.19933838837304968</v>
       </c>
       <c r="J100" s="0">
-        <v>0</v>
+        <v>-0.19933838837304968</v>
       </c>
       <c r="K100" s="0">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L100" s="0">
-        <v>0.19933838837304968</v>
+        <v>0</v>
       </c>
       <c r="M100" s="0">
-        <v>-0.19933838837304968</v>
+        <v>0</v>
       </c>
       <c r="N100" s="0">
-        <v>-2.8024519049263112e-08</v>
+        <v>-2.9141310966477421e-06</v>
       </c>
       <c r="O100" s="0">
         <v>-2.8024519049263112e-08</v>
       </c>
       <c r="P100" s="0">
-        <v>-2.9141310966477421e-06</v>
+        <v>-2.8024519049263112e-08</v>
       </c>
       <c r="Q100" s="0">
         <v>134238412.51228359</v>
@@ -9223,14 +9919,14 @@
         <v>134238450.26279727</v>
       </c>
       <c r="T100" s="0">
+        <v>0</v>
+      </c>
+      <c r="U100" s="0">
         <v>-8.5046015003553244e-08</v>
       </c>
-      <c r="U100" s="0">
+      <c r="V100" s="0">
         <v>8.5046015003553244e-08</v>
       </c>
-      <c r="V100" s="0">
-        <v>0</v>
-      </c>
       <c r="W100" s="0">
         <v>0</v>
       </c>
@@ -9241,16 +9937,16 @@
         <v>0</v>
       </c>
       <c r="Z100" s="0">
+        <v>-3.6251059823203078</v>
+      </c>
+      <c r="AA100" s="0">
         <v>2.978605127798041</v>
       </c>
-      <c r="AA100" s="0">
-        <v>-4.1993383883730493</v>
-      </c>
       <c r="AB100" s="0">
-        <v>-3.6251059823203078</v>
+        <v>-3</v>
       </c>
       <c r="AC100" s="0">
-        <v>4.1993383883730493</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -9258,28 +9954,28 @@
         <v>9.9000000000000004</v>
       </c>
       <c r="B101" s="0">
+        <v>-2.4977595896574889</v>
+      </c>
+      <c r="C101" s="0">
+        <v>-2.4977595896574889</v>
+      </c>
+      <c r="D101" s="0">
+        <v>-1.8985156282608995</v>
+      </c>
+      <c r="E101" s="0">
         <v>3.0981016943650173</v>
       </c>
-      <c r="C101" s="0">
+      <c r="F101" s="0">
         <v>3.0981016943899822</v>
       </c>
-      <c r="D101" s="0">
+      <c r="G101" s="0">
         <v>3.0981017001080833</v>
       </c>
-      <c r="E101" s="0">
-        <v>-1.8985156282608995</v>
-      </c>
-      <c r="F101" s="0">
-        <v>-2.4977595896574889</v>
-      </c>
-      <c r="G101" s="0">
-        <v>-2.4977595896574889</v>
-      </c>
       <c r="H101" s="0">
-        <v>0</v>
+        <v>-0.14622381344119753</v>
       </c>
       <c r="I101" s="0">
-        <v>0</v>
+        <v>0.14622381344119753</v>
       </c>
       <c r="J101" s="0">
         <v>0</v>
@@ -9288,10 +9984,10 @@
         <v>0</v>
       </c>
       <c r="L101" s="0">
-        <v>-0.14622381344119753</v>
+        <v>0</v>
       </c>
       <c r="M101" s="0">
-        <v>0.14622381344119753</v>
+        <v>0</v>
       </c>
       <c r="N101" s="0">
         <v>9.274419421545841e-08</v>
@@ -9330,16 +10026,16 @@
         <v>0</v>
       </c>
       <c r="Z101" s="0">
+        <v>-3.7446025488872841</v>
+      </c>
+      <c r="AA101" s="0">
         <v>3.0981016943650173</v>
       </c>
-      <c r="AA101" s="0">
-        <v>-4.1462238134411979</v>
-      </c>
       <c r="AB101" s="0">
-        <v>-3.7446025488872841</v>
+        <v>-3</v>
       </c>
       <c r="AC101" s="0">
-        <v>4.1462238134411979</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -9347,46 +10043,46 @@
         <v>10</v>
       </c>
       <c r="B102" s="0">
+        <v>-2.4842419362654566</v>
+      </c>
+      <c r="C102" s="0">
+        <v>-2.5430775399325212</v>
+      </c>
+      <c r="D102" s="0">
+        <v>-2.1583803905607009</v>
+      </c>
+      <c r="E102" s="0">
         <v>3.1953722743596686</v>
       </c>
-      <c r="C102" s="0">
+      <c r="F102" s="0">
         <v>3.1953723183020277</v>
       </c>
-      <c r="D102" s="0">
+      <c r="G102" s="0">
         <v>3.1953723183020277</v>
       </c>
-      <c r="E102" s="0">
-        <v>-2.1583803905607009</v>
-      </c>
-      <c r="F102" s="0">
-        <v>-2.4842419362654566</v>
-      </c>
-      <c r="G102" s="0">
-        <v>-2.5430775399325212</v>
-      </c>
       <c r="H102" s="0">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I102" s="0">
+        <v>0</v>
+      </c>
+      <c r="J102" s="0">
+        <v>0</v>
+      </c>
+      <c r="K102" s="0">
+        <v>0</v>
+      </c>
+      <c r="L102" s="0">
         <v>-5.7243213961150426e-13</v>
       </c>
-      <c r="J102" s="0">
+      <c r="M102" s="0">
         <v>5.7243213961150426e-13</v>
       </c>
-      <c r="K102" s="0">
-        <v>0</v>
-      </c>
-      <c r="L102" s="0">
-        <v>-0</v>
-      </c>
-      <c r="M102" s="0">
-        <v>0</v>
-      </c>
       <c r="N102" s="0">
+        <v>-1.6638650137031141e-07</v>
+      </c>
+      <c r="O102" s="0">
         <v>1.1496622654628739e-07</v>
-      </c>
-      <c r="O102" s="0">
-        <v>-1.6638650137031141e-07</v>
       </c>
       <c r="P102" s="0">
         <v>1.2891803137177045e-06</v>
@@ -9419,16 +10115,16 @@
         <v>0.0018848845018177595</v>
       </c>
       <c r="Z102" s="0">
+        <v>-3.8418731288819354</v>
+      </c>
+      <c r="AA102" s="0">
         <v>3.1953722743596686</v>
       </c>
-      <c r="AA102" s="0">
-        <v>-4.0000000000005729</v>
-      </c>
       <c r="AB102" s="0">
-        <v>-3.8418731288819354</v>
+        <v>-3</v>
       </c>
       <c r="AC102" s="0">
-        <v>4.0000000000005729</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
